--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -96,16 +96,13 @@
     <t>30.04.2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Réedition du cahier des charge</t>
+    <t xml:space="preserve">Réedition du cahier des charges</t>
   </si>
   <si>
     <t>Recherche</t>
   </si>
   <si>
-    <t xml:space="preserve">Création du dépot github + README</t>
-  </si>
-  <si>
-    <t>Maquettage</t>
+    <t xml:space="preserve">Création du dépot GitHub, arboressance du projet et README</t>
   </si>
   <si>
     <t>Programmation</t>
@@ -1622,7 +1619,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="200">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1655,22 +1652,16 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
@@ -2060,17 +2051,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" spc="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-CH"/>
@@ -2091,6 +2072,25 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2112,7 +2112,6 @@
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2129,7 +2128,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2146,7 +2144,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2163,7 +2160,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2180,7 +2176,6 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2197,13 +2192,30 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:bubble3D val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
               <a:solidFill>
                 <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -2221,7 +2233,35 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -2231,7 +2271,35 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -2241,7 +2309,35 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -2251,7 +2347,35 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -2261,7 +2385,35 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -2271,16 +2423,81 @@
               <c:showLegendKey val="0"/>
               <c:showPercent val="0"/>
               <c:showSerName val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
             </c:dLbl>
-            <c:dLblPos val="outEnd"/>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout/>
+              <c:showBubbleSize val="0"/>
+              <c:showCatName val="0"/>
+              <c:showLegendKey val="0"/>
+              <c:showPercent val="0"/>
+              <c:showSerName val="0"/>
+              <c:showVal val="0"/>
+              <c:spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr/>
+                </a:p>
+              </c:txPr>
+            </c:dLbl>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -2292,7 +2509,6 @@
             </c:spPr>
             <c:txPr>
               <a:bodyPr/>
-              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="900">
@@ -2307,30 +2523,106 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="fr-FR"/>
+                <a:endParaRPr/>
               </a:p>
             </c:txPr>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Journal!$G$3:$G$10</c:f>
+              <c:f>Journal!$G$3:$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Cours</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Plannification</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Recherche</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Documentation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Programmation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tests</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Présentation</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Journal!$H$3:$H$10</c:f>
+              <c:f>Journal!$H$3:$H$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0" H";@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
+          <c:showLeaderLines val="1"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
@@ -2385,8 +2677,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0">
-      <a:off x="10297559" y="68035"/>
-      <a:ext cx="3731404" cy="3020785"/>
+      <a:off x="9225996" y="181144"/>
+      <a:ext cx="3716096" cy="2951898"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -3041,7 +3333,598 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3624,16 +4507,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>153434</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>68035</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>367746</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>156481</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>458389</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>90996</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3643,8 +4526,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0">
-        <a:off x="10297559" y="68035"/>
-        <a:ext cx="3731404" cy="3020785"/>
+        <a:off x="9225996" y="181144"/>
+        <a:ext cx="3716096" cy="2951898"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4259,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
+        <f>types[[#This Row],[somme]]/$H$10</f>
         <v>0</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
@@ -4271,7 +5154,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28.5">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -4284,7 +5167,7 @@
       <c r="E4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
@@ -4292,23 +5175,23 @@
         <v>2.5</v>
       </c>
       <c r="I4" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.19230769230769232</v>
+        <f>types[[#This Row],[somme]]/$H$10</f>
+        <v>0.17241379310344829</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
     </row>
     <row r="5" ht="28.5">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="6">
         <v>0.125</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -4319,35 +5202,35 @@
         <v>0</v>
       </c>
       <c r="I5" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
+        <f>types[[#This Row],[somme]]/$H$10</f>
         <v>0</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I6" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0</v>
+        <f>types[[#This Row],[somme]]/$H$10</f>
+        <v>0.82758620689655171</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -4358,15 +5241,15 @@
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
       <c r="G7" s="9" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.80769230769230771</v>
+        <f>types[[#This Row],[somme]]/$H$10</f>
+        <v>0</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="13"/>
@@ -4384,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
+        <f>types[[#This Row],[somme]]/$H$10</f>
         <v>0</v>
       </c>
       <c r="J8" s="4"/>
@@ -4395,15 +5278,15 @@
       <c r="C9" s="6"/>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="16">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
       <c r="I9" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
+        <f>types[[#This Row],[somme]]/$H$10</f>
         <v>0</v>
       </c>
       <c r="J9" s="4"/>
@@ -4414,16 +5297,16 @@
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="19">
-        <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+      <c r="H10" s="10">
+        <f>SUM(H3:H9)</f>
+        <v>14.5</v>
       </c>
       <c r="I10" s="11">
-        <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0</v>
+        <f>types[[#This Row],[somme]]/$H$10</f>
+        <v>1</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -4433,13 +5316,7 @@
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
-      <c r="G11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="10">
-        <f>SUM(H3:H10)</f>
-        <v>13</v>
-      </c>
+      <c r="H11" s="10"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
@@ -4448,20 +5325,19 @@
       <c r="C12" s="6"/>
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
-      <c r="H12" s="10"/>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="10">
+        <f>SUM(Plannification!C2:S2)-H10</f>
+        <v>60.5</v>
+      </c>
     </row>
     <row r="13" ht="42.75">
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="8"/>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="10">
-        <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>62</v>
-      </c>
     </row>
     <row r="14" ht="28.5">
       <c r="B14" s="5"/>
@@ -4618,9 +5494,9 @@
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="22"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20"/>
     </row>
     <row r="40">
       <c r="B40" s="5"/>
@@ -4671,200 +5547,200 @@
       <c r="E47" s="8"/>
     </row>
     <row r="48" ht="28.5">
-      <c r="B48" s="23"/>
-      <c r="C48" s="24"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="42.75">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="57">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="28.5">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="B53" s="23"/>
-      <c r="C53" s="25"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="23"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="23"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="23"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="23"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="23"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="23"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="23"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="23"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="23"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="23"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="23"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="23"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="23"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="23"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="23"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="23"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="23"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="23"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="23"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="23"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="23"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="23"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="23"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="23"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="7"/>
-      <c r="C75" s="25"/>
+      <c r="C75" s="23"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="23"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="23"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="23"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="23"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
@@ -4884,7 +5760,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{0056003A-008B-49FD-9E76-00F80038006A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000A00DA-0098-4BB5-A4AB-00C2006100E6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -4921,1665 +5797,1665 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
+      <c r="A2" s="24" t="str" cm="1">
         <f t="array" ref="A2:A4">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="24" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="24" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
-        <v>0.14583333333333334</v>
+        <v>0.20833333333333331</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26"/>
-      <c r="C28" s="29">
+      <c r="A28" s="24"/>
+      <c r="C28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26"/>
-      <c r="C29" s="29">
+      <c r="A29" s="24"/>
+      <c r="C29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26"/>
-      <c r="C30" s="29">
+      <c r="A30" s="24"/>
+      <c r="C30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26"/>
-      <c r="C31" s="29">
+      <c r="A31" s="24"/>
+      <c r="C31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26"/>
-      <c r="C32" s="29">
+      <c r="A32" s="24"/>
+      <c r="C32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26"/>
-      <c r="C33" s="29">
+      <c r="A33" s="24"/>
+      <c r="C33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26"/>
-      <c r="C34" s="29">
+      <c r="A34" s="24"/>
+      <c r="C34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26"/>
-      <c r="C35" s="29">
+      <c r="A35" s="24"/>
+      <c r="C35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26"/>
-      <c r="C36" s="29">
+      <c r="A36" s="24"/>
+      <c r="C36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26"/>
-      <c r="C37" s="29">
+      <c r="A37" s="24"/>
+      <c r="C37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26"/>
-      <c r="C38" s="29">
+      <c r="A38" s="24"/>
+      <c r="C38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="24"/>
+      <c r="C39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="28"/>
+      <c r="B43" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="28"/>
+      <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="28"/>
+      <c r="B46" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="29"/>
+      <c r="B47" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="29"/>
+      <c r="B49" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="29"/>
+      <c r="B53" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="29"/>
+      <c r="B55" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="29"/>
+      <c r="B59" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="29"/>
+      <c r="B61" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="29"/>
+      <c r="B65" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="29"/>
+      <c r="B67" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="29"/>
+      <c r="B70" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="29"/>
+      <c r="B71" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="29"/>
+      <c r="B73" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="29"/>
+      <c r="B74" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="29"/>
+      <c r="B76" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="29"/>
+      <c r="B77" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="29"/>
+      <c r="B79" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="29"/>
+      <c r="B80" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="29"/>
+      <c r="B82" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="29"/>
+      <c r="B83" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="29"/>
+      <c r="B85" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="29"/>
+      <c r="B86" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="29"/>
+      <c r="B88" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="29"/>
+      <c r="B89" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="29"/>
+      <c r="B91" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="29"/>
+      <c r="B92" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="29"/>
+      <c r="B93" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="29"/>
+      <c r="B94" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="29"/>
+      <c r="B95" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="29"/>
+      <c r="B96" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="29"/>
+      <c r="B97" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="29"/>
+      <c r="B98" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="29"/>
+      <c r="B99" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="29"/>
+      <c r="B100" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="29"/>
+      <c r="B101" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="29"/>
+      <c r="B102" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="29"/>
+      <c r="B103" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="29"/>
+      <c r="B104" s="25" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="29"/>
+      <c r="B105" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="29"/>
+      <c r="B106" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="29"/>
+      <c r="B107" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="29"/>
+      <c r="B108" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="29"/>
+      <c r="B109" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="29"/>
+      <c r="B110" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="29"/>
+      <c r="B111" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="29"/>
+      <c r="B112" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="29"/>
+      <c r="B113" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="29"/>
+      <c r="B114" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="27"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="27"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="27"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="27"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="27"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="27"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="27"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="27"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="27"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="27"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="27"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="27"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="27"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="27"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="27"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="27"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="27"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="27"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="27"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="27"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="27"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="27"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="27"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="27"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="27"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="27"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="27"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="27"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="27"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="27"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="27"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="27"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="27"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="27"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="27"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="27"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="27"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="27"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="27"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6608,1266 +7484,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="33" t="s">
+    <row r="1" s="30" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="C1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="G1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="30"/>
+      <c r="AT1" s="30"/>
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+    </row>
+    <row r="2" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33">
+        <v>7</v>
+      </c>
+      <c r="D2" s="33">
+        <v>4</v>
+      </c>
+      <c r="E2" s="33">
+        <v>4</v>
+      </c>
+      <c r="F2" s="33">
+        <v>7</v>
+      </c>
+      <c r="G2" s="33">
         <v>5</v>
       </c>
-      <c r="D1" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="S1" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-    </row>
-    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="H2" s="33">
+        <v>7</v>
+      </c>
+      <c r="I2" s="34">
+        <v>0</v>
+      </c>
+      <c r="J2" s="34">
+        <v>0</v>
+      </c>
+      <c r="K2" s="33">
+        <v>5</v>
+      </c>
+      <c r="L2" s="33">
+        <v>4</v>
+      </c>
+      <c r="M2" s="33">
+        <v>7</v>
+      </c>
+      <c r="N2" s="33">
+        <v>4</v>
+      </c>
+      <c r="O2" s="33">
+        <v>5</v>
+      </c>
+      <c r="P2" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="33">
+        <v>4</v>
+      </c>
+      <c r="R2" s="33">
+        <v>7</v>
+      </c>
+      <c r="S2" s="33">
+        <v>5</v>
+      </c>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+    </row>
+    <row r="3" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35">
-        <v>7</v>
-      </c>
-      <c r="D2" s="35">
-        <v>4</v>
-      </c>
-      <c r="E2" s="35">
-        <v>4</v>
-      </c>
-      <c r="F2" s="35">
-        <v>7</v>
-      </c>
-      <c r="G2" s="35">
-        <v>5</v>
-      </c>
-      <c r="H2" s="35">
-        <v>7</v>
-      </c>
-      <c r="I2" s="36">
-        <v>0</v>
-      </c>
-      <c r="J2" s="36">
-        <v>0</v>
-      </c>
-      <c r="K2" s="35">
-        <v>5</v>
-      </c>
-      <c r="L2" s="35">
-        <v>4</v>
-      </c>
-      <c r="M2" s="35">
-        <v>7</v>
-      </c>
-      <c r="N2" s="35">
-        <v>4</v>
-      </c>
-      <c r="O2" s="35">
-        <v>5</v>
-      </c>
-      <c r="P2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
-        <v>4</v>
-      </c>
-      <c r="R2" s="35">
-        <v>7</v>
-      </c>
-      <c r="S2" s="35">
-        <v>5</v>
-      </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-    </row>
-    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="40" t="str">
+      <c r="C3" s="38" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42" t="str">
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42" t="str">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="40" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="51"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="49"/>
       <c r="V4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" t="s">
         <v>41</v>
       </c>
-      <c r="W4" t="s">
+    </row>
+    <row r="5" ht="10.5" customHeight="1">
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="57"/>
+    </row>
+    <row r="6" ht="10.5" customHeight="1">
+      <c r="A6" s="50"/>
+      <c r="B6" s="58" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="59"/>
-    </row>
-    <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="60" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="63"/>
+    </row>
+    <row r="7" ht="10.5" customHeight="1">
+      <c r="A7" s="50"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="63"/>
+    </row>
+    <row r="8" ht="10.5" customHeight="1">
+      <c r="A8" s="50"/>
+      <c r="B8" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="57"/>
+    </row>
+    <row r="9" ht="10.5" customHeight="1">
+      <c r="A9" s="50"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="53"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="57"/>
+    </row>
+    <row r="10" ht="10.5" customHeight="1">
+      <c r="A10" s="50"/>
+      <c r="B10" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="65"/>
-    </row>
-    <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="65"/>
-    </row>
-    <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="59"/>
-    </row>
-    <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="59"/>
-    </row>
-    <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="70" t="s">
+      <c r="C10" s="60"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="59"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="71"/>
+    </row>
+    <row r="11" ht="10.5" customHeight="1">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="76"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
+      <c r="S11" s="79"/>
+    </row>
+    <row r="12" ht="10.5" customHeight="1">
+      <c r="A12" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="73"/>
-    </row>
-    <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="81"/>
-    </row>
-    <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="82" t="s">
+      <c r="B12" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="49"/>
+    </row>
+    <row r="13" ht="10.5" customHeight="1">
+      <c r="A13" s="82"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="57"/>
+    </row>
+    <row r="14" ht="10.5" customHeight="1">
+      <c r="A14" s="82"/>
+      <c r="B14" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
-    </row>
-    <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="59"/>
-    </row>
-    <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="70" t="s">
+      <c r="C14" s="60"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="63"/>
+    </row>
+    <row r="15" ht="10.5" customHeight="1">
+      <c r="A15" s="82"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="63"/>
+    </row>
+    <row r="16" ht="10.5" customHeight="1">
+      <c r="A16" s="82"/>
+      <c r="B16" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="65"/>
-    </row>
-    <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="65"/>
-    </row>
-    <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="68" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="57"/>
+    </row>
+    <row r="17" ht="10.5" customHeight="1">
+      <c r="A17" s="82"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="57"/>
+    </row>
+    <row r="18" ht="10.5" customHeight="1">
+      <c r="A18" s="82"/>
+      <c r="B18" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
-    </row>
-    <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="59"/>
-    </row>
-    <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="70" t="s">
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="63"/>
+    </row>
+    <row r="19" ht="10.5" customHeight="1">
+      <c r="A19" s="83"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="79"/>
+    </row>
+    <row r="20" ht="10.5" customHeight="1">
+      <c r="A20" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="65"/>
-    </row>
-    <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="81"/>
-    </row>
-    <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="44" t="s">
+      <c r="B20" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="49"/>
+    </row>
+    <row r="21" ht="10.5" customHeight="1">
+      <c r="A21" s="50"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="57"/>
+    </row>
+    <row r="22" ht="10.5" customHeight="1">
+      <c r="A22" s="50"/>
+      <c r="B22" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="51"/>
-    </row>
-    <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="59"/>
-    </row>
-    <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="70" t="s">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="63"/>
+    </row>
+    <row r="23" ht="10.5" customHeight="1">
+      <c r="A23" s="50"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="63"/>
+    </row>
+    <row r="24" ht="10.5" customHeight="1">
+      <c r="A24" s="50"/>
+      <c r="B24" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="65"/>
-    </row>
-    <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="65"/>
-    </row>
-    <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="68" t="s">
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="57"/>
+    </row>
+    <row r="25" ht="10.5" customHeight="1">
+      <c r="A25" s="50"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="57"/>
+    </row>
+    <row r="26" ht="10.5" customHeight="1">
+      <c r="A26" s="50"/>
+      <c r="B26" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="59"/>
-    </row>
-    <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
-    </row>
-    <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="70" t="s">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="63"/>
+    </row>
+    <row r="27" ht="10.5" customHeight="1">
+      <c r="A27" s="50"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="63"/>
+    </row>
+    <row r="28" ht="10.5" customHeight="1">
+      <c r="A28" s="50"/>
+      <c r="B28" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="65"/>
-    </row>
-    <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="65"/>
-    </row>
-    <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="68" t="s">
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="57"/>
+    </row>
+    <row r="29" ht="10.5" customHeight="1">
+      <c r="A29" s="72"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="78"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="88"/>
+      <c r="N29" s="89"/>
+      <c r="O29" s="87"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="90"/>
+    </row>
+    <row r="30" ht="10.5" customHeight="1">
+      <c r="A30" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="59"/>
-    </row>
-    <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="92"/>
-    </row>
-    <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="93" t="s">
+      <c r="B30" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="93"/>
+      <c r="P30" s="93"/>
+      <c r="Q30" s="93"/>
+      <c r="R30" s="93"/>
+      <c r="S30" s="96"/>
+    </row>
+    <row r="31" ht="10.5" customHeight="1">
+      <c r="A31" s="97"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="63"/>
+    </row>
+    <row r="32" ht="10.5" customHeight="1">
+      <c r="A32" s="97"/>
+      <c r="B32" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="98"/>
-    </row>
-    <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="65"/>
-    </row>
-    <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="70" t="s">
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="69"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="57"/>
+    </row>
+    <row r="33" ht="10.5" customHeight="1">
+      <c r="A33" s="97"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="57"/>
+    </row>
+    <row r="34" ht="10.5" customHeight="1">
+      <c r="A34" s="97"/>
+      <c r="B34" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="59"/>
-    </row>
-    <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="59"/>
-    </row>
-    <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="70" t="s">
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="69"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="63"/>
+    </row>
+    <row r="35" ht="10.5" customHeight="1">
+      <c r="A35" s="97"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="61"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="60"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="63"/>
+    </row>
+    <row r="36" ht="10.5" customHeight="1">
+      <c r="A36" s="97"/>
+      <c r="B36" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="65"/>
-    </row>
-    <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="65"/>
-    </row>
-    <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="99"/>
-      <c r="B36" s="68" t="s">
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="59"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="57"/>
+    </row>
+    <row r="37" ht="10.5" customHeight="1">
+      <c r="A37" s="97"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="57"/>
+    </row>
+    <row r="38" ht="10.5" customHeight="1">
+      <c r="A38" s="97"/>
+      <c r="B38" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="59"/>
-    </row>
-    <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="99"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="59"/>
-    </row>
-    <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="99"/>
-      <c r="B38" s="70" t="s">
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="63"/>
+    </row>
+    <row r="39" ht="10.5" customHeight="1">
+      <c r="A39" s="97"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="63"/>
+    </row>
+    <row r="40" ht="10.5" customHeight="1">
+      <c r="A40" s="97"/>
+      <c r="B40" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="65"/>
-    </row>
-    <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="99"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="65"/>
-    </row>
-    <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="99"/>
-      <c r="B40" s="68" t="s">
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="59"/>
+      <c r="R40" s="59"/>
+      <c r="S40" s="57"/>
+    </row>
+    <row r="41" ht="10.5" customHeight="1">
+      <c r="A41" s="97"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="53"/>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="57"/>
+    </row>
+    <row r="42" ht="10.5" customHeight="1">
+      <c r="A42" s="97"/>
+      <c r="B42" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="59"/>
-    </row>
-    <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="99"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="59"/>
-    </row>
-    <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="99"/>
-      <c r="B42" s="70" t="s">
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="61"/>
+      <c r="N42" s="62"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="71"/>
+    </row>
+    <row r="43" ht="10.5" customHeight="1">
+      <c r="A43" s="98"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="74"/>
+      <c r="M43" s="76"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="74"/>
+      <c r="P43" s="74"/>
+      <c r="Q43" s="74"/>
+      <c r="R43" s="74"/>
+      <c r="S43" s="79"/>
+    </row>
+    <row r="44" ht="10.5" customHeight="1">
+      <c r="A44" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="63"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="73"/>
-    </row>
-    <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="100"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="44" t="s">
+      <c r="B44" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="45"/>
+      <c r="P44" s="45"/>
+      <c r="Q44" s="45"/>
+      <c r="R44" s="45"/>
+      <c r="S44" s="99"/>
+    </row>
+    <row r="45" ht="10.5" customHeight="1">
+      <c r="A45" s="50"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="53"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="57"/>
+      <c r="V45" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="B44" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="101"/>
-    </row>
-    <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="59"/>
-      <c r="V45" s="102" t="s">
+      <c r="W45" s="59"/>
+    </row>
+    <row r="46" ht="10.5" customHeight="1">
+      <c r="A46" s="50"/>
+      <c r="B46" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="W45" s="61"/>
-    </row>
-    <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="103" t="s">
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="62"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="71"/>
+      <c r="V46" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="73"/>
-      <c r="V46" s="102" t="s">
+      <c r="W46" s="52"/>
+    </row>
+    <row r="47" ht="10.5" customHeight="1">
+      <c r="A47" s="72"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="78"/>
+      <c r="J47" s="78"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="76"/>
+      <c r="N47" s="77"/>
+      <c r="O47" s="74"/>
+      <c r="P47" s="74"/>
+      <c r="Q47" s="74"/>
+      <c r="R47" s="74"/>
+      <c r="S47" s="79"/>
+      <c r="V47" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="W46" s="54"/>
-    </row>
-    <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="74"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="81"/>
-      <c r="V47" s="102" t="s">
+      <c r="W47" s="65"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="V54" s="103">
+        <v>46185</v>
+      </c>
+      <c r="W54" t="s">
         <v>68</v>
-      </c>
-      <c r="W47" s="67"/>
-    </row>
-    <row r="54" ht="14.25">
-      <c r="V54" s="105">
-        <v>46185</v>
-      </c>
-      <c r="W54" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -7875,7 +8751,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -7883,7 +8759,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -7947,801 +8823,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="106"/>
+      <c r="B1" s="104"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="108" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="107" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="F2" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="111" t="s">
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="111" t="s">
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="111" t="s">
+      <c r="S2" s="110"/>
+      <c r="AD2" s="28"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="113" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="114">
+        <v>4</v>
+      </c>
+      <c r="F3" s="115">
+        <v>1</v>
+      </c>
+      <c r="G3" s="116">
+        <v>2</v>
+      </c>
+      <c r="H3" s="116">
+        <v>3</v>
+      </c>
+      <c r="I3" s="114">
+        <v>4</v>
+      </c>
+      <c r="J3" s="115">
+        <v>1</v>
+      </c>
+      <c r="K3" s="116">
+        <v>2</v>
+      </c>
+      <c r="L3" s="116">
+        <v>3</v>
+      </c>
+      <c r="M3" s="114">
+        <v>4</v>
+      </c>
+      <c r="N3" s="115">
+        <v>1</v>
+      </c>
+      <c r="O3" s="116">
+        <v>2</v>
+      </c>
+      <c r="P3" s="116">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="114">
+        <v>4</v>
+      </c>
+      <c r="R3" s="115">
+        <v>1</v>
+      </c>
+      <c r="S3" s="117">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="AD2" s="30"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="116">
-        <v>4</v>
-      </c>
-      <c r="F3" s="117">
-        <v>1</v>
-      </c>
-      <c r="G3" s="118">
-        <v>2</v>
-      </c>
-      <c r="H3" s="118">
-        <v>3</v>
-      </c>
-      <c r="I3" s="116">
-        <v>4</v>
-      </c>
-      <c r="J3" s="117">
-        <v>1</v>
-      </c>
-      <c r="K3" s="118">
-        <v>2</v>
-      </c>
-      <c r="L3" s="118">
-        <v>3</v>
-      </c>
-      <c r="M3" s="116">
-        <v>4</v>
-      </c>
-      <c r="N3" s="117">
-        <v>1</v>
-      </c>
-      <c r="O3" s="118">
-        <v>2</v>
-      </c>
-      <c r="P3" s="118">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="116">
-        <v>4</v>
-      </c>
-      <c r="R3" s="117">
-        <v>1</v>
-      </c>
-      <c r="S3" s="119">
-        <v>2</v>
-      </c>
-      <c r="U3" t="s">
+    </row>
+    <row r="4" ht="12" customHeight="1">
+      <c r="B4" s="118" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="120" t="s">
+      <c r="C4" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="124"/>
+      <c r="U4" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
-      <c r="U4" t="s">
+    </row>
+    <row r="5" ht="12" customHeight="1">
+      <c r="B5" s="118"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="131"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="131"/>
+      <c r="O5" s="130"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="131"/>
+      <c r="S5" s="132"/>
+    </row>
+    <row r="6" ht="12" customHeight="1">
+      <c r="B6" s="118"/>
+      <c r="C6" s="133" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
-    </row>
-    <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="135" t="s">
+      <c r="D6" s="134"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="139"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="140"/>
+      <c r="U6" s="141" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="142"/>
-      <c r="U6" s="143" t="s">
+      <c r="V6" s="141"/>
+    </row>
+    <row r="7" ht="12" customHeight="1">
+      <c r="B7" s="118"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="132"/>
+      <c r="U7" t="s">
         <v>83</v>
       </c>
-      <c r="V6" s="143"/>
-    </row>
-    <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="134"/>
-      <c r="U7" t="s">
+    </row>
+    <row r="8" ht="12" customHeight="1">
+      <c r="B8" s="118"/>
+      <c r="C8" s="133" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="135" t="s">
+      <c r="D8" s="134"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="140"/>
+      <c r="U8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="142"/>
-      <c r="U8" t="s">
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="B9" s="118"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="132"/>
+    </row>
+    <row r="10" ht="12" customHeight="1">
+      <c r="B10" s="118"/>
+      <c r="C10" s="133" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="134"/>
-    </row>
-    <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="135" t="s">
+      <c r="D10" s="134"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="138"/>
+      <c r="P10" s="138"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="140"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="B11" s="142"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="148"/>
+      <c r="L11" s="148"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="148"/>
+      <c r="P11" s="148"/>
+      <c r="Q11" s="145"/>
+      <c r="R11" s="146"/>
+      <c r="S11" s="149"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="B12" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
-    </row>
-    <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="151"/>
-    </row>
-    <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="107" t="s">
+      <c r="C12" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="108" t="s">
+      <c r="D12" s="119"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="123"/>
+      <c r="S12" s="124"/>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="B13" s="118"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="131"/>
+      <c r="S13" s="132"/>
+    </row>
+    <row r="14" ht="12" customHeight="1">
+      <c r="B14" s="118"/>
+      <c r="C14" s="133" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
-    </row>
-    <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="134"/>
-    </row>
-    <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="135" t="s">
+      <c r="D14" s="152"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="140"/>
+    </row>
+    <row r="15" ht="12" customHeight="1">
+      <c r="B15" s="118"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="130"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="132"/>
+    </row>
+    <row r="16" ht="12" customHeight="1">
+      <c r="B16" s="118"/>
+      <c r="C16" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
-    </row>
-    <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="134"/>
-    </row>
-    <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="135" t="s">
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="138"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="140"/>
+    </row>
+    <row r="17" ht="12" customHeight="1">
+      <c r="B17" s="142"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="155"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="148"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="146"/>
+      <c r="O17" s="148"/>
+      <c r="P17" s="148"/>
+      <c r="Q17" s="145"/>
+      <c r="R17" s="146"/>
+      <c r="S17" s="149"/>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="B18" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
-    </row>
-    <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="151"/>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="109" t="s">
+      <c r="C18" s="106" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="D18" s="119"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="123"/>
+      <c r="S18" s="124"/>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="B19" s="118"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="131"/>
+      <c r="O19" s="130"/>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="131"/>
+      <c r="S19" s="132"/>
+    </row>
+    <row r="20" ht="12" customHeight="1">
+      <c r="B20" s="118"/>
+      <c r="C20" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
-    </row>
-    <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="129"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
-    </row>
-    <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="135" t="s">
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="154"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="138"/>
+      <c r="Q20" s="135"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="140"/>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="B21" s="118"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="130"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="156"/>
+      <c r="O21" s="130"/>
+      <c r="P21" s="130"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="132"/>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="B22" s="118"/>
+      <c r="C22" s="133" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
-    </row>
-    <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="134"/>
-    </row>
-    <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="135" t="s">
+      <c r="D22" s="134"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="139"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="138"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="140"/>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="148"/>
+      <c r="L23" s="148"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="148"/>
+      <c r="P23" s="148"/>
+      <c r="Q23" s="145"/>
+      <c r="R23" s="146"/>
+      <c r="S23" s="149"/>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="B24" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="141"/>
-      <c r="S22" s="142"/>
-    </row>
-    <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="151"/>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="109" t="s">
+      <c r="C24" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="D24" s="119"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="151"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="150"/>
+      <c r="P24" s="150"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="123"/>
+      <c r="S24" s="124"/>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="B25" s="118"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="130"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="130"/>
+      <c r="L25" s="130"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="130"/>
+      <c r="P25" s="130"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="132"/>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="B26" s="118"/>
+      <c r="C26" s="133" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="126"/>
-    </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="133"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="134"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="135" t="s">
+      <c r="D26" s="134"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="137"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="135"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="140"/>
+    </row>
+    <row r="27" ht="12" customHeight="1">
+      <c r="B27" s="118"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="127"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="130"/>
+      <c r="P27" s="130"/>
+      <c r="Q27" s="127"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="132"/>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="B28" s="118"/>
+      <c r="C28" s="133" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="141"/>
-      <c r="S26" s="142"/>
-    </row>
-    <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="134"/>
-    </row>
-    <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="135" t="s">
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="139"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="154"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="140"/>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="B29" s="118"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="158"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="161"/>
+      <c r="P29" s="160"/>
+      <c r="Q29" s="158"/>
+      <c r="R29" s="159"/>
+      <c r="S29" s="163"/>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="B30" s="164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="165" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="156"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
-    </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="162"/>
-      <c r="Q29" s="160"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="165"/>
-    </row>
-    <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="166" t="s">
+      <c r="D30" s="119"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="168"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="169"/>
+      <c r="R30" s="167"/>
+      <c r="S30" s="170"/>
+    </row>
+    <row r="31" ht="12" customHeight="1">
+      <c r="B31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="177"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="174"/>
+      <c r="Q31" s="176"/>
+      <c r="R31" s="174"/>
+      <c r="S31" s="132"/>
+    </row>
+    <row r="32" ht="12" customHeight="1">
+      <c r="B32" s="171"/>
+      <c r="C32" s="172" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="167" t="s">
+      <c r="D32" s="134"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="179"/>
+      <c r="K32" s="179"/>
+      <c r="L32" s="180"/>
+      <c r="M32" s="181"/>
+      <c r="N32" s="179"/>
+      <c r="O32" s="180"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="181"/>
+      <c r="R32" s="179"/>
+      <c r="S32" s="182"/>
+    </row>
+    <row r="33" ht="12" customHeight="1">
+      <c r="B33" s="171"/>
+      <c r="C33" s="172"/>
+      <c r="D33" s="126"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="177"/>
+      <c r="G33" s="174"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="184"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="177"/>
+      <c r="L33" s="175"/>
+      <c r="M33" s="176"/>
+      <c r="N33" s="174"/>
+      <c r="O33" s="175"/>
+      <c r="P33" s="174"/>
+      <c r="Q33" s="176"/>
+      <c r="R33" s="174"/>
+      <c r="S33" s="132"/>
+    </row>
+    <row r="34" ht="12" customHeight="1">
+      <c r="B34" s="171"/>
+      <c r="C34" s="125" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="172"/>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="177"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="134"/>
-    </row>
-    <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="183"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="183"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="184"/>
-    </row>
-    <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="177"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="178"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="134"/>
-    </row>
-    <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="173"/>
-      <c r="C34" s="127" t="s">
+      <c r="D34" s="157"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="187"/>
+      <c r="M34" s="188"/>
+      <c r="N34" s="186"/>
+      <c r="O34" s="187"/>
+      <c r="P34" s="186"/>
+      <c r="Q34" s="188"/>
+      <c r="R34" s="186"/>
+      <c r="S34" s="189"/>
+      <c r="U34" s="190"/>
+      <c r="V34" s="191" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="191"/>
-      <c r="U34" s="192"/>
-      <c r="V34" s="193" t="s">
+    </row>
+    <row r="35" ht="13.800000000000001" customHeight="1">
+      <c r="B35" s="192"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="144"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="195"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="197"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="196"/>
+      <c r="M35" s="197"/>
+      <c r="N35" s="195"/>
+      <c r="O35" s="196"/>
+      <c r="P35" s="195"/>
+      <c r="Q35" s="197"/>
+      <c r="R35" s="195"/>
+      <c r="S35" s="149"/>
+      <c r="U35" s="198"/>
+      <c r="V35" s="199" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="194"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="199"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="151"/>
-      <c r="U35" s="200"/>
-      <c r="V35" s="201" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>date</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t xml:space="preserve">Création du dépot GitHub, arboressance du projet et README</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche de protocol de comm. + recherche sur le projet</t>
   </si>
   <si>
     <t>Programmation</t>
@@ -1619,7 +1622,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="202">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1652,6 +1655,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1741,6 +1747,9 @@
     <xf fontId="0" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="3" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
@@ -4578,8 +4587,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E6">
-  <autoFilter ref="B2:E6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E7">
+  <autoFilter ref="B2:E7"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5176,7 +5185,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.17241379310344829</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5191,7 +5200,7 @@
       <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -5199,11 +5208,11 @@
       </c>
       <c r="H5" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0</v>
+        <v>0.12121212121212122</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5218,7 +5227,7 @@
       <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="9" t="s">
@@ -5230,18 +5239,26 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.82758620689655171</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7">
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G7" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
@@ -5260,7 +5277,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="G8" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
@@ -5278,10 +5295,10 @@
       <c r="C9" s="6"/>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
-      <c r="G9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="16">
+      <c r="G9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="17">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
@@ -5290,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="17"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10">
       <c r="B10" s="5"/>
@@ -5298,11 +5315,11 @@
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H3:H9)</f>
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
@@ -5326,11 +5343,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="10">
         <f>SUM(Plannification!C2:S2)-H10</f>
-        <v>60.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="13" ht="42.75">
@@ -5494,9 +5511,9 @@
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="20"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="21"/>
     </row>
     <row r="40">
       <c r="B40" s="5"/>
@@ -5547,200 +5564,200 @@
       <c r="E47" s="8"/>
     </row>
     <row r="48" ht="28.5">
-      <c r="B48" s="21"/>
-      <c r="C48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="23"/>
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="42.75">
-      <c r="B49" s="21"/>
-      <c r="C49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="57">
-      <c r="B50" s="21"/>
-      <c r="C50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="28.5">
-      <c r="B51" s="21"/>
-      <c r="C51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="21"/>
-      <c r="C52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="B53" s="21"/>
-      <c r="C53" s="23"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="21"/>
-      <c r="C54" s="23"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="24"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="21"/>
-      <c r="C55" s="23"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="21"/>
-      <c r="C56" s="23"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="21"/>
-      <c r="C57" s="23"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="21"/>
-      <c r="C58" s="23"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="21"/>
-      <c r="C59" s="23"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="21"/>
-      <c r="C60" s="23"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="24"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="21"/>
-      <c r="C61" s="23"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="21"/>
-      <c r="C62" s="23"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="21"/>
-      <c r="C63" s="23"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="21"/>
-      <c r="C64" s="23"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="21"/>
-      <c r="C65" s="23"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="21"/>
-      <c r="C66" s="23"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="21"/>
-      <c r="C67" s="23"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="21"/>
-      <c r="C68" s="23"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="21"/>
-      <c r="C69" s="23"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="21"/>
-      <c r="C70" s="23"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="21"/>
-      <c r="C71" s="23"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="21"/>
-      <c r="C72" s="23"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="21"/>
-      <c r="C73" s="23"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="21"/>
-      <c r="C74" s="23"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="7"/>
-      <c r="C75" s="23"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
@@ -5759,12 +5776,18 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{000A00DA-0098-4BB5-A4AB-00C2006100E6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
+        <x14:dataValidation xr:uid="{009D00F6-00B3-4783-BFDC-000100FE005C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D55</xm:sqref>
+          <xm:sqref>D8:D55</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{00BA004D-002C-4BC8-97ED-00FC00090041}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$G$3:$G$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5797,1665 +5820,1665 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str" cm="1">
+      <c r="A2" s="25" t="str" cm="1">
         <f t="array" ref="A2:A4">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
-        <v>0.20833333333333331</v>
+        <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24"/>
-      <c r="C28" s="27">
+      <c r="A28" s="25"/>
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="C29" s="27">
+      <c r="A29" s="25"/>
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24"/>
-      <c r="C30" s="27">
+      <c r="A30" s="25"/>
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24"/>
-      <c r="C31" s="27">
+      <c r="A31" s="25"/>
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24"/>
-      <c r="C32" s="27">
+      <c r="A32" s="25"/>
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24"/>
-      <c r="C33" s="27">
+      <c r="A33" s="25"/>
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24"/>
-      <c r="C34" s="27">
+      <c r="A34" s="25"/>
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24"/>
-      <c r="C35" s="27">
+      <c r="A35" s="25"/>
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24"/>
-      <c r="C36" s="27">
+      <c r="A36" s="25"/>
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24"/>
-      <c r="C37" s="27">
+      <c r="A37" s="25"/>
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24"/>
-      <c r="C38" s="27">
+      <c r="A38" s="25"/>
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="27"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="27"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="27"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7484,1266 +7507,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="32" t="s">
+    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="B1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="I1" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="K1" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="L1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="M1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="N1" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="O1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="Q1" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
-      <c r="AQ1" s="30"/>
-      <c r="AR1" s="30"/>
-      <c r="AS1" s="30"/>
-      <c r="AT1" s="30"/>
-      <c r="AU1" s="30"/>
-      <c r="AV1" s="30"/>
-      <c r="AW1" s="30"/>
-      <c r="AX1" s="30"/>
-      <c r="AY1" s="30"/>
-      <c r="AZ1" s="30"/>
-      <c r="BA1" s="30"/>
-      <c r="BB1" s="30"/>
-      <c r="BC1" s="30"/>
-    </row>
-    <row r="2" s="30" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33">
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+    </row>
+    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34">
         <v>7</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="34">
         <v>4</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="34">
         <v>4</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="34">
         <v>7</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="34">
         <v>5</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="34">
         <v>7</v>
       </c>
-      <c r="I2" s="34">
-        <v>0</v>
-      </c>
-      <c r="J2" s="34">
-        <v>0</v>
-      </c>
-      <c r="K2" s="33">
+      <c r="I2" s="35">
+        <v>0</v>
+      </c>
+      <c r="J2" s="35">
+        <v>0</v>
+      </c>
+      <c r="K2" s="34">
         <v>5</v>
       </c>
-      <c r="L2" s="33">
+      <c r="L2" s="34">
         <v>4</v>
       </c>
-      <c r="M2" s="33">
+      <c r="M2" s="34">
         <v>7</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="34">
         <v>4</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="34">
         <v>5</v>
       </c>
-      <c r="P2" s="33">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="33">
+      <c r="P2" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="34">
         <v>4</v>
       </c>
-      <c r="R2" s="33">
+      <c r="R2" s="34">
         <v>7</v>
       </c>
-      <c r="S2" s="33">
+      <c r="S2" s="34">
         <v>5</v>
       </c>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-    </row>
-    <row r="3" s="30" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+    </row>
+    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="38" t="str">
+      <c r="B3" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="39" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40" t="str">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="40" t="str">
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="41" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="49"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="50"/>
       <c r="V4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" t="s">
         <v>41</v>
       </c>
+      <c r="W4" s="51" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="57"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="59"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="50"/>
-      <c r="B6" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="63"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="50"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="63"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="66" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="57"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="59"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="57"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="59"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="71"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="73"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="79"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="81"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="81" t="s">
+      <c r="A12" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="49"/>
+      <c r="B12" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="50"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="57"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="59"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="68" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="63"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="65"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="82"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="63"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="57"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="59"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="82"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="57"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="59"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="63"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="65"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="83"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="79"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76"/>
+      <c r="S19" s="81"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="81" t="s">
+      <c r="A20" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="49"/>
+      <c r="B20" s="83" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="50"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="50"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="57"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="59"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="50"/>
-      <c r="B22" s="68" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="63"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="65"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="63"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="65"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="50"/>
-      <c r="B24" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="57"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="55"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="59"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="57"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="59"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="50"/>
-      <c r="B26" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="63"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="65"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="50"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="63"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="65"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="57"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="59"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="87"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="90"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="92"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="91" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="92" t="s">
+      <c r="A30" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="93"/>
-      <c r="P30" s="93"/>
-      <c r="Q30" s="93"/>
-      <c r="R30" s="93"/>
-      <c r="S30" s="96"/>
+      <c r="B30" s="94" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="98"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="60"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="63"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="65"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="97"/>
-      <c r="B32" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="57"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="59"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="97"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="57"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="59"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="97"/>
-      <c r="B34" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="60"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="60"/>
-      <c r="S34" s="63"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="65"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="97"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="60"/>
-      <c r="P35" s="60"/>
-      <c r="Q35" s="60"/>
-      <c r="R35" s="60"/>
-      <c r="S35" s="63"/>
+      <c r="A35" s="99"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="65"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="97"/>
-      <c r="B36" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="54"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="57"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="59"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="97"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="57"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="59"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="97"/>
-      <c r="B38" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="59"/>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="60"/>
-      <c r="S38" s="63"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="65"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="97"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="62"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="63"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="65"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="97"/>
-      <c r="B40" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="54"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="57"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="59"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="97"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="57"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="59"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="97"/>
-      <c r="B42" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="62"/>
-      <c r="O42" s="60"/>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="71"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="62"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="73"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="98"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="74"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="76"/>
-      <c r="N43" s="77"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="79"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="81"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="45"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="99"/>
+      <c r="A44" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="48"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="101"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="50"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="54"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="57"/>
-      <c r="V45" s="100" t="s">
-        <v>64</v>
-      </c>
-      <c r="W45" s="59"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="56"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="59"/>
+      <c r="V45" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="50"/>
-      <c r="B46" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="62"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="60"/>
-      <c r="M46" s="61"/>
-      <c r="N46" s="62"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="60"/>
-      <c r="R46" s="60"/>
-      <c r="S46" s="71"/>
-      <c r="V46" s="100" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="W46" s="52"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="62"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="73"/>
+      <c r="V46" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="W46" s="54"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="72"/>
-      <c r="B47" s="102"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="74"/>
-      <c r="L47" s="74"/>
-      <c r="M47" s="76"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="74"/>
-      <c r="Q47" s="74"/>
-      <c r="R47" s="74"/>
-      <c r="S47" s="79"/>
-      <c r="V47" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="W47" s="65"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="81"/>
+      <c r="V47" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="W47" s="67"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="103">
+      <c r="V54" s="105">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8751,7 +8774,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8759,7 +8782,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -8823,801 +8846,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="104"/>
+      <c r="B1" s="106"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="105" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="106" t="s">
+      <c r="B2" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="107" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="108" t="s">
+      <c r="C2" s="108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="109" t="s">
+      <c r="E2" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="109" t="s">
+      <c r="F2" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="109" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="109" t="s">
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="110"/>
-      <c r="AD2" s="28"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="112"/>
+      <c r="AD2" s="29"/>
     </row>
     <row r="3">
-      <c r="B3" s="111"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="113" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="114">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="116">
         <v>4</v>
       </c>
-      <c r="F3" s="115">
+      <c r="F3" s="117">
         <v>1</v>
       </c>
-      <c r="G3" s="116">
+      <c r="G3" s="118">
         <v>2</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="118">
         <v>3</v>
       </c>
-      <c r="I3" s="114">
+      <c r="I3" s="116">
         <v>4</v>
       </c>
-      <c r="J3" s="115">
+      <c r="J3" s="117">
         <v>1</v>
       </c>
-      <c r="K3" s="116">
+      <c r="K3" s="118">
         <v>2</v>
       </c>
-      <c r="L3" s="116">
+      <c r="L3" s="118">
         <v>3</v>
       </c>
-      <c r="M3" s="114">
+      <c r="M3" s="116">
         <v>4</v>
       </c>
-      <c r="N3" s="115">
+      <c r="N3" s="117">
         <v>1</v>
       </c>
-      <c r="O3" s="116">
+      <c r="O3" s="118">
         <v>2</v>
       </c>
-      <c r="P3" s="116">
+      <c r="P3" s="118">
         <v>3</v>
       </c>
-      <c r="Q3" s="114">
+      <c r="Q3" s="116">
         <v>4</v>
       </c>
-      <c r="R3" s="115">
+      <c r="R3" s="117">
         <v>1</v>
       </c>
-      <c r="S3" s="117">
+      <c r="S3" s="119">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="118" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="106" t="s">
+      <c r="B4" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="124"/>
+      <c r="C4" s="108" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="131"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="132"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="118"/>
-      <c r="C6" s="133" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="134"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="139"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="139"/>
-      <c r="S6" s="140"/>
-      <c r="U6" s="141" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="141"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="141"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="142"/>
+      <c r="U6" s="143" t="s">
+        <v>83</v>
+      </c>
+      <c r="V6" s="143"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="118"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="132"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="118"/>
-      <c r="C8" s="133" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="134"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="140"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="135" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="136"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="141"/>
+      <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="118"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="131"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="132"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="134"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="118"/>
-      <c r="C10" s="133" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="134"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
-      <c r="M10" s="135"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="140"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="136"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="142"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="142"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="148"/>
-      <c r="L11" s="148"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="148"/>
-      <c r="P11" s="148"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="146"/>
-      <c r="S11" s="149"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="148"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="151"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="106" t="s">
+      <c r="B12" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="119"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="123"/>
-      <c r="S12" s="124"/>
+      <c r="C12" s="108" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="125"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="118"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="131"/>
-      <c r="S13" s="132"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="134"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="118"/>
-      <c r="C14" s="133" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="152"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="139"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="135"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="140"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="142"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="118"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="132"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="155"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="134"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="118"/>
-      <c r="C16" s="133" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="139"/>
-      <c r="O16" s="138"/>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="140"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="136"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="142"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="155"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="148"/>
-      <c r="M17" s="145"/>
-      <c r="N17" s="146"/>
-      <c r="O17" s="148"/>
-      <c r="P17" s="148"/>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="146"/>
-      <c r="S17" s="149"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="151"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="107" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="106" t="s">
+      <c r="B18" s="109" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="119"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="123"/>
-      <c r="S18" s="124"/>
+      <c r="C18" s="108" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="121"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="125"/>
+      <c r="S18" s="126"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="118"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="131"/>
-      <c r="O19" s="130"/>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="127"/>
-      <c r="R19" s="131"/>
-      <c r="S19" s="132"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="118"/>
-      <c r="C20" s="133" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="154"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="138"/>
-      <c r="P20" s="138"/>
-      <c r="Q20" s="135"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="140"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="135" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="142"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="118"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="130"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="156"/>
-      <c r="O21" s="130"/>
-      <c r="P21" s="130"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="132"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="134"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="118"/>
-      <c r="C22" s="133" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="139"/>
-      <c r="O22" s="138"/>
-      <c r="P22" s="138"/>
-      <c r="Q22" s="135"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="140"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="141"/>
+      <c r="S22" s="142"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="148"/>
-      <c r="L23" s="148"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="146"/>
-      <c r="O23" s="148"/>
-      <c r="P23" s="148"/>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="146"/>
-      <c r="S23" s="149"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="150"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="150"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="150"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="151"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="107" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="106" t="s">
+      <c r="B24" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="120"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="151"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="150"/>
-      <c r="P24" s="150"/>
-      <c r="Q24" s="120"/>
-      <c r="R24" s="123"/>
-      <c r="S24" s="124"/>
+      <c r="C24" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="121"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="153"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="152"/>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="126"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="118"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="130"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="130"/>
-      <c r="L25" s="130"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="131"/>
-      <c r="O25" s="130"/>
-      <c r="P25" s="130"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="131"/>
-      <c r="S25" s="132"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="134"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="118"/>
-      <c r="C26" s="133" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="139"/>
-      <c r="O26" s="137"/>
-      <c r="P26" s="137"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="140"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="136"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="137"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="142"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="118"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="131"/>
-      <c r="O27" s="130"/>
-      <c r="P27" s="130"/>
-      <c r="Q27" s="127"/>
-      <c r="R27" s="131"/>
-      <c r="S27" s="132"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="133"/>
+      <c r="S27" s="134"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="118"/>
-      <c r="C28" s="133" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="139"/>
-      <c r="O28" s="138"/>
-      <c r="P28" s="137"/>
-      <c r="Q28" s="154"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="140"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="156"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="142"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="118"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="159"/>
-      <c r="K29" s="160"/>
-      <c r="L29" s="161"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="162"/>
-      <c r="O29" s="161"/>
-      <c r="P29" s="160"/>
-      <c r="Q29" s="158"/>
-      <c r="R29" s="159"/>
-      <c r="S29" s="163"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="163"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="163"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="163"/>
+      <c r="P29" s="162"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="165"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="165" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="119"/>
-      <c r="E30" s="166"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="169"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="167"/>
-      <c r="L30" s="168"/>
-      <c r="M30" s="169"/>
-      <c r="N30" s="167"/>
-      <c r="O30" s="168"/>
-      <c r="P30" s="167"/>
-      <c r="Q30" s="169"/>
-      <c r="R30" s="167"/>
-      <c r="S30" s="170"/>
+      <c r="C30" s="167" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="121"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="171"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="172"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="171"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="177"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="175"/>
-      <c r="P31" s="174"/>
-      <c r="Q31" s="176"/>
-      <c r="R31" s="174"/>
-      <c r="S31" s="132"/>
+      <c r="B31" s="173"/>
+      <c r="C31" s="174"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="177"/>
+      <c r="M31" s="178"/>
+      <c r="N31" s="176"/>
+      <c r="O31" s="177"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="178"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="134"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="171"/>
-      <c r="C32" s="172" t="s">
+      <c r="B32" s="173"/>
+      <c r="C32" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="134"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="179"/>
-      <c r="K32" s="179"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="181"/>
-      <c r="N32" s="179"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="181"/>
-      <c r="R32" s="179"/>
-      <c r="S32" s="182"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="183"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="183"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="184"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="172"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="173"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="174"/>
-      <c r="H33" s="183"/>
-      <c r="I33" s="184"/>
-      <c r="J33" s="174"/>
-      <c r="K33" s="177"/>
-      <c r="L33" s="175"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="174"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="174"/>
-      <c r="Q33" s="176"/>
-      <c r="R33" s="174"/>
-      <c r="S33" s="132"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="174"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="176"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="177"/>
+      <c r="M33" s="178"/>
+      <c r="N33" s="176"/>
+      <c r="O33" s="177"/>
+      <c r="P33" s="176"/>
+      <c r="Q33" s="178"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="134"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="171"/>
-      <c r="C34" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="157"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="187"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="186"/>
-      <c r="K34" s="186"/>
-      <c r="L34" s="187"/>
-      <c r="M34" s="188"/>
-      <c r="N34" s="186"/>
-      <c r="O34" s="187"/>
-      <c r="P34" s="186"/>
-      <c r="Q34" s="188"/>
-      <c r="R34" s="186"/>
-      <c r="S34" s="189"/>
-      <c r="U34" s="190"/>
-      <c r="V34" s="191" t="s">
+      <c r="B34" s="173"/>
+      <c r="C34" s="127" t="s">
         <v>101</v>
       </c>
+      <c r="D34" s="159"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="188"/>
+      <c r="O34" s="189"/>
+      <c r="P34" s="188"/>
+      <c r="Q34" s="190"/>
+      <c r="R34" s="188"/>
+      <c r="S34" s="191"/>
+      <c r="U34" s="192"/>
+      <c r="V34" s="193" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="192"/>
-      <c r="C35" s="193"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="196"/>
-      <c r="I35" s="197"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="196"/>
-      <c r="M35" s="197"/>
-      <c r="N35" s="195"/>
-      <c r="O35" s="196"/>
-      <c r="P35" s="195"/>
-      <c r="Q35" s="197"/>
-      <c r="R35" s="195"/>
-      <c r="S35" s="149"/>
-      <c r="U35" s="198"/>
-      <c r="V35" s="199" t="s">
-        <v>102</v>
+      <c r="B35" s="194"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="197"/>
+      <c r="Q35" s="199"/>
+      <c r="R35" s="197"/>
+      <c r="S35" s="151"/>
+      <c r="U35" s="200"/>
+      <c r="V35" s="201" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>date</t>
   </si>
@@ -111,7 +111,16 @@
     <t>Programmation</t>
   </si>
   <si>
+    <t>01.05.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche de composants</t>
+  </si>
+  <si>
     <t>Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des composant séléctionnés</t>
   </si>
   <si>
     <t>Présentation</t>
@@ -1659,6 +1668,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1747,9 +1759,6 @@
     <xf fontId="0" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf fontId="3" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
@@ -2855,6 +2864,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>30.04.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>01.05.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4587,8 +4599,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E7">
-  <autoFilter ref="B2:E7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E9">
+  <autoFilter ref="B2:E9"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5185,7 +5197,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.15151515151515152</v>
+        <v>0.11904761904761904</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5208,11 +5220,11 @@
       </c>
       <c r="H5" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>2</v>
+        <v>3.4999999999999996</v>
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.12121212121212122</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5235,17 +5247,17 @@
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.72727272727272729</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="6">
@@ -5254,7 +5266,7 @@
       <c r="D7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="9" t="s">
@@ -5272,12 +5284,20 @@
       <c r="K7" s="13"/>
     </row>
     <row r="8" ht="28.5">
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
+      <c r="B8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>19</v>
+      </c>
       <c r="G8" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
@@ -5291,14 +5311,22 @@
       <c r="K8" s="13"/>
     </row>
     <row r="9">
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="G9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="17">
+      <c r="B9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="18">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
@@ -5307,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="18"/>
+      <c r="K9" s="19"/>
     </row>
     <row r="10">
       <c r="B10" s="5"/>
@@ -5315,11 +5343,11 @@
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H3:H9)</f>
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
@@ -5343,11 +5371,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H12" s="10">
         <f>SUM(Plannification!C2:S2)-H10</f>
-        <v>58.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="42.75">
@@ -5511,9 +5539,9 @@
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="22"/>
     </row>
     <row r="40">
       <c r="B40" s="5"/>
@@ -5564,200 +5592,200 @@
       <c r="E47" s="8"/>
     </row>
     <row r="48" ht="28.5">
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="42.75">
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="57">
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="28.5">
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="B53" s="22"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="25"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="22"/>
-      <c r="C54" s="24"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="22"/>
-      <c r="C55" s="24"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="25"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="22"/>
-      <c r="C56" s="24"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="22"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="22"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="22"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="22"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="22"/>
-      <c r="C61" s="24"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="22"/>
-      <c r="C62" s="24"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="22"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="22"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="22"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="22"/>
-      <c r="C66" s="24"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="22"/>
-      <c r="C67" s="24"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="22"/>
-      <c r="C68" s="24"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="22"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="22"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="22"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="22"/>
-      <c r="C72" s="24"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="22"/>
-      <c r="C73" s="24"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="22"/>
-      <c r="C74" s="24"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="7"/>
-      <c r="C75" s="24"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="24"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="24"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="24"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="24"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="24"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
@@ -5777,13 +5805,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{009D00F6-00B3-4783-BFDC-000100FE005C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{0025001D-007C-4000-8E90-00BB00850032}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>D8:D55</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00BA004D-002C-4BC8-97ED-00FC00090041}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D7006A-002D-4CFE-8984-004900140053}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$9</xm:f>
           </x14:formula1>
@@ -5820,1665 +5848,1668 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="str" cm="1">
-        <f t="array" ref="A2:A4">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="26" t="str" cm="1">
+        <f t="array" ref="A2:A5">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="25"/>
-      <c r="B5" s="26">
+      <c r="A5" s="26" t="str">
+        <f/>
+        <v>01.05.2026</v>
+      </c>
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="27"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25"/>
-      <c r="C28" s="28">
+      <c r="A28" s="26"/>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25"/>
-      <c r="C29" s="28">
+      <c r="A29" s="26"/>
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25"/>
-      <c r="C30" s="28">
+      <c r="A30" s="26"/>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25"/>
-      <c r="C31" s="28">
+      <c r="A31" s="26"/>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25"/>
-      <c r="C32" s="28">
+      <c r="A32" s="26"/>
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="C33" s="28">
+      <c r="A33" s="26"/>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25"/>
-      <c r="C34" s="28">
+      <c r="A34" s="26"/>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25"/>
-      <c r="C35" s="28">
+      <c r="A35" s="26"/>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25"/>
-      <c r="C36" s="28">
+      <c r="A36" s="26"/>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25"/>
-      <c r="C37" s="28">
+      <c r="A37" s="26"/>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25"/>
-      <c r="C38" s="28">
+      <c r="A38" s="26"/>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25"/>
-      <c r="C39" s="28">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29"/>
-      <c r="B42" s="26" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29"/>
-      <c r="B43" s="26" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="26" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29"/>
-      <c r="B45" s="26" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29"/>
-      <c r="B46" s="26" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30"/>
-      <c r="B47" s="26" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30"/>
-      <c r="B48" s="26" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30"/>
-      <c r="B49" s="26" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30"/>
-      <c r="B50" s="26" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30"/>
-      <c r="B51" s="26" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30"/>
-      <c r="B52" s="26" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30"/>
-      <c r="B53" s="26" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30"/>
-      <c r="B54" s="26" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30"/>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30"/>
-      <c r="B56" s="26" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30"/>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30"/>
-      <c r="B58" s="26" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30"/>
-      <c r="B59" s="26" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30"/>
-      <c r="B60" s="26" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30"/>
-      <c r="B61" s="26" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30"/>
-      <c r="B62" s="26" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30"/>
-      <c r="B63" s="26" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30"/>
-      <c r="B64" s="26" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30"/>
-      <c r="B65" s="26" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30"/>
-      <c r="B66" s="26" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30"/>
-      <c r="B67" s="26" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30"/>
-      <c r="B68" s="26" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30"/>
-      <c r="B69" s="26" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30"/>
-      <c r="B70" s="26" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30"/>
-      <c r="B71" s="26" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30"/>
-      <c r="B72" s="26" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30"/>
-      <c r="B73" s="26" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30"/>
-      <c r="B74" s="26" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30"/>
-      <c r="B75" s="26" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30"/>
-      <c r="B76" s="26" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30"/>
-      <c r="B77" s="26" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30"/>
-      <c r="B78" s="26" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30"/>
-      <c r="B79" s="26" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30"/>
-      <c r="B80" s="26" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30"/>
-      <c r="B81" s="26" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30"/>
-      <c r="B82" s="26" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30"/>
-      <c r="B83" s="26" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30"/>
-      <c r="B84" s="26" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30"/>
-      <c r="B85" s="26" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30"/>
-      <c r="B86" s="26" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30"/>
-      <c r="B87" s="26" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30"/>
-      <c r="B88" s="26" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30"/>
-      <c r="B89" s="26" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30"/>
-      <c r="B90" s="26" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30"/>
-      <c r="B91" s="26" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30"/>
-      <c r="B92" s="26" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30"/>
-      <c r="B93" s="26" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30"/>
-      <c r="B94" s="26" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30"/>
-      <c r="B95" s="26" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30"/>
-      <c r="B96" s="26" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30"/>
-      <c r="B97" s="26" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30"/>
-      <c r="B98" s="26" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30"/>
-      <c r="B99" s="26" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30"/>
-      <c r="B100" s="26" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30"/>
-      <c r="B101" s="26" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30"/>
-      <c r="B102" s="26" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30"/>
-      <c r="B103" s="26" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30"/>
-      <c r="B104" s="26" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30"/>
-      <c r="B105" s="26" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30"/>
-      <c r="B106" s="26" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30"/>
-      <c r="B107" s="26" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="30"/>
-      <c r="B108" s="26" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30"/>
-      <c r="B109" s="26" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30"/>
-      <c r="B110" s="26" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30"/>
-      <c r="B111" s="26" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="30"/>
-      <c r="B112" s="26" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30"/>
-      <c r="B113" s="26" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30"/>
-      <c r="B114" s="26" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7507,293 +7538,293 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="34" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="35" t="s">
+      <c r="F1" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="G1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="H1" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="I1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="J1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="L1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="M1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="N1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="O1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="P1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="31"/>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="31"/>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="31"/>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-    </row>
-    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="Q1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="34">
+      <c r="R1" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+      <c r="AO1" s="32"/>
+      <c r="AP1" s="32"/>
+      <c r="AQ1" s="32"/>
+      <c r="AR1" s="32"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="32"/>
+      <c r="AU1" s="32"/>
+      <c r="AV1" s="32"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="32"/>
+      <c r="AY1" s="32"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="32"/>
+      <c r="BB1" s="32"/>
+      <c r="BC1" s="32"/>
+    </row>
+    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35">
         <v>7</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="35">
         <v>4</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="35">
         <v>4</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="35">
         <v>7</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="35">
         <v>5</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="35">
         <v>7</v>
       </c>
-      <c r="I2" s="35">
-        <v>0</v>
-      </c>
-      <c r="J2" s="35">
-        <v>0</v>
-      </c>
-      <c r="K2" s="34">
+      <c r="I2" s="36">
+        <v>0</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0</v>
+      </c>
+      <c r="K2" s="35">
         <v>5</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="35">
         <v>4</v>
       </c>
-      <c r="M2" s="34">
+      <c r="M2" s="35">
         <v>7</v>
       </c>
-      <c r="N2" s="34">
+      <c r="N2" s="35">
         <v>4</v>
       </c>
-      <c r="O2" s="34">
+      <c r="O2" s="35">
         <v>5</v>
       </c>
-      <c r="P2" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="34">
+      <c r="P2" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="35">
         <v>4</v>
       </c>
-      <c r="R2" s="34">
+      <c r="R2" s="35">
         <v>7</v>
       </c>
-      <c r="S2" s="34">
+      <c r="S2" s="35">
         <v>5</v>
       </c>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="31"/>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="31"/>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="31"/>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-    </row>
-    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="39" t="str">
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
+      <c r="AS2" s="32"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="32"/>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="32"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+    </row>
+    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41" t="str">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41" t="str">
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="42" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-      <c r="AK3" s="31"/>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="31"/>
-      <c r="AN3" s="31"/>
-      <c r="AO3" s="31"/>
-      <c r="AP3" s="31"/>
-      <c r="AQ3" s="31"/>
-      <c r="AR3" s="31"/>
-      <c r="AS3" s="31"/>
-      <c r="AT3" s="31"/>
-      <c r="AU3" s="31"/>
-      <c r="AV3" s="31"/>
-      <c r="AW3" s="31"/>
-      <c r="AX3" s="31"/>
-      <c r="AY3" s="31"/>
-      <c r="AZ3" s="31"/>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="31"/>
-      <c r="BC3" s="31"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AQ3" s="32"/>
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AV3" s="32"/>
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BA3" s="32"/>
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="50"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="51" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
@@ -7820,7 +7851,7 @@
     <row r="6" ht="10.5" customHeight="1">
       <c r="A6" s="52"/>
       <c r="B6" s="60" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="62"/>
@@ -7908,7 +7939,7 @@
     <row r="10" ht="10.5" customHeight="1">
       <c r="A10" s="52"/>
       <c r="B10" s="70" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="61"/>
@@ -7951,28 +7982,28 @@
     </row>
     <row r="12" ht="10.5" customHeight="1">
       <c r="A12" s="82" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B12" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="50"/>
+        <v>49</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="51"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
       <c r="A13" s="84"/>
@@ -7998,7 +8029,7 @@
     <row r="14" ht="10.5" customHeight="1">
       <c r="A14" s="84"/>
       <c r="B14" s="70" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" s="62"/>
       <c r="D14" s="61"/>
@@ -8042,7 +8073,7 @@
     <row r="16" ht="10.5" customHeight="1">
       <c r="A16" s="84"/>
       <c r="B16" s="68" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="61"/>
@@ -8086,7 +8117,7 @@
     <row r="18" ht="10.5" customHeight="1">
       <c r="A18" s="84"/>
       <c r="B18" s="70" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
@@ -8128,29 +8159,29 @@
       <c r="S19" s="81"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="43" t="s">
-        <v>50</v>
+      <c r="A20" s="44" t="s">
+        <v>53</v>
       </c>
       <c r="B20" s="83" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
+        <v>54</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="86"/>
       <c r="H20" s="87"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="51"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
       <c r="A21" s="52"/>
@@ -8176,7 +8207,7 @@
     <row r="22" ht="10.5" customHeight="1">
       <c r="A22" s="52"/>
       <c r="B22" s="70" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -8220,7 +8251,7 @@
     <row r="24" ht="10.5" customHeight="1">
       <c r="A24" s="52"/>
       <c r="B24" s="68" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
@@ -8264,7 +8295,7 @@
     <row r="26" ht="10.5" customHeight="1">
       <c r="A26" s="52"/>
       <c r="B26" s="70" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
@@ -8308,7 +8339,7 @@
     <row r="28" ht="10.5" customHeight="1">
       <c r="A28" s="52"/>
       <c r="B28" s="68" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C28" s="55"/>
       <c r="D28" s="55"/>
@@ -8351,10 +8382,10 @@
     </row>
     <row r="30" ht="10.5" customHeight="1">
       <c r="A30" s="93" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B30" s="94" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C30" s="95"/>
       <c r="D30" s="95"/>
@@ -8362,10 +8393,10 @@
       <c r="F30" s="95"/>
       <c r="G30" s="96"/>
       <c r="H30" s="97"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
       <c r="K30" s="95"/>
-      <c r="L30" s="45"/>
+      <c r="L30" s="46"/>
       <c r="M30" s="86"/>
       <c r="N30" s="87"/>
       <c r="O30" s="95"/>
@@ -8398,7 +8429,7 @@
     <row r="32" ht="10.5" customHeight="1">
       <c r="A32" s="99"/>
       <c r="B32" s="70" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C32" s="55"/>
       <c r="D32" s="55"/>
@@ -8442,7 +8473,7 @@
     <row r="34" ht="10.5" customHeight="1">
       <c r="A34" s="99"/>
       <c r="B34" s="70" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C34" s="62"/>
       <c r="D34" s="62"/>
@@ -8486,7 +8517,7 @@
     <row r="36" ht="10.5" customHeight="1">
       <c r="A36" s="99"/>
       <c r="B36" s="68" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
@@ -8530,7 +8561,7 @@
     <row r="38" ht="10.5" customHeight="1">
       <c r="A38" s="99"/>
       <c r="B38" s="70" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C38" s="62"/>
       <c r="D38" s="62"/>
@@ -8574,7 +8605,7 @@
     <row r="40" ht="10.5" customHeight="1">
       <c r="A40" s="99"/>
       <c r="B40" s="68" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55"/>
@@ -8618,7 +8649,7 @@
     <row r="42" ht="10.5" customHeight="1">
       <c r="A42" s="99"/>
       <c r="B42" s="70" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C42" s="62"/>
       <c r="D42" s="62"/>
@@ -8660,28 +8691,28 @@
       <c r="S43" s="81"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
+      <c r="A44" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
       <c r="S44" s="101"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
@@ -8705,14 +8736,14 @@
       <c r="R45" s="55"/>
       <c r="S45" s="59"/>
       <c r="V45" s="102" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
       <c r="A46" s="52"/>
       <c r="B46" s="103" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="62"/>
@@ -8732,7 +8763,7 @@
       <c r="R46" s="62"/>
       <c r="S46" s="73"/>
       <c r="V46" s="102" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W46" s="54"/>
     </row>
@@ -8757,7 +8788,7 @@
       <c r="R47" s="76"/>
       <c r="S47" s="81"/>
       <c r="V47" s="102" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="W47" s="67"/>
     </row>
@@ -8766,7 +8797,7 @@
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8774,7 +8805,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8782,7 +8813,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8850,46 +8881,46 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="107" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" s="111" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G2" s="111"/>
       <c r="H2" s="111"/>
       <c r="I2" s="110"/>
       <c r="J2" s="111" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K2" s="111"/>
       <c r="L2" s="111"/>
       <c r="M2" s="110"/>
       <c r="N2" s="111" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O2" s="111"/>
       <c r="P2" s="111"/>
       <c r="Q2" s="110"/>
       <c r="R2" s="111" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="S2" s="112"/>
-      <c r="AD2" s="29"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
       <c r="B3" s="113"/>
       <c r="C3" s="114"/>
       <c r="D3" s="115" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" s="116">
         <v>4</v>
@@ -8937,15 +8968,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="120" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="122"/>
@@ -8964,7 +8995,7 @@
       <c r="R4" s="125"/>
       <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -8990,7 +9021,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="120"/>
       <c r="C6" s="135" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D6" s="136"/>
       <c r="E6" s="137"/>
@@ -9009,7 +9040,7 @@
       <c r="R6" s="141"/>
       <c r="S6" s="142"/>
       <c r="U6" s="143" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="V6" s="143"/>
     </row>
@@ -9033,13 +9064,13 @@
       <c r="R7" s="133"/>
       <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="120"/>
       <c r="C8" s="135" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" s="136"/>
       <c r="E8" s="137"/>
@@ -9058,7 +9089,7 @@
       <c r="R8" s="141"/>
       <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -9084,7 +9115,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="120"/>
       <c r="C10" s="135" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D10" s="136"/>
       <c r="E10" s="137"/>
@@ -9125,10 +9156,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="107" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" s="108" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D12" s="121"/>
       <c r="E12" s="122"/>
@@ -9170,7 +9201,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="120"/>
       <c r="C14" s="135" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" s="154"/>
       <c r="E14" s="137"/>
@@ -9212,7 +9243,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="120"/>
       <c r="C16" s="135" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D16" s="136"/>
       <c r="E16" s="137"/>
@@ -9253,10 +9284,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="109" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C18" s="108" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D18" s="121"/>
       <c r="E18" s="122"/>
@@ -9298,7 +9329,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="120"/>
       <c r="C20" s="135" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="136"/>
       <c r="E20" s="137"/>
@@ -9340,7 +9371,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="120"/>
       <c r="C22" s="135" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D22" s="136"/>
       <c r="E22" s="137"/>
@@ -9381,10 +9412,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="109" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C24" s="108" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D24" s="121"/>
       <c r="E24" s="122"/>
@@ -9426,7 +9457,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="120"/>
       <c r="C26" s="135" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D26" s="136"/>
       <c r="E26" s="137"/>
@@ -9468,7 +9499,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="120"/>
       <c r="C28" s="135" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D28" s="136"/>
       <c r="E28" s="137"/>
@@ -9512,7 +9543,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="167" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D30" s="121"/>
       <c r="E30" s="168"/>
@@ -9596,7 +9627,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="173"/>
       <c r="C34" s="127" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D34" s="159"/>
       <c r="E34" s="187"/>
@@ -9616,7 +9647,7 @@
       <c r="S34" s="191"/>
       <c r="U34" s="192"/>
       <c r="V34" s="193" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9640,7 +9671,7 @@
       <c r="S35" s="151"/>
       <c r="U35" s="200"/>
       <c r="V35" s="201" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>date</t>
   </si>
@@ -126,7 +126,13 @@
     <t>Présentation</t>
   </si>
   <si>
+    <t xml:space="preserve">Recherche des composant chez distributeur</t>
+  </si>
+  <si>
     <t>Somme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création d'une liste de composant avec prix</t>
   </si>
   <si>
     <t xml:space="preserve">Temps restant </t>
@@ -1664,15 +1670,6 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1680,6 +1677,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
@@ -4599,8 +4605,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E9">
-  <autoFilter ref="B2:E9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E11">
+  <autoFilter ref="B2:E11"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5197,7 +5203,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.11904761904761904</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5220,11 +5226,11 @@
       </c>
       <c r="H5" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>3.4999999999999996</v>
+        <v>5.9999999999999991</v>
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.16666666666666666</v>
+        <v>0.24999999999999997</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5247,11 +5253,11 @@
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.7142857142857143</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5284,16 +5290,16 @@
       <c r="K7" s="13"/>
     </row>
     <row r="8" ht="28.5">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="6">
-        <v>0.0625</v>
-      </c>
-      <c r="D8" s="15" t="s">
+        <v>0.125</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="9" t="s">
@@ -5311,22 +5317,22 @@
       <c r="K8" s="13"/>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="6">
         <v>0.125</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="15">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
@@ -5335,19 +5341,27 @@
         <v>0</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="19"/>
+      <c r="K9" s="16"/>
     </row>
     <row r="10">
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
+      <c r="B10" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="G10" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H3:H9)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$10</f>
@@ -5357,10 +5371,18 @@
       <c r="K10" s="4"/>
     </row>
     <row r="11" ht="28.5">
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="B11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>25</v>
+      </c>
       <c r="H11" s="10"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5371,11 +5393,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H12" s="10">
         <f>SUM(Plannification!C2:S2)-H10</f>
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="42.75">
@@ -5805,13 +5827,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{0025001D-007C-4000-8E90-00BB00850032}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00AB00E0-0001-4D04-93E1-00A4001C0040}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>D8:D55</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00D7006A-002D-4CFE-8984-004900140053}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00210008-00AD-44E6-9F69-001400A400C0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$9</xm:f>
           </x14:formula1>
@@ -5887,7 +5909,7 @@
       </c>
       <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
-        <v>0.1875</v>
+        <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
@@ -7540,10 +7562,10 @@
   <sheetData>
     <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="A1" s="33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="35" t="s">
         <v>5</v>
@@ -7555,46 +7577,46 @@
         <v>12</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
@@ -7635,7 +7657,7 @@
     </row>
     <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
       <c r="A2" s="33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="35">
@@ -7728,10 +7750,10 @@
     </row>
     <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
@@ -7821,10 +7843,10 @@
       <c r="R4" s="47"/>
       <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
@@ -7851,7 +7873,7 @@
     <row r="6" ht="10.5" customHeight="1">
       <c r="A6" s="52"/>
       <c r="B6" s="60" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="62"/>
@@ -7939,7 +7961,7 @@
     <row r="10" ht="10.5" customHeight="1">
       <c r="A10" s="52"/>
       <c r="B10" s="70" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="61"/>
@@ -7982,10 +8004,10 @@
     </row>
     <row r="12" ht="10.5" customHeight="1">
       <c r="A12" s="82" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="83" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="46"/>
@@ -8029,7 +8051,7 @@
     <row r="14" ht="10.5" customHeight="1">
       <c r="A14" s="84"/>
       <c r="B14" s="70" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" s="62"/>
       <c r="D14" s="61"/>
@@ -8073,7 +8095,7 @@
     <row r="16" ht="10.5" customHeight="1">
       <c r="A16" s="84"/>
       <c r="B16" s="68" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="61"/>
@@ -8117,7 +8139,7 @@
     <row r="18" ht="10.5" customHeight="1">
       <c r="A18" s="84"/>
       <c r="B18" s="70" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
@@ -8160,10 +8182,10 @@
     </row>
     <row r="20" ht="10.5" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="83" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="47"/>
@@ -8207,7 +8229,7 @@
     <row r="22" ht="10.5" customHeight="1">
       <c r="A22" s="52"/>
       <c r="B22" s="70" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -8251,7 +8273,7 @@
     <row r="24" ht="10.5" customHeight="1">
       <c r="A24" s="52"/>
       <c r="B24" s="68" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
@@ -8295,7 +8317,7 @@
     <row r="26" ht="10.5" customHeight="1">
       <c r="A26" s="52"/>
       <c r="B26" s="70" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
@@ -8339,7 +8361,7 @@
     <row r="28" ht="10.5" customHeight="1">
       <c r="A28" s="52"/>
       <c r="B28" s="68" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" s="55"/>
       <c r="D28" s="55"/>
@@ -8382,10 +8404,10 @@
     </row>
     <row r="30" ht="10.5" customHeight="1">
       <c r="A30" s="93" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="94" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C30" s="95"/>
       <c r="D30" s="95"/>
@@ -8429,7 +8451,7 @@
     <row r="32" ht="10.5" customHeight="1">
       <c r="A32" s="99"/>
       <c r="B32" s="70" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" s="55"/>
       <c r="D32" s="55"/>
@@ -8473,7 +8495,7 @@
     <row r="34" ht="10.5" customHeight="1">
       <c r="A34" s="99"/>
       <c r="B34" s="70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C34" s="62"/>
       <c r="D34" s="62"/>
@@ -8517,7 +8539,7 @@
     <row r="36" ht="10.5" customHeight="1">
       <c r="A36" s="99"/>
       <c r="B36" s="68" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
@@ -8561,7 +8583,7 @@
     <row r="38" ht="10.5" customHeight="1">
       <c r="A38" s="99"/>
       <c r="B38" s="70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C38" s="62"/>
       <c r="D38" s="62"/>
@@ -8605,7 +8627,7 @@
     <row r="40" ht="10.5" customHeight="1">
       <c r="A40" s="99"/>
       <c r="B40" s="68" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55"/>
@@ -8649,7 +8671,7 @@
     <row r="42" ht="10.5" customHeight="1">
       <c r="A42" s="99"/>
       <c r="B42" s="70" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C42" s="62"/>
       <c r="D42" s="62"/>
@@ -8692,7 +8714,7 @@
     </row>
     <row r="44" ht="10.5" customHeight="1">
       <c r="A44" s="44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B44" s="45" t="s">
         <v>22</v>
@@ -8736,14 +8758,14 @@
       <c r="R45" s="55"/>
       <c r="S45" s="59"/>
       <c r="V45" s="102" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
       <c r="A46" s="52"/>
       <c r="B46" s="103" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="62"/>
@@ -8763,7 +8785,7 @@
       <c r="R46" s="62"/>
       <c r="S46" s="73"/>
       <c r="V46" s="102" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="W46" s="54"/>
     </row>
@@ -8788,7 +8810,7 @@
       <c r="R47" s="76"/>
       <c r="S47" s="81"/>
       <c r="V47" s="102" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W47" s="67"/>
     </row>
@@ -8797,7 +8819,7 @@
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8805,7 +8827,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8813,7 +8835,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -8881,37 +8903,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="107" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="108" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2" s="111" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" s="111"/>
       <c r="H2" s="111"/>
       <c r="I2" s="110"/>
       <c r="J2" s="111" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K2" s="111"/>
       <c r="L2" s="111"/>
       <c r="M2" s="110"/>
       <c r="N2" s="111" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" s="111"/>
       <c r="P2" s="111"/>
       <c r="Q2" s="110"/>
       <c r="R2" s="111" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S2" s="112"/>
       <c r="AD2" s="30"/>
@@ -8920,7 +8942,7 @@
       <c r="B3" s="113"/>
       <c r="C3" s="114"/>
       <c r="D3" s="115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" s="116">
         <v>4</v>
@@ -8968,15 +8990,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="120" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="122"/>
@@ -8995,7 +9017,7 @@
       <c r="R4" s="125"/>
       <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -9021,7 +9043,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="120"/>
       <c r="C6" s="135" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" s="136"/>
       <c r="E6" s="137"/>
@@ -9040,7 +9062,7 @@
       <c r="R6" s="141"/>
       <c r="S6" s="142"/>
       <c r="U6" s="143" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V6" s="143"/>
     </row>
@@ -9064,13 +9086,13 @@
       <c r="R7" s="133"/>
       <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="120"/>
       <c r="C8" s="135" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" s="136"/>
       <c r="E8" s="137"/>
@@ -9089,7 +9111,7 @@
       <c r="R8" s="141"/>
       <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -9115,7 +9137,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="120"/>
       <c r="C10" s="135" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="136"/>
       <c r="E10" s="137"/>
@@ -9156,10 +9178,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="107" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" s="108" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="121"/>
       <c r="E12" s="122"/>
@@ -9201,7 +9223,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="120"/>
       <c r="C14" s="135" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D14" s="154"/>
       <c r="E14" s="137"/>
@@ -9243,7 +9265,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="120"/>
       <c r="C16" s="135" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="136"/>
       <c r="E16" s="137"/>
@@ -9284,10 +9306,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="109" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C18" s="108" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D18" s="121"/>
       <c r="E18" s="122"/>
@@ -9329,7 +9351,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="120"/>
       <c r="C20" s="135" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D20" s="136"/>
       <c r="E20" s="137"/>
@@ -9371,7 +9393,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="120"/>
       <c r="C22" s="135" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D22" s="136"/>
       <c r="E22" s="137"/>
@@ -9412,10 +9434,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="109" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C24" s="108" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D24" s="121"/>
       <c r="E24" s="122"/>
@@ -9457,7 +9479,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="120"/>
       <c r="C26" s="135" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D26" s="136"/>
       <c r="E26" s="137"/>
@@ -9499,7 +9521,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="120"/>
       <c r="C28" s="135" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D28" s="136"/>
       <c r="E28" s="137"/>
@@ -9543,7 +9565,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="167" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D30" s="121"/>
       <c r="E30" s="168"/>
@@ -9627,7 +9649,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="173"/>
       <c r="C34" s="127" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D34" s="159"/>
       <c r="E34" s="187"/>
@@ -9647,7 +9669,7 @@
       <c r="S34" s="191"/>
       <c r="U34" s="192"/>
       <c r="V34" s="193" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9671,7 +9693,7 @@
       <c r="S35" s="151"/>
       <c r="U35" s="200"/>
       <c r="V35" s="201" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -12,7 +12,7 @@
     <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$34</definedName>
   </definedNames>
   <calcPr concurrentCalc="0"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>date</t>
   </si>
@@ -123,16 +123,22 @@
     <t xml:space="preserve">Documentation des composant séléctionnés</t>
   </si>
   <si>
+    <t>Prototypage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche des composant chez distributeur</t>
+  </si>
+  <si>
     <t>Présentation</t>
   </si>
   <si>
-    <t xml:space="preserve">Recherche des composant chez distributeur</t>
+    <t xml:space="preserve">Création d'une liste de composant avec prix</t>
   </si>
   <si>
     <t>Somme</t>
   </si>
   <si>
-    <t xml:space="preserve">Création d'une liste de composant avec prix</t>
+    <t xml:space="preserve">Ajout des différentes librairies sur KiCad</t>
   </si>
   <si>
     <t xml:space="preserve">Temps restant </t>
@@ -1637,7 +1643,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="201">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1670,6 +1676,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1677,14 +1686,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -2123,9 +2126,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.049720"/>
+          <c:x val="0.199440"/>
           <c:y val="0.130670"/>
-          <c:w val="0.900540"/>
+          <c:w val="0.596420"/>
           <c:h val="0.701530"/>
         </c:manualLayout>
       </c:layout>
@@ -2575,17 +2578,17 @@
                   <c:v>Tests</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Présentation</c:v>
+                  <c:v>Prototypage</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Journal!$H$3:$H$9</c:f>
+              <c:f>Journal!$H$3:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>0.0" H";@</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2593,10 +2596,10 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.999999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>15.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2605,6 +2608,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2701,8 +2707,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0">
-      <a:off x="9225996" y="181144"/>
-      <a:ext cx="3716096" cy="2951898"/>
+      <a:off x="9234654" y="182658"/>
+      <a:ext cx="3713606" cy="3157227"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -2873,6 +2879,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>01.05.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5/4/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4535,15 +4544,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>367746</xdr:colOff>
+      <xdr:colOff>367745</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2550</xdr:rowOff>
+      <xdr:rowOff>2549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>458389</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>90996</xdr:rowOff>
+      <xdr:colOff>458388</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>90995</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4553,8 +4562,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0">
-        <a:off x="9225996" y="181144"/>
-        <a:ext cx="3716096" cy="2951898"/>
+        <a:off x="9234654" y="182658"/>
+        <a:ext cx="3713606" cy="3157227"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4605,8 +4614,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E11">
-  <autoFilter ref="B2:E11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E12">
+  <autoFilter ref="B2:E12"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5169,15 +5178,15 @@
         <v>0</v>
       </c>
       <c r="I3" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
+        <f>types[[#This Row],[somme]]/$H$11</f>
         <v>0</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
-        <f t="array" ref="J3">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
+        <f t="array" ref="J3">_xlfn._xlws.FILTER(G3:G11,H3:H11&gt;0)</f>
         <v>Plannification</v>
       </c>
       <c r="K3" s="13" cm="1">
-        <f t="array" ref="K3">_xlfn._xlws.FILTER(H3:H10,H3:H10&gt;0)</f>
+        <f t="array" ref="K3">_xlfn._xlws.FILTER(H3:H11,H3:H11&gt;0)</f>
         <v>2.5</v>
       </c>
     </row>
@@ -5202,8 +5211,8 @@
         <v>2.5</v>
       </c>
       <c r="I4" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.10416666666666667</v>
+        <f>types[[#This Row],[somme]]/$H$11</f>
+        <v>9.6153846153846159e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5229,8 +5238,8 @@
         <v>5.9999999999999991</v>
       </c>
       <c r="I5" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.24999999999999997</v>
+        <f>types[[#This Row],[somme]]/$H$11</f>
+        <v>0.23076923076923073</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5240,7 +5249,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
@@ -5256,8 +5265,8 @@
         <v>15.5</v>
       </c>
       <c r="I6" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0.64583333333333337</v>
+        <f>types[[#This Row],[somme]]/$H$11</f>
+        <v>0.59615384615384615</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5267,7 +5276,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5283,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
+        <f>types[[#This Row],[somme]]/$H$11</f>
         <v>0</v>
       </c>
       <c r="J7" s="4"/>
@@ -5310,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
+        <f>types[[#This Row],[somme]]/$H$11</f>
         <v>0</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="13"/>
     </row>
-    <row r="9">
+    <row r="9" ht="28.5">
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
@@ -5332,83 +5341,99 @@
       <c r="G9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I9" s="11"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="16"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10">
-        <f>SUM(H3:H9)</f>
-        <v>24</v>
+      <c r="H10" s="16">
+        <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
+        <v>0</v>
       </c>
       <c r="I10" s="11">
-        <f>types[[#This Row],[somme]]/$H$10</f>
+        <f>types[[#This Row],[somme]]/$H$11</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="10">
+        <f>SUM(H3:H10)</f>
+        <v>26</v>
+      </c>
+      <c r="I11" s="11">
+        <f>types[[#This Row],[somme]]/$H$11</f>
         <v>1</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" ht="28.5">
-      <c r="B11" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="10"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12">
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="10">
-        <f>SUM(Plannification!C2:S2)-H10</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" ht="42.75">
+    <row r="12" ht="28.5">
+      <c r="B12" s="5">
+        <v>46146</v>
+      </c>
+      <c r="C12" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13">
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="8"/>
-    </row>
-    <row r="14" ht="28.5">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="10">
+        <f>SUM(Plannification!C2:S2)-H11</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75">
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
     </row>
@@ -5418,19 +5443,19 @@
       <c r="D15" s="7"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16">
+    <row r="16" ht="28.5">
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="28.5">
+    <row r="17">
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18">
+    <row r="18" ht="28.5">
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
@@ -5490,49 +5515,49 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" ht="28.5">
+    <row r="28">
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="28.5">
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="42.75">
+    <row r="30">
       <c r="B30" s="5"/>
       <c r="C30" s="6"/>
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" ht="28.5">
+    <row r="31" ht="42.75">
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="57">
+    <row r="32" ht="28.5">
       <c r="B32" s="5"/>
       <c r="C32" s="6"/>
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="57">
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" ht="28.5">
+    <row r="34">
       <c r="B34" s="5"/>
       <c r="C34" s="6"/>
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="28.5">
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
@@ -5544,34 +5569,34 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37" ht="28.5">
+    <row r="37">
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
     </row>
-    <row r="38" ht="57">
+    <row r="38" ht="28.5">
       <c r="B38" s="5"/>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
     </row>
-    <row r="39" ht="28.5">
+    <row r="39" ht="57">
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="22"/>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" ht="28.5">
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-    </row>
-    <row r="41" ht="42.75">
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41">
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
       <c r="D41" s="7"/>
@@ -5583,19 +5608,19 @@
       <c r="D42" s="7"/>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" ht="28.5">
+    <row r="43" ht="42.75">
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
       <c r="D43" s="7"/>
       <c r="E43" s="8"/>
     </row>
-    <row r="44" ht="57">
+    <row r="44" ht="28.5">
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="57">
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
       <c r="D45" s="7"/>
@@ -5607,209 +5632,215 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" ht="42.75">
+    <row r="47">
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" ht="28.5">
-      <c r="B48" s="23"/>
-      <c r="C48" s="24"/>
+    <row r="48" ht="42.75">
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
       <c r="D48" s="7"/>
       <c r="E48" s="8"/>
     </row>
-    <row r="49" ht="42.75">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
+    <row r="49" ht="28.5">
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
-    <row r="50" ht="57">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
+    <row r="50" ht="42.75">
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
-    <row r="51" ht="28.5">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
+    <row r="51" ht="57">
+      <c r="B51" s="22"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
-    <row r="53">
-      <c r="B53" s="23"/>
-      <c r="C53" s="25"/>
+    <row r="53" ht="28.5">
+      <c r="B53" s="22"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="24"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="23"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="23"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="23"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="23"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="23"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="24"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="23"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="23"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="23"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="23"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="23"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="23"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="23"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="23"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="23"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="23"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="23"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="23"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="23"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="23"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="7"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="7"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5827,15 +5858,15 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00AB00E0-0001-4D04-93E1-00A4001C0040}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FD00AB-00EB-4E76-AA38-0029006D00B5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>$G$3:$G$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{00010053-00A6-4867-A5CA-006600ED0084}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>D8:D55</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00210008-00AD-44E6-9F69-001400A400C0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>$G$3:$G$9</xm:f>
           </x14:formula1>
           <xm:sqref>D3:D7</xm:sqref>
         </x14:dataValidation>
@@ -5870,1668 +5901,1671 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
-        <f t="array" ref="A2:A5">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="25" t="str" cm="1">
+        <f t="array" ref="A2:A6">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="25" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27">
+      <c r="A6" s="25">
+        <f/>
+        <v>46146</v>
+      </c>
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
-        <v>0</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26"/>
-      <c r="C28" s="29">
+      <c r="A28" s="25"/>
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26"/>
-      <c r="C29" s="29">
+      <c r="A29" s="25"/>
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26"/>
-      <c r="C30" s="29">
+      <c r="A30" s="25"/>
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26"/>
-      <c r="C31" s="29">
+      <c r="A31" s="25"/>
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26"/>
-      <c r="C32" s="29">
+      <c r="A32" s="25"/>
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26"/>
-      <c r="C33" s="29">
+      <c r="A33" s="25"/>
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26"/>
-      <c r="C34" s="29">
+      <c r="A34" s="25"/>
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26"/>
-      <c r="C35" s="29">
+      <c r="A35" s="25"/>
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26"/>
-      <c r="C36" s="29">
+      <c r="A36" s="25"/>
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26"/>
-      <c r="C37" s="29">
+      <c r="A37" s="25"/>
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26"/>
-      <c r="C38" s="29">
+      <c r="A38" s="25"/>
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7556,1270 +7590,1270 @@
     <col customWidth="1" min="3" max="19" width="5.57421875"/>
     <col customWidth="1" min="20" max="21" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="22" max="22" width="13.88671875"/>
-    <col bestFit="1" customWidth="1" min="23" max="23" width="30.61328125"/>
+    <col customWidth="1" min="23" max="23" width="32.421875"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="35" t="s">
+    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="G1" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="H1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="I1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="J1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="K1" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="L1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="M1" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="N1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="O1" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="P1" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="Q1" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-    </row>
-    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="R1" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35">
+      <c r="S1" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+    </row>
+    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34">
         <v>7</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="34">
         <v>4</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="34">
         <v>4</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="34">
         <v>7</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="34">
         <v>5</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="34">
         <v>7</v>
       </c>
-      <c r="I2" s="36">
-        <v>0</v>
-      </c>
-      <c r="J2" s="36">
-        <v>0</v>
-      </c>
-      <c r="K2" s="35">
+      <c r="I2" s="35">
+        <v>0</v>
+      </c>
+      <c r="J2" s="35">
+        <v>0</v>
+      </c>
+      <c r="K2" s="34">
         <v>5</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="34">
         <v>4</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="34">
         <v>7</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="34">
         <v>4</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="34">
         <v>5</v>
       </c>
-      <c r="P2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
+      <c r="P2" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="34">
         <v>4</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="34">
         <v>7</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="34">
         <v>5</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-    </row>
-    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="40" t="str">
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+    </row>
+    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="39" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42" t="str">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42" t="str">
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="41" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="51"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="50"/>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="59"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="58"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="65"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="64"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="65"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="64"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="51"/>
+      <c r="B8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="58"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="59"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="58"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="73"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="72"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="81"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="80"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="83" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
+      <c r="A12" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="50"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="59"/>
+      <c r="A13" s="83"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="58"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="65"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="64"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="65"/>
+      <c r="A15" s="83"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="64"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="58"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="59"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="58"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="65"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="64"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="81"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="S19" s="80"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="83" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="51"/>
+      <c r="A20" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="50"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="59"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="58"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="65"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="64"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="65"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="64"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="59"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="58"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="58"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="65"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="64"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="65"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="64"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="59"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="58"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="92"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="88"/>
+      <c r="Q29" s="88"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="91"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="94" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="98"/>
+      <c r="A30" s="92" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="97"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="65"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="64"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="59"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="58"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="59"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="54"/>
+      <c r="R33" s="54"/>
+      <c r="S33" s="58"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="65"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="64"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="65"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="64"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="99"/>
-      <c r="B36" s="68" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="59"/>
+      <c r="A36" s="98"/>
+      <c r="B36" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="60"/>
+      <c r="Q36" s="54"/>
+      <c r="R36" s="54"/>
+      <c r="S36" s="58"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="99"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="59"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="54"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="54"/>
+      <c r="S37" s="58"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="99"/>
-      <c r="B38" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="65"/>
+      <c r="A38" s="98"/>
+      <c r="B38" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="64"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="99"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="65"/>
+      <c r="A39" s="98"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="64"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="99"/>
-      <c r="B40" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="59"/>
+      <c r="A40" s="98"/>
+      <c r="B40" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="54"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="58"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="99"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="59"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="56"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="58"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="99"/>
-      <c r="B42" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="63"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="73"/>
+      <c r="A42" s="98"/>
+      <c r="B42" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="72"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="100"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="81"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="77"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="75"/>
+      <c r="S43" s="80"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="101"/>
+      <c r="A44" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="48"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="100"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="59"/>
-      <c r="V45" s="102" t="s">
-        <v>70</v>
-      </c>
-      <c r="W45" s="61"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="54"/>
+      <c r="S45" s="58"/>
+      <c r="V45" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="W45" s="60"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="103" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="73"/>
-      <c r="V46" s="102" t="s">
-        <v>72</v>
-      </c>
-      <c r="W46" s="54"/>
+      <c r="A46" s="51"/>
+      <c r="B46" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="72"/>
+      <c r="V46" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="W46" s="53"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="74"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="81"/>
-      <c r="V47" s="102" t="s">
-        <v>73</v>
-      </c>
-      <c r="W47" s="67"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="78"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="75"/>
+      <c r="P47" s="75"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="75"/>
+      <c r="S47" s="80"/>
+      <c r="V47" s="101" t="s">
+        <v>75</v>
+      </c>
+      <c r="W47" s="66"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="105">
+      <c r="V54" s="104">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8827,7 +8861,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8835,7 +8869,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -8899,801 +8933,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="106"/>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="108" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="109" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="110" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="111" t="s">
+      <c r="B2" s="106" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="111" t="s">
+      <c r="E2" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="111" t="s">
+      <c r="F2" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="111" t="s">
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="AD2" s="30"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="110" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="111"/>
+      <c r="AD2" s="29"/>
     </row>
     <row r="3">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="116">
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="115">
         <v>4</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="116">
         <v>1</v>
       </c>
-      <c r="G3" s="118">
+      <c r="G3" s="117">
         <v>2</v>
       </c>
-      <c r="H3" s="118">
+      <c r="H3" s="117">
         <v>3</v>
       </c>
-      <c r="I3" s="116">
+      <c r="I3" s="115">
         <v>4</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="116">
         <v>1</v>
       </c>
-      <c r="K3" s="118">
+      <c r="K3" s="117">
         <v>2</v>
       </c>
-      <c r="L3" s="118">
+      <c r="L3" s="117">
         <v>3</v>
       </c>
-      <c r="M3" s="116">
+      <c r="M3" s="115">
         <v>4</v>
       </c>
-      <c r="N3" s="117">
+      <c r="N3" s="116">
         <v>1</v>
       </c>
-      <c r="O3" s="118">
+      <c r="O3" s="117">
         <v>2</v>
       </c>
-      <c r="P3" s="118">
+      <c r="P3" s="117">
         <v>3</v>
       </c>
-      <c r="Q3" s="116">
+      <c r="Q3" s="115">
         <v>4</v>
       </c>
-      <c r="R3" s="117">
+      <c r="R3" s="116">
         <v>1</v>
       </c>
-      <c r="S3" s="119">
+      <c r="S3" s="118">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="120" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
+      <c r="B4" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="120"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="125"/>
       <c r="U4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="131"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="131"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="133"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="135" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="142"/>
-      <c r="U6" s="143" t="s">
-        <v>88</v>
-      </c>
-      <c r="V6" s="143"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="134" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="135"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="139"/>
+      <c r="P6" s="139"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="141"/>
+      <c r="U6" s="142" t="s">
+        <v>90</v>
+      </c>
+      <c r="V6" s="142"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="134"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="132"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="132"/>
+      <c r="S7" s="133"/>
       <c r="U7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="135" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="142"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="134" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="135"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="141"/>
       <c r="U8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="134"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="132"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="133"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="135" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="135"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="136"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="141"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="151"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
+      <c r="H11" s="148"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="149"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="150"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="107" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="108" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
+      <c r="B12" s="106" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="152"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="124"/>
+      <c r="S12" s="125"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="134"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="131"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="133"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="134" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="153"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="140"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="141"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="134"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="131"/>
+      <c r="Q15" s="128"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="133"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="135" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="134" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="155"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="139"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="141"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="151"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="149"/>
+      <c r="P17" s="149"/>
+      <c r="Q17" s="146"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="150"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="109" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="108" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
+      <c r="B18" s="108" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="125"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="129"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="132"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="132"/>
+      <c r="O19" s="131"/>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="133"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="135" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="134" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="155"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="140"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="140"/>
+      <c r="S20" s="141"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="134"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="128"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="133"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="135" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="141"/>
-      <c r="S22" s="142"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="134" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="135"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="140"/>
+      <c r="O22" s="139"/>
+      <c r="P22" s="139"/>
+      <c r="Q22" s="136"/>
+      <c r="R22" s="140"/>
+      <c r="S22" s="141"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="151"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="149"/>
+      <c r="L23" s="149"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="149"/>
+      <c r="P23" s="149"/>
+      <c r="Q23" s="146"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="150"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="109" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="108" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="126"/>
+      <c r="B24" s="108" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="107" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="123"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="152"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="151"/>
+      <c r="P24" s="151"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="125"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="133"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="134"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="132"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="131"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="132"/>
+      <c r="S25" s="133"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="141"/>
-      <c r="S26" s="142"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="135"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="140"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="138"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="140"/>
+      <c r="S26" s="141"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="134"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="132"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="131"/>
+      <c r="Q27" s="128"/>
+      <c r="R27" s="132"/>
+      <c r="S27" s="133"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="156"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="135"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="140"/>
+      <c r="O28" s="139"/>
+      <c r="P28" s="138"/>
+      <c r="Q28" s="155"/>
+      <c r="R28" s="140"/>
+      <c r="S28" s="141"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="162"/>
-      <c r="Q29" s="160"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="165"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="159"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="159"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="162"/>
+      <c r="M29" s="159"/>
+      <c r="N29" s="163"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="159"/>
+      <c r="R29" s="160"/>
+      <c r="S29" s="164"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="166" t="s">
+      <c r="B30" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="167" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="172"/>
+      <c r="C30" s="166" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="168"/>
+      <c r="K30" s="168"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="168"/>
+      <c r="O30" s="169"/>
+      <c r="P30" s="168"/>
+      <c r="Q30" s="170"/>
+      <c r="R30" s="168"/>
+      <c r="S30" s="171"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="177"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="134"/>
+      <c r="B31" s="172"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="175"/>
+      <c r="Q31" s="177"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="133"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174" t="s">
+      <c r="B32" s="172"/>
+      <c r="C32" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="183"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="183"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="184"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="180"/>
+      <c r="K32" s="180"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="180"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="180"/>
+      <c r="Q32" s="182"/>
+      <c r="R32" s="180"/>
+      <c r="S32" s="183"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="177"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="178"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="134"/>
+      <c r="B33" s="172"/>
+      <c r="C33" s="173"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="175"/>
+      <c r="K33" s="178"/>
+      <c r="L33" s="176"/>
+      <c r="M33" s="177"/>
+      <c r="N33" s="175"/>
+      <c r="O33" s="176"/>
+      <c r="P33" s="175"/>
+      <c r="Q33" s="177"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="133"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="173"/>
-      <c r="C34" s="127" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="191"/>
-      <c r="U34" s="192"/>
-      <c r="V34" s="193" t="s">
-        <v>107</v>
+      <c r="B34" s="172"/>
+      <c r="C34" s="126" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="158"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="187"/>
+      <c r="K34" s="187"/>
+      <c r="L34" s="188"/>
+      <c r="M34" s="189"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="188"/>
+      <c r="P34" s="187"/>
+      <c r="Q34" s="189"/>
+      <c r="R34" s="187"/>
+      <c r="S34" s="190"/>
+      <c r="U34" s="191"/>
+      <c r="V34" s="192" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="194"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="199"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="151"/>
-      <c r="U35" s="200"/>
-      <c r="V35" s="201" t="s">
-        <v>108</v>
+      <c r="B35" s="193"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="197"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="196"/>
+      <c r="K35" s="196"/>
+      <c r="L35" s="197"/>
+      <c r="M35" s="198"/>
+      <c r="N35" s="196"/>
+      <c r="O35" s="197"/>
+      <c r="P35" s="196"/>
+      <c r="Q35" s="198"/>
+      <c r="R35" s="196"/>
+      <c r="S35" s="150"/>
+      <c r="U35" s="199"/>
+      <c r="V35" s="200" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>date</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ajout des différentes librairies sur KiCad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création d'une librairie de composants pour le projet</t>
   </si>
   <si>
     <t xml:space="preserve">Temps restant </t>
@@ -1643,7 +1646,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="202">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1688,6 +1691,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -2608,7 +2614,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -4614,8 +4620,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E12">
-  <autoFilter ref="B2:E12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E13">
+  <autoFilter ref="B2:E13"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5212,7 +5218,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.6153846153846159e-002</v>
+        <v>8.771929824561403e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5239,7 +5245,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.23076923076923073</v>
+        <v>0.21052631578947364</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5266,7 +5272,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.59615384615384615</v>
+        <v>0.54385964912280704</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5343,7 +5349,7 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5394,7 +5400,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5421,16 +5427,24 @@
       <c r="K12" s="4"/>
     </row>
     <row r="13">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
+      <c r="B13" s="5">
+        <v>46146</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>49</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5592,9 +5606,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="22"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5645,200 +5659,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="22"/>
-      <c r="C53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="22"/>
-      <c r="C54" s="24"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="22"/>
-      <c r="C55" s="24"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="25"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="22"/>
-      <c r="C56" s="24"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="22"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="22"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="22"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="22"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="22"/>
-      <c r="C61" s="24"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="22"/>
-      <c r="C62" s="24"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="22"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="22"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="22"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="22"/>
-      <c r="C66" s="24"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="22"/>
-      <c r="C67" s="24"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="22"/>
-      <c r="C68" s="24"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="22"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="22"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="22"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="22"/>
-      <c r="C72" s="24"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="22"/>
-      <c r="C73" s="24"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="22"/>
-      <c r="C74" s="24"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="22"/>
-      <c r="C75" s="24"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="24"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="24"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="24"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="24"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="24"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="24"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5858,13 +5872,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00FD00AB-00EB-4E76-AA38-0029006D00B5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008300DB-00D5-4EA7-8517-0061009E0028}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00010053-00A6-4867-A5CA-006600ED0084}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00E2001C-0058-4F3A-AFD1-008E00CF0010}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5901,1671 +5915,1671 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="str" cm="1">
+      <c r="A2" s="26" t="str" cm="1">
         <f t="array" ref="A2:A6">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="25">
+      <c r="A6" s="26">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.1875</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="27"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25"/>
-      <c r="C28" s="28">
+      <c r="A28" s="26"/>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25"/>
-      <c r="C29" s="28">
+      <c r="A29" s="26"/>
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25"/>
-      <c r="C30" s="28">
+      <c r="A30" s="26"/>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25"/>
-      <c r="C31" s="28">
+      <c r="A31" s="26"/>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25"/>
-      <c r="C32" s="28">
+      <c r="A32" s="26"/>
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="C33" s="28">
+      <c r="A33" s="26"/>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25"/>
-      <c r="C34" s="28">
+      <c r="A34" s="26"/>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25"/>
-      <c r="C35" s="28">
+      <c r="A35" s="26"/>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25"/>
-      <c r="C36" s="28">
+      <c r="A36" s="26"/>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25"/>
-      <c r="C37" s="28">
+      <c r="A37" s="26"/>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25"/>
-      <c r="C38" s="28">
+      <c r="A38" s="26"/>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25"/>
-      <c r="C39" s="28">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29"/>
-      <c r="B42" s="26" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29"/>
-      <c r="B43" s="26" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="26" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29"/>
-      <c r="B45" s="26" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29"/>
-      <c r="B46" s="26" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30"/>
-      <c r="B47" s="26" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30"/>
-      <c r="B48" s="26" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30"/>
-      <c r="B49" s="26" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30"/>
-      <c r="B50" s="26" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30"/>
-      <c r="B51" s="26" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30"/>
-      <c r="B52" s="26" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30"/>
-      <c r="B53" s="26" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30"/>
-      <c r="B54" s="26" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30"/>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30"/>
-      <c r="B56" s="26" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30"/>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30"/>
-      <c r="B58" s="26" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30"/>
-      <c r="B59" s="26" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30"/>
-      <c r="B60" s="26" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30"/>
-      <c r="B61" s="26" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30"/>
-      <c r="B62" s="26" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30"/>
-      <c r="B63" s="26" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30"/>
-      <c r="B64" s="26" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30"/>
-      <c r="B65" s="26" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30"/>
-      <c r="B66" s="26" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30"/>
-      <c r="B67" s="26" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30"/>
-      <c r="B68" s="26" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30"/>
-      <c r="B69" s="26" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30"/>
-      <c r="B70" s="26" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30"/>
-      <c r="B71" s="26" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30"/>
-      <c r="B72" s="26" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30"/>
-      <c r="B73" s="26" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30"/>
-      <c r="B74" s="26" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30"/>
-      <c r="B75" s="26" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30"/>
-      <c r="B76" s="26" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30"/>
-      <c r="B77" s="26" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30"/>
-      <c r="B78" s="26" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30"/>
-      <c r="B79" s="26" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30"/>
-      <c r="B80" s="26" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30"/>
-      <c r="B81" s="26" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30"/>
-      <c r="B82" s="26" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30"/>
-      <c r="B83" s="26" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30"/>
-      <c r="B84" s="26" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30"/>
-      <c r="B85" s="26" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30"/>
-      <c r="B86" s="26" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30"/>
-      <c r="B87" s="26" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30"/>
-      <c r="B88" s="26" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30"/>
-      <c r="B89" s="26" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30"/>
-      <c r="B90" s="26" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30"/>
-      <c r="B91" s="26" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30"/>
-      <c r="B92" s="26" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30"/>
-      <c r="B93" s="26" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30"/>
-      <c r="B94" s="26" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30"/>
-      <c r="B95" s="26" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30"/>
-      <c r="B96" s="26" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30"/>
-      <c r="B97" s="26" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30"/>
-      <c r="B98" s="26" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30"/>
-      <c r="B99" s="26" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30"/>
-      <c r="B100" s="26" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30"/>
-      <c r="B101" s="26" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30"/>
-      <c r="B102" s="26" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30"/>
-      <c r="B103" s="26" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30"/>
-      <c r="B104" s="26" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30"/>
-      <c r="B105" s="26" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30"/>
-      <c r="B106" s="26" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30"/>
-      <c r="B107" s="26" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="30"/>
-      <c r="B108" s="26" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30"/>
-      <c r="B109" s="26" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30"/>
-      <c r="B110" s="26" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30"/>
-      <c r="B111" s="26" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="30"/>
-      <c r="B112" s="26" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30"/>
-      <c r="B113" s="26" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30"/>
-      <c r="B114" s="26" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7594,1266 +7608,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="33" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="B1" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="34" t="s">
+      <c r="F1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="J1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="L1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="M1" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="N1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="O1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="R1" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="31"/>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="31"/>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="31"/>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-    </row>
-    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="S1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="34">
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+      <c r="AO1" s="32"/>
+      <c r="AP1" s="32"/>
+      <c r="AQ1" s="32"/>
+      <c r="AR1" s="32"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="32"/>
+      <c r="AU1" s="32"/>
+      <c r="AV1" s="32"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="32"/>
+      <c r="AY1" s="32"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="32"/>
+      <c r="BB1" s="32"/>
+      <c r="BC1" s="32"/>
+    </row>
+    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35">
         <v>7</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="35">
         <v>4</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="35">
         <v>4</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="35">
         <v>7</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="35">
         <v>5</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="35">
         <v>7</v>
       </c>
-      <c r="I2" s="35">
-        <v>0</v>
-      </c>
-      <c r="J2" s="35">
-        <v>0</v>
-      </c>
-      <c r="K2" s="34">
+      <c r="I2" s="36">
+        <v>0</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0</v>
+      </c>
+      <c r="K2" s="35">
         <v>5</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="35">
         <v>4</v>
       </c>
-      <c r="M2" s="34">
+      <c r="M2" s="35">
         <v>7</v>
       </c>
-      <c r="N2" s="34">
+      <c r="N2" s="35">
         <v>4</v>
       </c>
-      <c r="O2" s="34">
+      <c r="O2" s="35">
         <v>5</v>
       </c>
-      <c r="P2" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="34">
+      <c r="P2" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="35">
         <v>4</v>
       </c>
-      <c r="R2" s="34">
+      <c r="R2" s="35">
         <v>7</v>
       </c>
-      <c r="S2" s="34">
+      <c r="S2" s="35">
         <v>5</v>
       </c>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="31"/>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="31"/>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="31"/>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-    </row>
-    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="38" t="s">
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
+      <c r="AS2" s="32"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="32"/>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="32"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+    </row>
+    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="39" t="str">
+      <c r="B3" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41" t="str">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41" t="str">
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="42" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-      <c r="AK3" s="31"/>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="31"/>
-      <c r="AN3" s="31"/>
-      <c r="AO3" s="31"/>
-      <c r="AP3" s="31"/>
-      <c r="AQ3" s="31"/>
-      <c r="AR3" s="31"/>
-      <c r="AS3" s="31"/>
-      <c r="AT3" s="31"/>
-      <c r="AU3" s="31"/>
-      <c r="AV3" s="31"/>
-      <c r="AW3" s="31"/>
-      <c r="AX3" s="31"/>
-      <c r="AY3" s="31"/>
-      <c r="AZ3" s="31"/>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="31"/>
-      <c r="BC3" s="31"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AQ3" s="32"/>
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AV3" s="32"/>
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BA3" s="32"/>
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="50"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="58"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="59"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="51"/>
-      <c r="B6" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="64"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="51"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="64"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="67" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="58"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="59"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="58"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="59"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="72"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="73"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="80"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="81"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="82" t="s">
+      <c r="A12" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="50"/>
+      <c r="B12" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="51"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="83"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="58"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="59"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="64"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="65"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="64"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="83"/>
-      <c r="B16" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="58"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="59"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="58"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="59"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="83"/>
-      <c r="B18" s="69" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="61"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="64"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="65"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="84"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="80"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76"/>
+      <c r="S19" s="81"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="82" t="s">
+      <c r="A20" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="50"/>
+      <c r="B20" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="51"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="51"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="58"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="59"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="51"/>
-      <c r="B22" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="64"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="65"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="51"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="64"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="65"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="51"/>
-      <c r="B24" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="S24" s="58"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="55"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="59"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="51"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="54"/>
-      <c r="S25" s="58"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="59"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="51"/>
-      <c r="B26" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="64"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="65"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="51"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="61"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="64"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="65"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="51"/>
-      <c r="B28" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="58"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="59"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="73"/>
-      <c r="B29" s="87"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="88"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="91"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="92"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="92" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="93" t="s">
+      <c r="A30" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
-      <c r="S30" s="97"/>
+      <c r="B30" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="98"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="64"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="65"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="98"/>
-      <c r="B32" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="54"/>
-      <c r="R32" s="54"/>
-      <c r="S32" s="58"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="59"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="98"/>
-      <c r="B33" s="65"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="58"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="59"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="98"/>
-      <c r="B34" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="64"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="65"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="65"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="62"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="64"/>
+      <c r="A35" s="99"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="65"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="98"/>
-      <c r="B36" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
-      <c r="Q36" s="54"/>
-      <c r="R36" s="54"/>
-      <c r="S36" s="58"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="59"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="98"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="58"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="59"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="98"/>
-      <c r="B38" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="61"/>
-      <c r="S38" s="64"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="65"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="98"/>
-      <c r="B39" s="65"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="61"/>
-      <c r="S39" s="64"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="65"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="98"/>
-      <c r="B40" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="54"/>
-      <c r="P40" s="54"/>
-      <c r="Q40" s="60"/>
-      <c r="R40" s="60"/>
-      <c r="S40" s="58"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="59"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="98"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="58"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="59"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="98"/>
-      <c r="B42" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="62"/>
-      <c r="N42" s="63"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="72"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="62"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="73"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="99"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="77"/>
-      <c r="N43" s="78"/>
-      <c r="O43" s="75"/>
-      <c r="P43" s="75"/>
-      <c r="Q43" s="75"/>
-      <c r="R43" s="75"/>
-      <c r="S43" s="80"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="81"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="44" t="s">
+      <c r="A44" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
-      <c r="S44" s="100"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="101"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="51"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="54"/>
-      <c r="L45" s="54"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="54"/>
-      <c r="R45" s="54"/>
-      <c r="S45" s="58"/>
-      <c r="V45" s="101" t="s">
-        <v>72</v>
-      </c>
-      <c r="W45" s="60"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="56"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="59"/>
+      <c r="V45" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="51"/>
-      <c r="B46" s="102" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="62"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="62"/>
-      <c r="N46" s="63"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="61"/>
-      <c r="R46" s="61"/>
-      <c r="S46" s="72"/>
-      <c r="V46" s="101" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="W46" s="53"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="62"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="73"/>
+      <c r="V46" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="W46" s="54"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="73"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="79"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="75"/>
-      <c r="M47" s="77"/>
-      <c r="N47" s="78"/>
-      <c r="O47" s="75"/>
-      <c r="P47" s="75"/>
-      <c r="Q47" s="75"/>
-      <c r="R47" s="75"/>
-      <c r="S47" s="80"/>
-      <c r="V47" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="W47" s="66"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="81"/>
+      <c r="V47" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="W47" s="67"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="104">
+      <c r="V54" s="105">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8861,7 +8875,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8869,7 +8883,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -8933,801 +8947,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="105"/>
+      <c r="B1" s="106"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="106" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="107" t="s">
+      <c r="B2" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="108" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="109" t="s">
+      <c r="C2" s="108" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="E2" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="110" t="s">
+      <c r="F2" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="110" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="110" t="s">
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="S2" s="111"/>
-      <c r="AD2" s="29"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="112"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="115">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="116">
         <v>4</v>
       </c>
-      <c r="F3" s="116">
+      <c r="F3" s="117">
         <v>1</v>
       </c>
-      <c r="G3" s="117">
+      <c r="G3" s="118">
         <v>2</v>
       </c>
-      <c r="H3" s="117">
+      <c r="H3" s="118">
         <v>3</v>
       </c>
-      <c r="I3" s="115">
+      <c r="I3" s="116">
         <v>4</v>
       </c>
-      <c r="J3" s="116">
+      <c r="J3" s="117">
         <v>1</v>
       </c>
-      <c r="K3" s="117">
+      <c r="K3" s="118">
         <v>2</v>
       </c>
-      <c r="L3" s="117">
+      <c r="L3" s="118">
         <v>3</v>
       </c>
-      <c r="M3" s="115">
+      <c r="M3" s="116">
         <v>4</v>
       </c>
-      <c r="N3" s="116">
+      <c r="N3" s="117">
         <v>1</v>
       </c>
-      <c r="O3" s="117">
+      <c r="O3" s="118">
         <v>2</v>
       </c>
-      <c r="P3" s="117">
+      <c r="P3" s="118">
         <v>3</v>
       </c>
-      <c r="Q3" s="115">
+      <c r="Q3" s="116">
         <v>4</v>
       </c>
-      <c r="R3" s="116">
+      <c r="R3" s="117">
         <v>1</v>
       </c>
-      <c r="S3" s="118">
+      <c r="S3" s="119">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="119" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="107" t="s">
+      <c r="B4" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="125"/>
+      <c r="C4" s="108" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="119"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="131"/>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="133"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="119"/>
-      <c r="C6" s="134" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="135"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="139"/>
-      <c r="L6" s="139"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="140"/>
-      <c r="O6" s="139"/>
-      <c r="P6" s="139"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="140"/>
-      <c r="S6" s="141"/>
-      <c r="U6" s="142" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="V6" s="142"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="141"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="142"/>
+      <c r="U6" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="V6" s="143"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="119"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="128"/>
-      <c r="R7" s="132"/>
-      <c r="S7" s="133"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="119"/>
-      <c r="C8" s="134" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="135"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="141"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="135" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="136"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="141"/>
+      <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="119"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="132"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="133"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="134"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="119"/>
-      <c r="C10" s="134" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="135"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="136"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="141"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="136"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="142"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="143"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="148"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="149"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="146"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="150"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="148"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="151"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="106" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="107" t="s">
+      <c r="B12" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="120"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="124"/>
-      <c r="S12" s="125"/>
+      <c r="C12" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="125"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="119"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="133"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="134"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="119"/>
-      <c r="C14" s="134" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="153"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="140"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="139"/>
-      <c r="Q14" s="136"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="141"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="142"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="119"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="128"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="133"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="155"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="134"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="119"/>
-      <c r="C16" s="134" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="155"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="139"/>
-      <c r="L16" s="139"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="140"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="136"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="141"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="136"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="143"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="146"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="146"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="148"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="147"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="146"/>
-      <c r="R17" s="147"/>
-      <c r="S17" s="150"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="151"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="108" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="107" t="s">
+      <c r="B18" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="120"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="125"/>
+      <c r="C18" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="121"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="125"/>
+      <c r="S18" s="126"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="119"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="132"/>
-      <c r="O19" s="131"/>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="133"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="119"/>
-      <c r="C20" s="134" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="135"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="155"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="136"/>
-      <c r="R20" s="140"/>
-      <c r="S20" s="141"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="142"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="119"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="128"/>
-      <c r="N21" s="157"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="128"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="133"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="134"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="119"/>
-      <c r="C22" s="134" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="139"/>
-      <c r="P22" s="139"/>
-      <c r="Q22" s="136"/>
-      <c r="R22" s="140"/>
-      <c r="S22" s="141"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="135" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="141"/>
+      <c r="S22" s="142"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="143"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="147"/>
-      <c r="K23" s="149"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="147"/>
-      <c r="O23" s="149"/>
-      <c r="P23" s="149"/>
-      <c r="Q23" s="146"/>
-      <c r="R23" s="147"/>
-      <c r="S23" s="150"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="150"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="150"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="150"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="151"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="108" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="107" t="s">
+      <c r="B24" s="109" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="120"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="123"/>
-      <c r="L24" s="123"/>
-      <c r="M24" s="152"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="151"/>
-      <c r="P24" s="151"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="125"/>
+      <c r="C24" s="108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="121"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="153"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="152"/>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="126"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="119"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="131"/>
-      <c r="L25" s="131"/>
-      <c r="M25" s="128"/>
-      <c r="N25" s="132"/>
-      <c r="O25" s="131"/>
-      <c r="P25" s="131"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="132"/>
-      <c r="S25" s="133"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="134"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="119"/>
-      <c r="C26" s="134" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="135"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="140"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="138"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="140"/>
-      <c r="S26" s="141"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="136"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="137"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="142"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="119"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="131"/>
-      <c r="L27" s="131"/>
-      <c r="M27" s="128"/>
-      <c r="N27" s="132"/>
-      <c r="O27" s="131"/>
-      <c r="P27" s="131"/>
-      <c r="Q27" s="128"/>
-      <c r="R27" s="132"/>
-      <c r="S27" s="133"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="133"/>
+      <c r="S27" s="134"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="119"/>
-      <c r="C28" s="134" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="140"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="139"/>
-      <c r="P28" s="138"/>
-      <c r="Q28" s="155"/>
-      <c r="R28" s="140"/>
-      <c r="S28" s="141"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="135" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="156"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="142"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="119"/>
-      <c r="C29" s="113"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="162"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="159"/>
-      <c r="N29" s="163"/>
-      <c r="O29" s="162"/>
-      <c r="P29" s="161"/>
-      <c r="Q29" s="159"/>
-      <c r="R29" s="160"/>
-      <c r="S29" s="164"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="163"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="163"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="163"/>
+      <c r="P29" s="162"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="165"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="165" t="s">
+      <c r="B30" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="166" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="120"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="168"/>
-      <c r="K30" s="168"/>
-      <c r="L30" s="169"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="168"/>
-      <c r="O30" s="169"/>
-      <c r="P30" s="168"/>
-      <c r="Q30" s="170"/>
-      <c r="R30" s="168"/>
-      <c r="S30" s="171"/>
+      <c r="C30" s="167" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="121"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="171"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="172"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="177"/>
-      <c r="N31" s="175"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="175"/>
-      <c r="Q31" s="177"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="133"/>
+      <c r="B31" s="173"/>
+      <c r="C31" s="174"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="177"/>
+      <c r="M31" s="178"/>
+      <c r="N31" s="176"/>
+      <c r="O31" s="177"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="178"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="134"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="172"/>
-      <c r="C32" s="173" t="s">
+      <c r="B32" s="173"/>
+      <c r="C32" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="135"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="180"/>
-      <c r="G32" s="180"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="182"/>
-      <c r="J32" s="180"/>
-      <c r="K32" s="180"/>
-      <c r="L32" s="181"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="181"/>
-      <c r="P32" s="180"/>
-      <c r="Q32" s="182"/>
-      <c r="R32" s="180"/>
-      <c r="S32" s="183"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="183"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="183"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="184"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="172"/>
-      <c r="C33" s="173"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="178"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="184"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="176"/>
-      <c r="M33" s="177"/>
-      <c r="N33" s="175"/>
-      <c r="O33" s="176"/>
-      <c r="P33" s="175"/>
-      <c r="Q33" s="177"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="133"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="174"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="176"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="177"/>
+      <c r="M33" s="178"/>
+      <c r="N33" s="176"/>
+      <c r="O33" s="177"/>
+      <c r="P33" s="176"/>
+      <c r="Q33" s="178"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="134"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="172"/>
-      <c r="C34" s="126" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="158"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="187"/>
-      <c r="G34" s="187"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="189"/>
-      <c r="J34" s="187"/>
-      <c r="K34" s="187"/>
-      <c r="L34" s="188"/>
-      <c r="M34" s="189"/>
-      <c r="N34" s="187"/>
-      <c r="O34" s="188"/>
-      <c r="P34" s="187"/>
-      <c r="Q34" s="189"/>
-      <c r="R34" s="187"/>
-      <c r="S34" s="190"/>
-      <c r="U34" s="191"/>
-      <c r="V34" s="192" t="s">
+      <c r="B34" s="173"/>
+      <c r="C34" s="127" t="s">
         <v>109</v>
       </c>
+      <c r="D34" s="159"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="188"/>
+      <c r="O34" s="189"/>
+      <c r="P34" s="188"/>
+      <c r="Q34" s="190"/>
+      <c r="R34" s="188"/>
+      <c r="S34" s="191"/>
+      <c r="U34" s="192"/>
+      <c r="V34" s="193" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="193"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="145"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="196"/>
-      <c r="K35" s="196"/>
-      <c r="L35" s="197"/>
-      <c r="M35" s="198"/>
-      <c r="N35" s="196"/>
-      <c r="O35" s="197"/>
-      <c r="P35" s="196"/>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="196"/>
-      <c r="S35" s="150"/>
-      <c r="U35" s="199"/>
-      <c r="V35" s="200" t="s">
-        <v>110</v>
+      <c r="B35" s="194"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="197"/>
+      <c r="Q35" s="199"/>
+      <c r="R35" s="197"/>
+      <c r="S35" s="151"/>
+      <c r="U35" s="200"/>
+      <c r="V35" s="201" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t xml:space="preserve">Temps restant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuit d'alimentation avec schéma + liste de matériel</t>
   </si>
   <si>
     <t>Phases</t>
@@ -403,9 +406,9 @@
     <numFmt numFmtId="165" formatCode="hh:mm;@"/>
     <numFmt numFmtId="166" formatCode="0.0&quot; H&quot;;@"/>
     <numFmt numFmtId="167" formatCode="0&quot;H&quot;"/>
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="169" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -1646,7 +1649,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="205">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1695,9 +1698,18 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1714,7 +1726,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="170" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2033,7 +2045,7 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="0"/>
     </dxf>
     <dxf>
@@ -2562,9 +2574,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Journal!$G$3:$G$9</c:f>
+              <c:f>Journal!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>Cours</c:v>
                 </c:pt>
@@ -2585,6 +2597,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Prototypage</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Présentation</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4620,8 +4635,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E13">
-  <autoFilter ref="B2:E13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E14">
+  <autoFilter ref="B2:E14"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5448,8 +5463,18 @@
       </c>
     </row>
     <row r="14" ht="42.75">
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
+      <c r="B14" s="20">
+        <v>46146</v>
+      </c>
+      <c r="C14" s="21">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" ht="28.5">
       <c r="B15" s="5"/>
@@ -5606,9 +5631,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5659,200 +5684,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="27"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="27"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="27"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="27"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="23"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="23"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="28"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="23"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="23"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="23"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="23"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="28"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="23"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="28"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="23"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="28"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="23"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="28"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="23"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="28"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="23"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="23"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="28"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="23"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="28"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="23"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="28"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="23"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="28"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="23"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="28"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="23"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="28"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="23"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="28"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="23"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="28"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="23"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="28"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="23"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="28"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="28"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="28"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="28"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="28"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="28"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="25"/>
+      <c r="C81" s="28"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5872,13 +5897,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{008300DB-00D5-4EA7-8517-0061009E0028}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00880089-0001-4496-A713-003100970018}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00E2001C-0058-4F3A-AFD1-008E00CF0010}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{009600EE-0003-4E7B-B8A5-00C400C100FA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5915,1671 +5940,1671 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
+      <c r="A2" s="29" t="str" cm="1">
         <f t="array" ref="A2:A6">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="30"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="29" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="29" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="29" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26">
+      <c r="A6" s="29">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27">
+      <c r="A9" s="29"/>
+      <c r="B9" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27">
+      <c r="A10" s="29"/>
+      <c r="B10" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="A18" s="29"/>
+      <c r="B18" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="A19" s="29"/>
+      <c r="B19" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="A24" s="29"/>
+      <c r="B24" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="31"/>
     </row>
     <row r="26">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
+      <c r="A27" s="29"/>
+      <c r="B27" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26"/>
-      <c r="C28" s="29">
+      <c r="A28" s="29"/>
+      <c r="C28" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26"/>
-      <c r="C29" s="29">
+      <c r="A29" s="29"/>
+      <c r="C29" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26"/>
-      <c r="C30" s="29">
+      <c r="A30" s="29"/>
+      <c r="C30" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26"/>
-      <c r="C31" s="29">
+      <c r="A31" s="29"/>
+      <c r="C31" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26"/>
-      <c r="C32" s="29">
+      <c r="A32" s="29"/>
+      <c r="C32" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26"/>
-      <c r="C33" s="29">
+      <c r="A33" s="29"/>
+      <c r="C33" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26"/>
-      <c r="C34" s="29">
+      <c r="A34" s="29"/>
+      <c r="C34" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26"/>
-      <c r="C35" s="29">
+      <c r="A35" s="29"/>
+      <c r="C35" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26"/>
-      <c r="C36" s="29">
+      <c r="A36" s="29"/>
+      <c r="C36" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26"/>
-      <c r="C37" s="29">
+      <c r="A37" s="29"/>
+      <c r="C37" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26"/>
-      <c r="C38" s="29">
+      <c r="A38" s="29"/>
+      <c r="C38" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="29"/>
+      <c r="C39" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="29"/>
+      <c r="B41" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="33"/>
+      <c r="B42" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="33"/>
+      <c r="B43" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="33"/>
+      <c r="B44" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="33"/>
+      <c r="B45" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="33"/>
+      <c r="B46" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="34"/>
+      <c r="B47" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="34"/>
+      <c r="B48" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="34"/>
+      <c r="B49" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="34"/>
+      <c r="B50" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="34"/>
+      <c r="B51" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="34"/>
+      <c r="B52" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="34"/>
+      <c r="B53" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="34"/>
+      <c r="B54" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="34"/>
+      <c r="B55" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="34"/>
+      <c r="B56" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="34"/>
+      <c r="B57" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="34"/>
+      <c r="B58" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="34"/>
+      <c r="B59" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="34"/>
+      <c r="B60" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="34"/>
+      <c r="B61" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="34"/>
+      <c r="B62" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="34"/>
+      <c r="B63" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="34"/>
+      <c r="B64" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="34"/>
+      <c r="B65" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="34"/>
+      <c r="B66" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="34"/>
+      <c r="B67" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="34"/>
+      <c r="B68" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="34"/>
+      <c r="B69" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="34"/>
+      <c r="B70" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="34"/>
+      <c r="B71" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="34"/>
+      <c r="B72" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="34"/>
+      <c r="B73" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="34"/>
+      <c r="B74" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="34"/>
+      <c r="B75" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="34"/>
+      <c r="B76" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="34"/>
+      <c r="B77" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="34"/>
+      <c r="B78" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="34"/>
+      <c r="B79" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="34"/>
+      <c r="B80" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="34"/>
+      <c r="B81" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="34"/>
+      <c r="B82" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="34"/>
+      <c r="B83" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="34"/>
+      <c r="B84" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="34"/>
+      <c r="B85" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="34"/>
+      <c r="B86" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="34"/>
+      <c r="B87" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="34"/>
+      <c r="B88" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="34"/>
+      <c r="B89" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="34"/>
+      <c r="B90" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="34"/>
+      <c r="B91" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="34"/>
+      <c r="B92" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="34"/>
+      <c r="B93" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="34"/>
+      <c r="B94" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="34"/>
+      <c r="B95" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="34"/>
+      <c r="B96" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="34"/>
+      <c r="B97" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="34"/>
+      <c r="B98" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="34"/>
+      <c r="B99" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="34"/>
+      <c r="B100" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="34"/>
+      <c r="B101" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="34"/>
+      <c r="B102" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="34"/>
+      <c r="B103" s="30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="34"/>
+      <c r="B104" s="30" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="34"/>
+      <c r="B105" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="34"/>
+      <c r="B106" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="34"/>
+      <c r="B107" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="34"/>
+      <c r="B108" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="34"/>
+      <c r="B109" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="34"/>
+      <c r="B110" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="34"/>
+      <c r="B111" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="34"/>
+      <c r="B112" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="34"/>
+      <c r="B113" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="34"/>
+      <c r="B114" s="30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="32"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="34"/>
+      <c r="B116" s="34"/>
+      <c r="C116" s="32"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="34"/>
+      <c r="B117" s="34"/>
+      <c r="C117" s="32"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="34"/>
+      <c r="B118" s="34"/>
+      <c r="C118" s="32"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="34"/>
+      <c r="B119" s="34"/>
+      <c r="C119" s="32"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="34"/>
+      <c r="B120" s="34"/>
+      <c r="C120" s="32"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="32"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="34"/>
+      <c r="B122" s="34"/>
+      <c r="C122" s="32"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="34"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="32"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="34"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="32"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="34"/>
+      <c r="B125" s="34"/>
+      <c r="C125" s="32"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="34"/>
+      <c r="B126" s="34"/>
+      <c r="C126" s="32"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="32"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="34"/>
+      <c r="B128" s="34"/>
+      <c r="C128" s="32"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="34"/>
+      <c r="B129" s="34"/>
+      <c r="C129" s="32"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="34"/>
+      <c r="B130" s="34"/>
+      <c r="C130" s="32"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="34"/>
+      <c r="B131" s="34"/>
+      <c r="C131" s="32"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="34"/>
+      <c r="B132" s="34"/>
+      <c r="C132" s="32"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="32"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="34"/>
+      <c r="B134" s="34"/>
+      <c r="C134" s="32"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="34"/>
+      <c r="B135" s="34"/>
+      <c r="C135" s="32"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="34"/>
+      <c r="B136" s="34"/>
+      <c r="C136" s="32"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="34"/>
+      <c r="B137" s="34"/>
+      <c r="C137" s="32"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="34"/>
+      <c r="B138" s="34"/>
+      <c r="C138" s="32"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="32"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="34"/>
+      <c r="B140" s="34"/>
+      <c r="C140" s="32"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="34"/>
+      <c r="B141" s="34"/>
+      <c r="C141" s="32"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="34"/>
+      <c r="B142" s="34"/>
+      <c r="C142" s="32"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="34"/>
+      <c r="B143" s="34"/>
+      <c r="C143" s="32"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="34"/>
+      <c r="B144" s="34"/>
+      <c r="C144" s="32"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="32"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="34"/>
+      <c r="B146" s="34"/>
+      <c r="C146" s="32"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="34"/>
+      <c r="B147" s="34"/>
+      <c r="C147" s="32"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="34"/>
+      <c r="B148" s="34"/>
+      <c r="C148" s="32"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="34"/>
+      <c r="B149" s="34"/>
+      <c r="C149" s="32"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="34"/>
+      <c r="B150" s="34"/>
+      <c r="C150" s="32"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="32"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="34"/>
+      <c r="B152" s="34"/>
+      <c r="C152" s="32"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="34"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="32"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="34"/>
+      <c r="B154" s="34"/>
+      <c r="C154" s="32"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="34"/>
+      <c r="B155" s="34"/>
+      <c r="C155" s="32"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="34"/>
+      <c r="B156" s="34"/>
+      <c r="C156" s="32"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="32"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="34"/>
+      <c r="B158" s="34"/>
+      <c r="C158" s="32"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="34"/>
+      <c r="B159" s="34"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="34"/>
+      <c r="B160" s="34"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="34"/>
+      <c r="B161" s="34"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="34"/>
+      <c r="B162" s="34"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="34"/>
+      <c r="B164" s="34"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="34"/>
+      <c r="B165" s="34"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="34"/>
+      <c r="B166" s="34"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="34"/>
+      <c r="B167" s="34"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="34"/>
+      <c r="B168" s="34"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="34"/>
+      <c r="B170" s="34"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="34"/>
+      <c r="B171" s="34"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="34"/>
+      <c r="B172" s="34"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="34"/>
+      <c r="B173" s="34"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="34"/>
+      <c r="B174" s="34"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="34"/>
+      <c r="B176" s="34"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="34"/>
+      <c r="B177" s="34"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="34"/>
+      <c r="B178" s="34"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="34"/>
+      <c r="B179" s="34"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="34"/>
+      <c r="B180" s="34"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="34"/>
+      <c r="B182" s="34"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="34"/>
+      <c r="B183" s="34"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="34"/>
+      <c r="B184" s="34"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="34"/>
+      <c r="B185" s="34"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="34"/>
+      <c r="B186" s="34"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="34"/>
+      <c r="B188" s="34"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="34"/>
+      <c r="B189" s="34"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="34"/>
+      <c r="B190" s="34"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="34"/>
+      <c r="B191" s="34"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="34"/>
+      <c r="B192" s="34"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="34"/>
+      <c r="B194" s="34"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="34"/>
+      <c r="B195" s="34"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="34"/>
+      <c r="B196" s="34"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="34"/>
+      <c r="B197" s="34"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="34"/>
+      <c r="B198" s="34"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="34"/>
+      <c r="B200" s="34"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="34"/>
+      <c r="B201" s="34"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="34"/>
+      <c r="B202" s="34"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="34"/>
+      <c r="B203" s="34"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="34"/>
+      <c r="B204" s="34"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="34"/>
+      <c r="B206" s="34"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="34"/>
+      <c r="B207" s="34"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="34"/>
+      <c r="B208" s="34"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="34"/>
+      <c r="B209" s="34"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="34"/>
+      <c r="B210" s="34"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="34"/>
+      <c r="B212" s="34"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="34"/>
+      <c r="B213" s="34"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="34"/>
+      <c r="B214" s="34"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="34"/>
+      <c r="B215" s="34"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="34"/>
+      <c r="B216" s="34"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="34"/>
+      <c r="B218" s="34"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="34"/>
+      <c r="B219" s="34"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="34"/>
+      <c r="B220" s="34"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="34"/>
+      <c r="B221" s="34"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="34"/>
+      <c r="B222" s="34"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="34"/>
+      <c r="B224" s="34"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="34"/>
+      <c r="B225" s="34"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="34"/>
+      <c r="B226" s="34"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="34"/>
+      <c r="B227" s="34"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="34"/>
+      <c r="B228" s="34"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="34"/>
+      <c r="B230" s="34"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="34"/>
+      <c r="B231" s="34"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="34"/>
+      <c r="B232" s="34"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="34"/>
+      <c r="B233" s="34"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="34"/>
+      <c r="B234" s="34"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7608,1266 +7633,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="34" t="s">
+    <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="H1" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="I1" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="J1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="K1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="M1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="N1" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="O1" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="Q1" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="R1" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-    </row>
-    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="S1" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35">
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+      <c r="AM1" s="35"/>
+      <c r="AN1" s="35"/>
+      <c r="AO1" s="35"/>
+      <c r="AP1" s="35"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="35"/>
+      <c r="AV1" s="35"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
+      <c r="AY1" s="35"/>
+      <c r="AZ1" s="35"/>
+      <c r="BA1" s="35"/>
+      <c r="BB1" s="35"/>
+      <c r="BC1" s="35"/>
+    </row>
+    <row r="2" s="35" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38">
         <v>7</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="38">
         <v>4</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="38">
         <v>4</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="38">
         <v>7</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="38">
         <v>5</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="38">
         <v>7</v>
       </c>
-      <c r="I2" s="36">
-        <v>0</v>
-      </c>
-      <c r="J2" s="36">
-        <v>0</v>
-      </c>
-      <c r="K2" s="35">
+      <c r="I2" s="39">
+        <v>0</v>
+      </c>
+      <c r="J2" s="39">
+        <v>0</v>
+      </c>
+      <c r="K2" s="38">
         <v>5</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="38">
         <v>4</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="38">
         <v>7</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="38">
         <v>4</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="38">
         <v>5</v>
       </c>
-      <c r="P2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
+      <c r="P2" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="38">
         <v>4</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="38">
         <v>7</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="38">
         <v>5</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-    </row>
-    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="39" t="s">
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+    </row>
+    <row r="3" s="35" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="40" t="str">
+      <c r="B3" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="43" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42" t="str">
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="45" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42" t="str">
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="45" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="35"/>
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35"/>
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="51"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="54"/>
       <c r="V4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="59"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="62"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="65"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="65"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="59"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="60"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="62"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="59"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="59"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="62"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="73"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="76"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="81"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="84"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="83" t="s">
+      <c r="A12" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
+      <c r="B12" s="86" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="54"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="59"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="62"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="65"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="65"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="65"/>
+      <c r="A15" s="87"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="68"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="62"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="59"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="62"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="65"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="68"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="81"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="84"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="83" t="s">
+      <c r="A20" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="51"/>
+      <c r="B20" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="54"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="59"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="62"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="65"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="68"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="65"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="68"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="59"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="62"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="62"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="65"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="68"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="65"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="68"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="59"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="62"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="92"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="93"/>
+      <c r="N29" s="94"/>
+      <c r="O29" s="92"/>
+      <c r="P29" s="92"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="92"/>
+      <c r="S29" s="95"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="94" t="s">
+      <c r="A30" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="98"/>
+      <c r="B30" s="97" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="49"/>
+      <c r="M30" s="89"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="101"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="65"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="65"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="68"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="59"/>
+      <c r="A32" s="102"/>
+      <c r="B32" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="62"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="59"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="58"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="58"/>
+      <c r="S33" s="62"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="65"/>
+      <c r="A34" s="102"/>
+      <c r="B34" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="65"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="68"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="65"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="66"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="68"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="99"/>
-      <c r="B36" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="59"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="62"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="99"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="59"/>
+      <c r="A37" s="102"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="62"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="99"/>
-      <c r="B38" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="65"/>
+      <c r="A38" s="102"/>
+      <c r="B38" s="73" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="64"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="68"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="99"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="65"/>
+      <c r="A39" s="102"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="66"/>
+      <c r="N39" s="67"/>
+      <c r="O39" s="65"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="68"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="99"/>
-      <c r="B40" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="59"/>
+      <c r="A40" s="102"/>
+      <c r="B40" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="59"/>
+      <c r="N40" s="60"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="64"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="62"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="99"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="59"/>
+      <c r="A41" s="102"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="62"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="99"/>
-      <c r="B42" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="63"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="73"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="66"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="64"/>
+      <c r="S42" s="76"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="100"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="81"/>
+      <c r="A43" s="103"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="82"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="81"/>
+      <c r="N43" s="82"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="79"/>
+      <c r="R43" s="79"/>
+      <c r="S43" s="84"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="101"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="52"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="104"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="59"/>
-      <c r="V45" s="102" t="s">
-        <v>73</v>
-      </c>
-      <c r="W45" s="61"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="59"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="62"/>
+      <c r="V45" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="W45" s="64"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="103" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="73"/>
-      <c r="V46" s="102" t="s">
+      <c r="A46" s="55"/>
+      <c r="B46" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="W46" s="54"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="67"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="65"/>
+      <c r="R46" s="65"/>
+      <c r="S46" s="76"/>
+      <c r="V46" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="W46" s="57"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="74"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="81"/>
-      <c r="V47" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="W47" s="67"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="107"/>
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="82"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="79"/>
+      <c r="L47" s="79"/>
+      <c r="M47" s="81"/>
+      <c r="N47" s="82"/>
+      <c r="O47" s="79"/>
+      <c r="P47" s="79"/>
+      <c r="Q47" s="79"/>
+      <c r="R47" s="79"/>
+      <c r="S47" s="84"/>
+      <c r="V47" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="W47" s="70"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="105">
+      <c r="V54" s="108">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8875,7 +8900,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8883,7 +8908,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -8947,801 +8972,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="106"/>
+      <c r="B1" s="109"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="107" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="108" t="s">
+      <c r="B2" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="109" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="110" t="s">
+      <c r="C2" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="112" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="E2" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="111" t="s">
+      <c r="F2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="111" t="s">
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="111" t="s">
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="114" t="s">
         <v>85</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="AD2" s="30"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="114" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="115"/>
+      <c r="AD2" s="33"/>
     </row>
     <row r="3">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="116">
+      <c r="B3" s="116"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="119">
         <v>4</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="120">
         <v>1</v>
       </c>
-      <c r="G3" s="118">
+      <c r="G3" s="121">
         <v>2</v>
       </c>
-      <c r="H3" s="118">
+      <c r="H3" s="121">
         <v>3</v>
       </c>
-      <c r="I3" s="116">
+      <c r="I3" s="119">
         <v>4</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="120">
         <v>1</v>
       </c>
-      <c r="K3" s="118">
+      <c r="K3" s="121">
         <v>2</v>
       </c>
-      <c r="L3" s="118">
+      <c r="L3" s="121">
         <v>3</v>
       </c>
-      <c r="M3" s="116">
+      <c r="M3" s="119">
         <v>4</v>
       </c>
-      <c r="N3" s="117">
+      <c r="N3" s="120">
         <v>1</v>
       </c>
-      <c r="O3" s="118">
+      <c r="O3" s="121">
         <v>2</v>
       </c>
-      <c r="P3" s="118">
+      <c r="P3" s="121">
         <v>3</v>
       </c>
-      <c r="Q3" s="116">
+      <c r="Q3" s="119">
         <v>4</v>
       </c>
-      <c r="R3" s="117">
+      <c r="R3" s="120">
         <v>1</v>
       </c>
-      <c r="S3" s="119">
+      <c r="S3" s="122">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="120" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="108" t="s">
+      <c r="B4" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
+      <c r="C4" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="124"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="127"/>
+      <c r="P4" s="127"/>
+      <c r="Q4" s="125"/>
+      <c r="R4" s="128"/>
+      <c r="S4" s="129"/>
       <c r="U4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="135"/>
+      <c r="P5" s="135"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="137"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="135" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="142"/>
-      <c r="U6" s="143" t="s">
+      <c r="B6" s="123"/>
+      <c r="C6" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="V6" s="143"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="144"/>
+      <c r="S6" s="145"/>
+      <c r="U6" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="V6" s="146"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="134"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="132"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="135"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="137"/>
       <c r="U7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="135" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="142"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="138" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="139"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="144"/>
+      <c r="O8" s="143"/>
+      <c r="P8" s="143"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="145"/>
       <c r="U8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="134"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="136"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="135"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="137"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="138" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="139"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="143"/>
+      <c r="L10" s="143"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="144"/>
+      <c r="O10" s="143"/>
+      <c r="P10" s="143"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="144"/>
+      <c r="S10" s="145"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="151"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="149"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="152"/>
+      <c r="H11" s="152"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="151"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="151"/>
+      <c r="O11" s="153"/>
+      <c r="P11" s="153"/>
+      <c r="Q11" s="150"/>
+      <c r="R11" s="151"/>
+      <c r="S11" s="154"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="107" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="108" t="s">
+      <c r="B12" s="110" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
+      <c r="C12" s="111" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="125"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="127"/>
+      <c r="P12" s="127"/>
+      <c r="Q12" s="125"/>
+      <c r="R12" s="128"/>
+      <c r="S12" s="129"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="134"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="132"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="137"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="135" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="138" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="157"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="140"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="140"/>
+      <c r="R14" s="144"/>
+      <c r="S14" s="145"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="134"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="135"/>
+      <c r="P15" s="135"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="136"/>
+      <c r="S15" s="137"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="135" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="138" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="159"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="145"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="151"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="160"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="151"/>
+      <c r="O17" s="153"/>
+      <c r="P17" s="153"/>
+      <c r="Q17" s="150"/>
+      <c r="R17" s="151"/>
+      <c r="S17" s="154"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="109" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="108" t="s">
+      <c r="B18" s="112" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
+      <c r="C18" s="111" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="124"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="125"/>
+      <c r="R18" s="128"/>
+      <c r="S18" s="129"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="129"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="134"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="135"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="132"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="135"/>
+      <c r="Q19" s="132"/>
+      <c r="R19" s="136"/>
+      <c r="S19" s="137"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="135" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="138" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="139"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="142"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="140"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="143"/>
+      <c r="Q20" s="140"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="145"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="134"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="132"/>
+      <c r="N21" s="161"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="136"/>
+      <c r="S21" s="137"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="141"/>
-      <c r="S22" s="142"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="142"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="140"/>
+      <c r="N22" s="144"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="143"/>
+      <c r="Q22" s="140"/>
+      <c r="R22" s="144"/>
+      <c r="S22" s="145"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="151"/>
+      <c r="B23" s="147"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="151"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="153"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="153"/>
+      <c r="L23" s="153"/>
+      <c r="M23" s="150"/>
+      <c r="N23" s="151"/>
+      <c r="O23" s="153"/>
+      <c r="P23" s="153"/>
+      <c r="Q23" s="150"/>
+      <c r="R23" s="151"/>
+      <c r="S23" s="154"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="109" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="108" t="s">
+      <c r="B24" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="126"/>
+      <c r="C24" s="111" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="124"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="156"/>
+      <c r="N24" s="126"/>
+      <c r="O24" s="155"/>
+      <c r="P24" s="155"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="129"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="133"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="134"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="135"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="132"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="135"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="137"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="141"/>
-      <c r="S26" s="142"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="138" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="139"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="144"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="144"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="142"/>
+      <c r="Q26" s="140"/>
+      <c r="R26" s="144"/>
+      <c r="S26" s="145"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="134"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="130"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="132"/>
+      <c r="N27" s="136"/>
+      <c r="O27" s="135"/>
+      <c r="P27" s="135"/>
+      <c r="Q27" s="132"/>
+      <c r="R27" s="136"/>
+      <c r="S27" s="137"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="135" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="156"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="138" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="139"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="143"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="140"/>
+      <c r="N28" s="144"/>
+      <c r="O28" s="143"/>
+      <c r="P28" s="142"/>
+      <c r="Q28" s="159"/>
+      <c r="R28" s="144"/>
+      <c r="S28" s="145"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="162"/>
-      <c r="Q29" s="160"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="165"/>
+      <c r="B29" s="123"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="165"/>
+      <c r="H29" s="166"/>
+      <c r="I29" s="163"/>
+      <c r="J29" s="164"/>
+      <c r="K29" s="165"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="163"/>
+      <c r="N29" s="167"/>
+      <c r="O29" s="166"/>
+      <c r="P29" s="165"/>
+      <c r="Q29" s="163"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="168"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="166" t="s">
+      <c r="B30" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="167" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="172"/>
+      <c r="C30" s="170" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="124"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="172"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="172"/>
+      <c r="K30" s="172"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="172"/>
+      <c r="O30" s="173"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="172"/>
+      <c r="S30" s="175"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="177"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="134"/>
+      <c r="B31" s="176"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="180"/>
+      <c r="M31" s="181"/>
+      <c r="N31" s="179"/>
+      <c r="O31" s="180"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="181"/>
+      <c r="R31" s="179"/>
+      <c r="S31" s="137"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174" t="s">
+      <c r="B32" s="176"/>
+      <c r="C32" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="183"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="183"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="184"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="183"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="184"/>
+      <c r="K32" s="184"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="186"/>
+      <c r="N32" s="184"/>
+      <c r="O32" s="185"/>
+      <c r="P32" s="184"/>
+      <c r="Q32" s="186"/>
+      <c r="R32" s="184"/>
+      <c r="S32" s="187"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="177"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="178"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="134"/>
+      <c r="B33" s="176"/>
+      <c r="C33" s="177"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="178"/>
+      <c r="F33" s="182"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="182"/>
+      <c r="L33" s="180"/>
+      <c r="M33" s="181"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="180"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="181"/>
+      <c r="R33" s="179"/>
+      <c r="S33" s="137"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="173"/>
-      <c r="C34" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="191"/>
-      <c r="U34" s="192"/>
-      <c r="V34" s="193" t="s">
+      <c r="B34" s="176"/>
+      <c r="C34" s="130" t="s">
         <v>110</v>
       </c>
+      <c r="D34" s="162"/>
+      <c r="E34" s="190"/>
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="192"/>
+      <c r="I34" s="193"/>
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="192"/>
+      <c r="M34" s="193"/>
+      <c r="N34" s="191"/>
+      <c r="O34" s="192"/>
+      <c r="P34" s="191"/>
+      <c r="Q34" s="193"/>
+      <c r="R34" s="191"/>
+      <c r="S34" s="194"/>
+      <c r="U34" s="195"/>
+      <c r="V34" s="196" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="194"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="199"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="151"/>
-      <c r="U35" s="200"/>
-      <c r="V35" s="201" t="s">
-        <v>111</v>
+      <c r="B35" s="197"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="199"/>
+      <c r="F35" s="200"/>
+      <c r="G35" s="200"/>
+      <c r="H35" s="201"/>
+      <c r="I35" s="202"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="200"/>
+      <c r="L35" s="201"/>
+      <c r="M35" s="202"/>
+      <c r="N35" s="200"/>
+      <c r="O35" s="201"/>
+      <c r="P35" s="200"/>
+      <c r="Q35" s="202"/>
+      <c r="R35" s="200"/>
+      <c r="S35" s="154"/>
+      <c r="U35" s="203"/>
+      <c r="V35" s="204" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>date</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve">Circuit d'alimentation avec schéma + liste de matériel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refonte de l'alimentation + norme EN 55032 Classe B</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1649,7 +1652,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="201">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1682,9 +1685,6 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1692,20 +1692,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -2903,6 +2894,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5/4/2026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5/5/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4565,7 +4559,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>367745</xdr:colOff>
+      <xdr:colOff>367744</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2549</xdr:rowOff>
     </xdr:from>
@@ -4635,8 +4629,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E14">
-  <autoFilter ref="B2:E14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E15">
+  <autoFilter ref="B2:E15"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5233,7 +5227,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>8.771929824561403e-002</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5260,7 +5254,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.21052631578947364</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5270,7 +5264,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
@@ -5287,7 +5281,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.54385964912280704</v>
+        <v>0.46969696969696972</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5297,7 +5291,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5359,12 +5353,12 @@
       <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5375,7 +5369,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5383,10 +5377,10 @@
       <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
@@ -5395,14 +5389,14 @@
         <v>0</v>
       </c>
       <c r="J10" s="4"/>
-      <c r="K10" s="17"/>
+      <c r="K10" s="16"/>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>6</v>
@@ -5415,7 +5409,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5429,12 +5423,12 @@
         <v>46146</v>
       </c>
       <c r="C12" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H12" s="10"/>
@@ -5451,7 +5445,7 @@
       <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G13" t="s">
@@ -5459,28 +5453,36 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>46.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="42.75">
-      <c r="B14" s="20">
+      <c r="B14" s="17">
         <v>46146</v>
       </c>
-      <c r="C14" s="21">
-        <v>6.25e-002</v>
-      </c>
-      <c r="D14" s="22" t="s">
+      <c r="C14" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="28.5">
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
+      <c r="B15" s="5">
+        <v>46147</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" ht="28.5">
       <c r="B16" s="5"/>
@@ -5631,9 +5633,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="25"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5684,200 +5686,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="26"/>
-      <c r="C49" s="27"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="26"/>
-      <c r="C50" s="27"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="26"/>
-      <c r="C51" s="27"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="26"/>
-      <c r="C52" s="27"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="26"/>
-      <c r="C53" s="27"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="26"/>
-      <c r="C54" s="28"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="24"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="26"/>
-      <c r="C55" s="28"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="26"/>
-      <c r="C56" s="28"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="26"/>
-      <c r="C57" s="28"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="26"/>
-      <c r="C58" s="28"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="26"/>
-      <c r="C59" s="28"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="26"/>
-      <c r="C60" s="28"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="24"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="26"/>
-      <c r="C61" s="28"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="26"/>
-      <c r="C62" s="28"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="26"/>
-      <c r="C63" s="28"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="26"/>
-      <c r="C64" s="28"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="26"/>
-      <c r="C65" s="28"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="26"/>
-      <c r="C66" s="28"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="26"/>
-      <c r="C67" s="28"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="26"/>
-      <c r="C68" s="28"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="26"/>
-      <c r="C69" s="28"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="26"/>
-      <c r="C70" s="28"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="26"/>
-      <c r="C71" s="28"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="26"/>
-      <c r="C72" s="28"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="26"/>
-      <c r="C73" s="28"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="26"/>
-      <c r="C74" s="28"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="26"/>
-      <c r="C75" s="28"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="28"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="28"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="28"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="28"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="28"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="28"/>
+      <c r="C81" s="24"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5897,13 +5899,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00880089-0001-4496-A713-003100970018}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{003B00FC-0097-4066-89A8-00A9002F00DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{009600EE-0003-4E7B-B8A5-00C400C100FA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{002000A1-00B3-4418-AB2E-0004000500D4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5940,1671 +5942,1674 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="str" cm="1">
-        <f t="array" ref="A2:A6">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="25" t="str" cm="1">
+        <f t="array" ref="A2:A7">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="30"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="25" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="29">
+      <c r="A6" s="25">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30">
+      <c r="A7" s="25">
+        <f/>
+        <v>46147</v>
+      </c>
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="29"/>
-      <c r="B8" s="30">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="29"/>
-      <c r="B9" s="30">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="29"/>
-      <c r="B19" s="30">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="31"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29"/>
-      <c r="C28" s="32">
+      <c r="A28" s="25"/>
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29"/>
-      <c r="C29" s="32">
+      <c r="A29" s="25"/>
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29"/>
-      <c r="C30" s="32">
+      <c r="A30" s="25"/>
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29"/>
-      <c r="C31" s="32">
+      <c r="A31" s="25"/>
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29"/>
-      <c r="C32" s="32">
+      <c r="A32" s="25"/>
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29"/>
-      <c r="C33" s="32">
+      <c r="A33" s="25"/>
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29"/>
-      <c r="C34" s="32">
+      <c r="A34" s="25"/>
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29"/>
-      <c r="C35" s="32">
+      <c r="A35" s="25"/>
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29"/>
-      <c r="C36" s="32">
+      <c r="A36" s="25"/>
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29"/>
-      <c r="C37" s="32">
+      <c r="A37" s="25"/>
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29"/>
-      <c r="C38" s="32">
+      <c r="A38" s="25"/>
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29"/>
-      <c r="C39" s="32">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29"/>
-      <c r="B41" s="30" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="33"/>
-      <c r="B42" s="30" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="33"/>
-      <c r="B43" s="30" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="33"/>
-      <c r="B44" s="30" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="33"/>
-      <c r="B45" s="30" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33"/>
-      <c r="B46" s="30" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34"/>
-      <c r="B47" s="30" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="34"/>
-      <c r="B48" s="30" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34"/>
-      <c r="B49" s="30" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="34"/>
-      <c r="B50" s="30" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34"/>
-      <c r="B51" s="30" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="34"/>
-      <c r="B52" s="30" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34"/>
-      <c r="B53" s="30" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="34"/>
-      <c r="B54" s="30" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34"/>
-      <c r="B55" s="30" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="34"/>
-      <c r="B56" s="30" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34"/>
-      <c r="B57" s="30" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="34"/>
-      <c r="B58" s="30" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34"/>
-      <c r="B59" s="30" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="34"/>
-      <c r="B60" s="30" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34"/>
-      <c r="B61" s="30" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34"/>
-      <c r="B62" s="30" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34"/>
-      <c r="B63" s="30" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="34"/>
-      <c r="B64" s="30" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="34"/>
-      <c r="B65" s="30" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="34"/>
-      <c r="B66" s="30" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="34"/>
-      <c r="B67" s="30" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="34"/>
-      <c r="B68" s="30" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="34"/>
-      <c r="B69" s="30" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="34"/>
-      <c r="B70" s="30" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="34"/>
-      <c r="B71" s="30" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="34"/>
-      <c r="B72" s="30" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="34"/>
-      <c r="B73" s="30" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="34"/>
-      <c r="B74" s="30" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="34"/>
-      <c r="B75" s="30" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="34"/>
-      <c r="B76" s="30" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="34"/>
-      <c r="B77" s="30" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="34"/>
-      <c r="B78" s="30" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="34"/>
-      <c r="B79" s="30" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="32">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="34"/>
-      <c r="B80" s="30" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="34"/>
-      <c r="B81" s="30" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="34"/>
-      <c r="B82" s="30" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="34"/>
-      <c r="B83" s="30" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="32">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="34"/>
-      <c r="B84" s="30" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="34"/>
-      <c r="B85" s="30" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="32">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="34"/>
-      <c r="B86" s="30" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="34"/>
-      <c r="B87" s="30" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="32">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="34"/>
-      <c r="B88" s="30" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="34"/>
-      <c r="B89" s="30" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="32">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="34"/>
-      <c r="B90" s="30" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="34"/>
-      <c r="B91" s="30" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="32">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="34"/>
-      <c r="B92" s="30" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="34"/>
-      <c r="B93" s="30" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="32">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="34"/>
-      <c r="B94" s="30" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="34"/>
-      <c r="B95" s="30" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="34"/>
-      <c r="B96" s="30" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="34"/>
-      <c r="B97" s="30" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="32">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="34"/>
-      <c r="B98" s="30" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="34"/>
-      <c r="B99" s="30" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="34"/>
-      <c r="B100" s="30" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="34"/>
-      <c r="B101" s="30" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="34"/>
-      <c r="B102" s="30" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="34"/>
-      <c r="B103" s="30" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="32">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="34"/>
-      <c r="B104" s="30" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="34"/>
-      <c r="B105" s="30" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="32">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="34"/>
-      <c r="B106" s="30" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="34"/>
-      <c r="B107" s="30" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="32">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="34"/>
-      <c r="B108" s="30" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="32">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="34"/>
-      <c r="B109" s="30" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="32">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="34"/>
-      <c r="B110" s="30" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="32">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="34"/>
-      <c r="B111" s="30" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="32">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="34"/>
-      <c r="B112" s="30" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="32">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="34"/>
-      <c r="B113" s="30" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="32">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="34"/>
-      <c r="B114" s="30" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="32">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="34"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="32"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="34"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="32"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="34"/>
-      <c r="B117" s="34"/>
-      <c r="C117" s="32"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="34"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="32"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="34"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="32"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="34"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="32"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="34"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="32"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="34"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="32"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="34"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="32"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="34"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="32"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="34"/>
-      <c r="B125" s="34"/>
-      <c r="C125" s="32"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="34"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="32"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="34"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="32"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="34"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="32"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="34"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="32"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="32"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="34"/>
-      <c r="B131" s="34"/>
-      <c r="C131" s="32"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="34"/>
-      <c r="B132" s="34"/>
-      <c r="C132" s="32"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="34"/>
-      <c r="B133" s="34"/>
-      <c r="C133" s="32"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="34"/>
-      <c r="B134" s="34"/>
-      <c r="C134" s="32"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="34"/>
-      <c r="B135" s="34"/>
-      <c r="C135" s="32"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="34"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="32"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="34"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="32"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="32"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="32"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="34"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="32"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="32"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="32"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="32"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="32"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="32"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="32"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="34"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="32"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="34"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="32"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="34"/>
-      <c r="B149" s="34"/>
-      <c r="C149" s="32"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="34"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="32"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="34"/>
-      <c r="B151" s="34"/>
-      <c r="C151" s="32"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="34"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="32"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="34"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="32"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="34"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="32"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="34"/>
-      <c r="B155" s="34"/>
-      <c r="C155" s="32"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="34"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="32"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="34"/>
-      <c r="B157" s="34"/>
-      <c r="C157" s="32"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="34"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="32"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="34"/>
-      <c r="B159" s="34"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="34"/>
-      <c r="B160" s="34"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="34"/>
-      <c r="B161" s="34"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="34"/>
-      <c r="B162" s="34"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="34"/>
-      <c r="B163" s="34"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="34"/>
-      <c r="B164" s="34"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="34"/>
-      <c r="B165" s="34"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="34"/>
-      <c r="B166" s="34"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="34"/>
-      <c r="B167" s="34"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="34"/>
-      <c r="B168" s="34"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="34"/>
-      <c r="B169" s="34"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="34"/>
-      <c r="B170" s="34"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="34"/>
-      <c r="B171" s="34"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="34"/>
-      <c r="B172" s="34"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="34"/>
-      <c r="B173" s="34"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="34"/>
-      <c r="B174" s="34"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="34"/>
-      <c r="B175" s="34"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="34"/>
-      <c r="B176" s="34"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="34"/>
-      <c r="B177" s="34"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="34"/>
-      <c r="B178" s="34"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="34"/>
-      <c r="B179" s="34"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="34"/>
-      <c r="B180" s="34"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="34"/>
-      <c r="B181" s="34"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="34"/>
-      <c r="B182" s="34"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="34"/>
-      <c r="B183" s="34"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="34"/>
-      <c r="B184" s="34"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="34"/>
-      <c r="B185" s="34"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="34"/>
-      <c r="B186" s="34"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="34"/>
-      <c r="B187" s="34"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="34"/>
-      <c r="B188" s="34"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="34"/>
-      <c r="B189" s="34"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="34"/>
-      <c r="B190" s="34"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="34"/>
-      <c r="B191" s="34"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="34"/>
-      <c r="B192" s="34"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="34"/>
-      <c r="B193" s="34"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="34"/>
-      <c r="B194" s="34"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="34"/>
-      <c r="B195" s="34"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="34"/>
-      <c r="B196" s="34"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="34"/>
-      <c r="B197" s="34"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="34"/>
-      <c r="B198" s="34"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="34"/>
-      <c r="B199" s="34"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="34"/>
-      <c r="B200" s="34"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="34"/>
-      <c r="B201" s="34"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="34"/>
-      <c r="B202" s="34"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="34"/>
-      <c r="B203" s="34"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="34"/>
-      <c r="B204" s="34"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="34"/>
-      <c r="B205" s="34"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="34"/>
-      <c r="B206" s="34"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="34"/>
-      <c r="B207" s="34"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="34"/>
-      <c r="B208" s="34"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="34"/>
-      <c r="B209" s="34"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="34"/>
-      <c r="B210" s="34"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="34"/>
-      <c r="B211" s="34"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="34"/>
-      <c r="B212" s="34"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="34"/>
-      <c r="B213" s="34"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="34"/>
-      <c r="B214" s="34"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="34"/>
-      <c r="B215" s="34"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="34"/>
-      <c r="B216" s="34"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="34"/>
-      <c r="B217" s="34"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="34"/>
-      <c r="B218" s="34"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="34"/>
-      <c r="B219" s="34"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="34"/>
-      <c r="B220" s="34"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="34"/>
-      <c r="B221" s="34"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="34"/>
-      <c r="B222" s="34"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="34"/>
-      <c r="B223" s="34"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="34"/>
-      <c r="B224" s="34"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="34"/>
-      <c r="B225" s="34"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="34"/>
-      <c r="B226" s="34"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="34"/>
-      <c r="B227" s="34"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="34"/>
-      <c r="B228" s="34"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="34"/>
-      <c r="B229" s="34"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="34"/>
-      <c r="B230" s="34"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="34"/>
-      <c r="B231" s="34"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="34"/>
-      <c r="B232" s="34"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="34"/>
-      <c r="B233" s="34"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="34"/>
-      <c r="B234" s="34"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="34"/>
-      <c r="B235" s="34"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7633,1266 +7638,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="37" t="s">
+    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="B1" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="38" t="s">
+      <c r="F1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="G1" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="H1" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="I1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="J1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="L1" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="M1" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="N1" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="O1" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="38" t="s">
+      <c r="P1" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="Q1" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="38" t="s">
+      <c r="R1" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="35"/>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="35"/>
-      <c r="AT1" s="35"/>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="35"/>
-      <c r="AX1" s="35"/>
-      <c r="AY1" s="35"/>
-      <c r="AZ1" s="35"/>
-      <c r="BA1" s="35"/>
-      <c r="BB1" s="35"/>
-      <c r="BC1" s="35"/>
-    </row>
-    <row r="2" s="35" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="S1" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38">
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+    </row>
+    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34">
         <v>7</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="34">
         <v>4</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="34">
         <v>4</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="34">
         <v>7</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="34">
         <v>5</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="34">
         <v>7</v>
       </c>
-      <c r="I2" s="39">
-        <v>0</v>
-      </c>
-      <c r="J2" s="39">
-        <v>0</v>
-      </c>
-      <c r="K2" s="38">
+      <c r="I2" s="35">
+        <v>0</v>
+      </c>
+      <c r="J2" s="35">
+        <v>0</v>
+      </c>
+      <c r="K2" s="34">
         <v>5</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L2" s="34">
         <v>4</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="34">
         <v>7</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="34">
         <v>4</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2" s="34">
         <v>5</v>
       </c>
-      <c r="P2" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="38">
+      <c r="P2" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="34">
         <v>4</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="34">
         <v>7</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="34">
         <v>5</v>
       </c>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-    </row>
-    <row r="3" s="35" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="42" t="s">
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+    </row>
+    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="43" t="str">
+      <c r="B3" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="39" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45" t="str">
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="45" t="str">
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="41" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35"/>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="54"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="50"/>
       <c r="V4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="62"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="58"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="55"/>
-      <c r="B6" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="68"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="64"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="55"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="68"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="64"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="71" t="s">
+      <c r="A8" s="51"/>
+      <c r="B8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="62"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="58"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="55"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="59"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="62"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="58"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="75"/>
-      <c r="O10" s="64"/>
-      <c r="P10" s="64"/>
-      <c r="Q10" s="64"/>
-      <c r="R10" s="64"/>
-      <c r="S10" s="76"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="72"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="77"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="79"/>
-      <c r="S11" s="84"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="80"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="85" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="86" t="s">
+      <c r="A12" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="54"/>
+      <c r="B12" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="50"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="59"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="62"/>
+      <c r="A13" s="83"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="58"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="87"/>
-      <c r="B14" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="68"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="64"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="87"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="68"/>
+      <c r="A15" s="83"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="64"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="87"/>
-      <c r="B16" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="62"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="58"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="87"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="62"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="58"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="87"/>
-      <c r="B18" s="73" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="65"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="68"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="64"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="84"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="S19" s="80"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="86" t="s">
+      <c r="A20" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="54"/>
+      <c r="B20" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="50"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="55"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="62"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="58"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="55"/>
-      <c r="B22" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="68"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="64"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="55"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="68"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="64"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="55"/>
-      <c r="B24" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="60"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="62"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="58"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="55"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="62"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="58"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="55"/>
-      <c r="B26" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="68"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="64"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="55"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="65"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="65"/>
-      <c r="R27" s="65"/>
-      <c r="S27" s="68"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="64"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="62"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="58"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="77"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="92"/>
-      <c r="P29" s="92"/>
-      <c r="Q29" s="92"/>
-      <c r="R29" s="92"/>
-      <c r="S29" s="95"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="88"/>
+      <c r="P29" s="88"/>
+      <c r="Q29" s="88"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="91"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="97" t="s">
+      <c r="A30" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="90"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="98"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="101"/>
+      <c r="B30" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="97"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="65"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="68"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="64"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="102"/>
-      <c r="B32" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="62"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="58"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="59"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="58"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="62"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="54"/>
+      <c r="R33" s="54"/>
+      <c r="S33" s="58"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="102"/>
-      <c r="B34" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="65"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="68"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="64"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="66"/>
-      <c r="N35" s="67"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="68"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="64"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="102"/>
-      <c r="B36" s="71" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="64"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="58"/>
-      <c r="S36" s="62"/>
+      <c r="A36" s="98"/>
+      <c r="B36" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="60"/>
+      <c r="Q36" s="54"/>
+      <c r="R36" s="54"/>
+      <c r="S36" s="58"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="102"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="60"/>
-      <c r="O37" s="58"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="58"/>
-      <c r="S37" s="62"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="54"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="54"/>
+      <c r="S37" s="58"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="66"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="64"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="68"/>
+      <c r="A38" s="98"/>
+      <c r="B38" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="64"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="102"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="66"/>
-      <c r="N39" s="67"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="68"/>
+      <c r="A39" s="98"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="64"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="102"/>
-      <c r="B40" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="60"/>
-      <c r="O40" s="58"/>
-      <c r="P40" s="58"/>
-      <c r="Q40" s="64"/>
-      <c r="R40" s="64"/>
-      <c r="S40" s="62"/>
+      <c r="A40" s="98"/>
+      <c r="B40" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="54"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="58"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="102"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="62"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="56"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="58"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="102"/>
-      <c r="B42" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="65"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="66"/>
-      <c r="N42" s="67"/>
-      <c r="O42" s="65"/>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="64"/>
-      <c r="S42" s="76"/>
+      <c r="A42" s="98"/>
+      <c r="B42" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="72"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="103"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
-      <c r="F43" s="79"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="82"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="79"/>
-      <c r="L43" s="79"/>
-      <c r="M43" s="81"/>
-      <c r="N43" s="82"/>
-      <c r="O43" s="79"/>
-      <c r="P43" s="79"/>
-      <c r="Q43" s="79"/>
-      <c r="R43" s="79"/>
-      <c r="S43" s="84"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="77"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="75"/>
+      <c r="S43" s="80"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="48" t="s">
+      <c r="A44" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="52"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="104"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="48"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="100"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="55"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="61"/>
-      <c r="J45" s="61"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="59"/>
-      <c r="N45" s="60"/>
-      <c r="O45" s="58"/>
-      <c r="P45" s="58"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="58"/>
-      <c r="S45" s="62"/>
-      <c r="V45" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="W45" s="64"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="54"/>
+      <c r="S45" s="58"/>
+      <c r="V45" s="101" t="s">
+        <v>75</v>
+      </c>
+      <c r="W45" s="60"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="55"/>
-      <c r="B46" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="61"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="66"/>
-      <c r="N46" s="67"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="R46" s="65"/>
-      <c r="S46" s="76"/>
-      <c r="V46" s="105" t="s">
+      <c r="A46" s="51"/>
+      <c r="B46" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="W46" s="57"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="72"/>
+      <c r="V46" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="W46" s="53"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="77"/>
-      <c r="B47" s="107"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="79"/>
-      <c r="L47" s="79"/>
-      <c r="M47" s="81"/>
-      <c r="N47" s="82"/>
-      <c r="O47" s="79"/>
-      <c r="P47" s="79"/>
-      <c r="Q47" s="79"/>
-      <c r="R47" s="79"/>
-      <c r="S47" s="84"/>
-      <c r="V47" s="105" t="s">
-        <v>77</v>
-      </c>
-      <c r="W47" s="70"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="78"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="75"/>
+      <c r="P47" s="75"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="75"/>
+      <c r="S47" s="80"/>
+      <c r="V47" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="W47" s="66"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="108">
+      <c r="V54" s="104">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8900,7 +8905,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8908,7 +8913,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -8972,801 +8977,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="109"/>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="110" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="111" t="s">
+      <c r="B2" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="112" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="113" t="s">
+      <c r="C2" s="107" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="114" t="s">
+      <c r="E2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="114" t="s">
+      <c r="F2" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="114" t="s">
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="114" t="s">
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="115"/>
-      <c r="AD2" s="33"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="110" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="111"/>
+      <c r="AD2" s="29"/>
     </row>
     <row r="3">
-      <c r="B3" s="116"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="119">
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="114" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="115">
         <v>4</v>
       </c>
-      <c r="F3" s="120">
+      <c r="F3" s="116">
         <v>1</v>
       </c>
-      <c r="G3" s="121">
+      <c r="G3" s="117">
         <v>2</v>
       </c>
-      <c r="H3" s="121">
+      <c r="H3" s="117">
         <v>3</v>
       </c>
-      <c r="I3" s="119">
+      <c r="I3" s="115">
         <v>4</v>
       </c>
-      <c r="J3" s="120">
+      <c r="J3" s="116">
         <v>1</v>
       </c>
-      <c r="K3" s="121">
+      <c r="K3" s="117">
         <v>2</v>
       </c>
-      <c r="L3" s="121">
+      <c r="L3" s="117">
         <v>3</v>
       </c>
-      <c r="M3" s="119">
+      <c r="M3" s="115">
         <v>4</v>
       </c>
-      <c r="N3" s="120">
+      <c r="N3" s="116">
         <v>1</v>
       </c>
-      <c r="O3" s="121">
+      <c r="O3" s="117">
         <v>2</v>
       </c>
-      <c r="P3" s="121">
+      <c r="P3" s="117">
         <v>3</v>
       </c>
-      <c r="Q3" s="119">
+      <c r="Q3" s="115">
         <v>4</v>
       </c>
-      <c r="R3" s="120">
+      <c r="R3" s="116">
         <v>1</v>
       </c>
-      <c r="S3" s="122">
+      <c r="S3" s="118">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="111" t="s">
+      <c r="B4" s="119" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="124"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="125"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
-      <c r="Q4" s="125"/>
-      <c r="R4" s="128"/>
-      <c r="S4" s="129"/>
+      <c r="C4" s="107" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="120"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="125"/>
       <c r="U4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="123"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="136"/>
-      <c r="O5" s="135"/>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="136"/>
-      <c r="S5" s="137"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="131"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="131"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="133"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="123"/>
-      <c r="C6" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="139"/>
-      <c r="E6" s="140"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="143"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="144"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="143"/>
-      <c r="M6" s="140"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="143"/>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="140"/>
-      <c r="R6" s="144"/>
-      <c r="S6" s="145"/>
-      <c r="U6" s="146" t="s">
+      <c r="B6" s="119"/>
+      <c r="C6" s="134" t="s">
         <v>92</v>
       </c>
-      <c r="V6" s="146"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="139"/>
+      <c r="P6" s="139"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="141"/>
+      <c r="U6" s="142" t="s">
+        <v>93</v>
+      </c>
+      <c r="V6" s="142"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="123"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="135"/>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="136"/>
-      <c r="S7" s="137"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="132"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="132"/>
+      <c r="S7" s="133"/>
       <c r="U7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="123"/>
-      <c r="C8" s="138" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="143"/>
-      <c r="L8" s="143"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="144"/>
-      <c r="O8" s="143"/>
-      <c r="P8" s="143"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="144"/>
-      <c r="S8" s="145"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="134" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="135"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="141"/>
       <c r="U8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="123"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="135"/>
-      <c r="M9" s="132"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="132"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="137"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="132"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="133"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="123"/>
-      <c r="C10" s="138" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="139"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="142"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="143"/>
-      <c r="L10" s="143"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="144"/>
-      <c r="O10" s="143"/>
-      <c r="P10" s="143"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="145"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="134" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="135"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="136"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="141"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="151"/>
-      <c r="K11" s="153"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="151"/>
-      <c r="O11" s="153"/>
-      <c r="P11" s="153"/>
-      <c r="Q11" s="150"/>
-      <c r="R11" s="151"/>
-      <c r="S11" s="154"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
+      <c r="H11" s="148"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="147"/>
+      <c r="O11" s="149"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="150"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="110" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="111" t="s">
+      <c r="B12" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="155"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
-      <c r="M12" s="125"/>
-      <c r="N12" s="128"/>
-      <c r="O12" s="127"/>
-      <c r="P12" s="127"/>
-      <c r="Q12" s="125"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="129"/>
+      <c r="C12" s="107" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="152"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="124"/>
+      <c r="S12" s="125"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="123"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="136"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="135"/>
-      <c r="Q13" s="132"/>
-      <c r="R13" s="136"/>
-      <c r="S13" s="137"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="131"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="133"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="123"/>
-      <c r="C14" s="138" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="157"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="143"/>
-      <c r="L14" s="143"/>
-      <c r="M14" s="140"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="143"/>
-      <c r="P14" s="143"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="145"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="134" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="153"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="140"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="141"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="123"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="132"/>
-      <c r="R15" s="136"/>
-      <c r="S15" s="137"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="129"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="131"/>
+      <c r="Q15" s="128"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="133"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="123"/>
-      <c r="C16" s="138" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="139"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="142"/>
-      <c r="I16" s="159"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
-      <c r="M16" s="140"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="143"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="145"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="134" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="155"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="139"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="141"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="153"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="160"/>
-      <c r="K17" s="152"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="151"/>
-      <c r="O17" s="153"/>
-      <c r="P17" s="153"/>
-      <c r="Q17" s="150"/>
-      <c r="R17" s="151"/>
-      <c r="S17" s="154"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="149"/>
+      <c r="P17" s="149"/>
+      <c r="Q17" s="146"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="150"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="112" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="111" t="s">
+      <c r="B18" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="124"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="125"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="127"/>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="125"/>
-      <c r="R18" s="128"/>
-      <c r="S18" s="129"/>
+      <c r="C18" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="125"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="123"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="136"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="135"/>
-      <c r="M19" s="132"/>
-      <c r="N19" s="136"/>
-      <c r="O19" s="135"/>
-      <c r="P19" s="135"/>
-      <c r="Q19" s="132"/>
-      <c r="R19" s="136"/>
-      <c r="S19" s="137"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="132"/>
+      <c r="K19" s="131"/>
+      <c r="L19" s="131"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="132"/>
+      <c r="O19" s="131"/>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="133"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="123"/>
-      <c r="C20" s="138" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="142"/>
-      <c r="L20" s="142"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="144"/>
-      <c r="O20" s="143"/>
-      <c r="P20" s="143"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="144"/>
-      <c r="S20" s="145"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="134" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="155"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="140"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="140"/>
+      <c r="S20" s="141"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="123"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="136"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="135"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="161"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="135"/>
-      <c r="Q21" s="132"/>
-      <c r="R21" s="136"/>
-      <c r="S21" s="137"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="128"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="133"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="123"/>
-      <c r="C22" s="138" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="142"/>
-      <c r="L22" s="142"/>
-      <c r="M22" s="140"/>
-      <c r="N22" s="144"/>
-      <c r="O22" s="143"/>
-      <c r="P22" s="143"/>
-      <c r="Q22" s="140"/>
-      <c r="R22" s="144"/>
-      <c r="S22" s="145"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="135"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="140"/>
+      <c r="O22" s="139"/>
+      <c r="P22" s="139"/>
+      <c r="Q22" s="136"/>
+      <c r="R22" s="140"/>
+      <c r="S22" s="141"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="151"/>
-      <c r="G23" s="153"/>
-      <c r="H23" s="153"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="151"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="150"/>
-      <c r="N23" s="151"/>
-      <c r="O23" s="153"/>
-      <c r="P23" s="153"/>
-      <c r="Q23" s="150"/>
-      <c r="R23" s="151"/>
-      <c r="S23" s="154"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="149"/>
+      <c r="L23" s="149"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="149"/>
+      <c r="P23" s="149"/>
+      <c r="Q23" s="146"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="150"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="112" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="111" t="s">
+      <c r="B24" s="108" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="124"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="156"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="155"/>
-      <c r="P24" s="155"/>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="128"/>
-      <c r="S24" s="129"/>
+      <c r="C24" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="123"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="152"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="151"/>
+      <c r="P24" s="151"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="125"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="123"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="135"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="135"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="132"/>
-      <c r="N25" s="136"/>
-      <c r="O25" s="135"/>
-      <c r="P25" s="135"/>
-      <c r="Q25" s="132"/>
-      <c r="R25" s="136"/>
-      <c r="S25" s="137"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="132"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="131"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="132"/>
+      <c r="S25" s="133"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="123"/>
-      <c r="C26" s="138" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="139"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="143"/>
-      <c r="L26" s="143"/>
-      <c r="M26" s="140"/>
-      <c r="N26" s="144"/>
-      <c r="O26" s="142"/>
-      <c r="P26" s="142"/>
-      <c r="Q26" s="140"/>
-      <c r="R26" s="144"/>
-      <c r="S26" s="145"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="134" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="135"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="140"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="138"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="140"/>
+      <c r="S26" s="141"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="123"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="132"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="132"/>
-      <c r="R27" s="136"/>
-      <c r="S27" s="137"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="132"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="131"/>
+      <c r="Q27" s="128"/>
+      <c r="R27" s="132"/>
+      <c r="S27" s="133"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="123"/>
-      <c r="C28" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="143"/>
-      <c r="L28" s="143"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="144"/>
-      <c r="O28" s="143"/>
-      <c r="P28" s="142"/>
-      <c r="Q28" s="159"/>
-      <c r="R28" s="144"/>
-      <c r="S28" s="145"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="134" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="135"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="140"/>
+      <c r="O28" s="139"/>
+      <c r="P28" s="138"/>
+      <c r="Q28" s="155"/>
+      <c r="R28" s="140"/>
+      <c r="S28" s="141"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="123"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="162"/>
-      <c r="E29" s="163"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="165"/>
-      <c r="H29" s="166"/>
-      <c r="I29" s="163"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="165"/>
-      <c r="L29" s="166"/>
-      <c r="M29" s="163"/>
-      <c r="N29" s="167"/>
-      <c r="O29" s="166"/>
-      <c r="P29" s="165"/>
-      <c r="Q29" s="163"/>
-      <c r="R29" s="164"/>
-      <c r="S29" s="168"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="159"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="159"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="162"/>
+      <c r="M29" s="159"/>
+      <c r="N29" s="163"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="159"/>
+      <c r="R29" s="160"/>
+      <c r="S29" s="164"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="169" t="s">
+      <c r="B30" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="170" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="124"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="172"/>
-      <c r="G30" s="172"/>
-      <c r="H30" s="173"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="172"/>
-      <c r="K30" s="172"/>
-      <c r="L30" s="173"/>
-      <c r="M30" s="174"/>
-      <c r="N30" s="172"/>
-      <c r="O30" s="173"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="172"/>
-      <c r="S30" s="175"/>
+      <c r="C30" s="166" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="168"/>
+      <c r="K30" s="168"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="168"/>
+      <c r="O30" s="169"/>
+      <c r="P30" s="168"/>
+      <c r="Q30" s="170"/>
+      <c r="R30" s="168"/>
+      <c r="S30" s="171"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="176"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="181"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="180"/>
-      <c r="M31" s="181"/>
-      <c r="N31" s="179"/>
-      <c r="O31" s="180"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="181"/>
-      <c r="R31" s="179"/>
-      <c r="S31" s="137"/>
+      <c r="B31" s="172"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="178"/>
+      <c r="L31" s="176"/>
+      <c r="M31" s="177"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="176"/>
+      <c r="P31" s="175"/>
+      <c r="Q31" s="177"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="133"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="176"/>
-      <c r="C32" s="177" t="s">
+      <c r="B32" s="172"/>
+      <c r="C32" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="139"/>
-      <c r="E32" s="183"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="186"/>
-      <c r="N32" s="184"/>
-      <c r="O32" s="185"/>
-      <c r="P32" s="184"/>
-      <c r="Q32" s="186"/>
-      <c r="R32" s="184"/>
-      <c r="S32" s="187"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="180"/>
+      <c r="K32" s="180"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="180"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="180"/>
+      <c r="Q32" s="182"/>
+      <c r="R32" s="180"/>
+      <c r="S32" s="183"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="176"/>
-      <c r="C33" s="177"/>
-      <c r="D33" s="131"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="182"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="188"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="179"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="180"/>
-      <c r="M33" s="181"/>
-      <c r="N33" s="179"/>
-      <c r="O33" s="180"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="181"/>
-      <c r="R33" s="179"/>
-      <c r="S33" s="137"/>
+      <c r="B33" s="172"/>
+      <c r="C33" s="173"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="175"/>
+      <c r="K33" s="178"/>
+      <c r="L33" s="176"/>
+      <c r="M33" s="177"/>
+      <c r="N33" s="175"/>
+      <c r="O33" s="176"/>
+      <c r="P33" s="175"/>
+      <c r="Q33" s="177"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="133"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="176"/>
-      <c r="C34" s="130" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="162"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="191"/>
-      <c r="G34" s="191"/>
-      <c r="H34" s="192"/>
-      <c r="I34" s="193"/>
-      <c r="J34" s="191"/>
-      <c r="K34" s="191"/>
-      <c r="L34" s="192"/>
-      <c r="M34" s="193"/>
-      <c r="N34" s="191"/>
-      <c r="O34" s="192"/>
-      <c r="P34" s="191"/>
-      <c r="Q34" s="193"/>
-      <c r="R34" s="191"/>
-      <c r="S34" s="194"/>
-      <c r="U34" s="195"/>
-      <c r="V34" s="196" t="s">
+      <c r="B34" s="172"/>
+      <c r="C34" s="126" t="s">
         <v>111</v>
       </c>
+      <c r="D34" s="158"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="187"/>
+      <c r="K34" s="187"/>
+      <c r="L34" s="188"/>
+      <c r="M34" s="189"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="188"/>
+      <c r="P34" s="187"/>
+      <c r="Q34" s="189"/>
+      <c r="R34" s="187"/>
+      <c r="S34" s="190"/>
+      <c r="U34" s="191"/>
+      <c r="V34" s="192" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="197"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="149"/>
-      <c r="E35" s="199"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="202"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="200"/>
-      <c r="L35" s="201"/>
-      <c r="M35" s="202"/>
-      <c r="N35" s="200"/>
-      <c r="O35" s="201"/>
-      <c r="P35" s="200"/>
-      <c r="Q35" s="202"/>
-      <c r="R35" s="200"/>
-      <c r="S35" s="154"/>
-      <c r="U35" s="203"/>
-      <c r="V35" s="204" t="s">
-        <v>112</v>
+      <c r="B35" s="193"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="195"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="197"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="196"/>
+      <c r="K35" s="196"/>
+      <c r="L35" s="197"/>
+      <c r="M35" s="198"/>
+      <c r="N35" s="196"/>
+      <c r="O35" s="197"/>
+      <c r="P35" s="196"/>
+      <c r="Q35" s="198"/>
+      <c r="R35" s="196"/>
+      <c r="S35" s="150"/>
+      <c r="U35" s="199"/>
+      <c r="V35" s="200" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>date</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t xml:space="preserve">Refonte de l'alimentation + norme EN 55032 Classe B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de toutes les documentation + prix des composants</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1652,7 +1655,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="202">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1694,6 +1697,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4629,8 +4635,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E15">
-  <autoFilter ref="B2:E15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E16">
+  <autoFilter ref="B2:E16"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5227,7 +5233,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.07575757575757576</v>
+        <v>7.5000000000000011e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5254,7 +5260,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.1818181818181818</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5264,7 +5270,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
@@ -5277,11 +5283,11 @@
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>15.5</v>
+        <v>15.833333333333332</v>
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.46969696969696972</v>
+        <v>0.47500000000000003</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5291,7 +5297,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5369,7 +5375,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5396,7 +5402,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>6</v>
@@ -5409,7 +5415,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>33</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5423,7 +5429,7 @@
         <v>46146</v>
       </c>
       <c r="C12" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>22</v>
@@ -5453,7 +5459,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>42</v>
+        <v>41.666666666666671</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5461,7 +5467,7 @@
         <v>46146</v>
       </c>
       <c r="C14" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>22</v>
@@ -5480,15 +5486,23 @@
       <c r="D15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" ht="28.5">
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
+      <c r="B16" s="5">
+        <v>46147</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.3888888888888888e-002</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="5"/>
@@ -5633,9 +5647,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="22"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5686,200 +5700,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="22"/>
-      <c r="C53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="22"/>
-      <c r="C54" s="24"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="22"/>
-      <c r="C55" s="24"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="25"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="22"/>
-      <c r="C56" s="24"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="22"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="22"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="22"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="22"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="22"/>
-      <c r="C61" s="24"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="22"/>
-      <c r="C62" s="24"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="22"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="22"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="22"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="22"/>
-      <c r="C66" s="24"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="22"/>
-      <c r="C67" s="24"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="22"/>
-      <c r="C68" s="24"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="22"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="22"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="22"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="22"/>
-      <c r="C72" s="24"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="22"/>
-      <c r="C73" s="24"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="22"/>
-      <c r="C74" s="24"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="22"/>
-      <c r="C75" s="24"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="24"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="24"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="24"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="24"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="24"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="24"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5899,13 +5913,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{003B00FC-0097-4066-89A8-00A9002F00DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00F600EE-0089-439D-B800-00B6005000A5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{002000A1-00B3-4418-AB2E-0004000500D4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00190095-0040-40AD-9CD4-001A00E80027}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5942,1674 +5956,1674 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="str" cm="1">
+      <c r="A2" s="26" t="str" cm="1">
         <f t="array" ref="A2:A7">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="25">
+      <c r="A6" s="26">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="25">
+      <c r="A7" s="26">
         <f/>
         <v>46147</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
-        <v>0.125</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26">
+      <c r="A8" s="26"/>
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="27"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25"/>
-      <c r="C28" s="28">
+      <c r="A28" s="26"/>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25"/>
-      <c r="C29" s="28">
+      <c r="A29" s="26"/>
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25"/>
-      <c r="C30" s="28">
+      <c r="A30" s="26"/>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25"/>
-      <c r="C31" s="28">
+      <c r="A31" s="26"/>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25"/>
-      <c r="C32" s="28">
+      <c r="A32" s="26"/>
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="C33" s="28">
+      <c r="A33" s="26"/>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25"/>
-      <c r="C34" s="28">
+      <c r="A34" s="26"/>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25"/>
-      <c r="C35" s="28">
+      <c r="A35" s="26"/>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25"/>
-      <c r="C36" s="28">
+      <c r="A36" s="26"/>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25"/>
-      <c r="C37" s="28">
+      <c r="A37" s="26"/>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25"/>
-      <c r="C38" s="28">
+      <c r="A38" s="26"/>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25"/>
-      <c r="C39" s="28">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29"/>
-      <c r="B42" s="26" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29"/>
-      <c r="B43" s="26" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="26" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29"/>
-      <c r="B45" s="26" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29"/>
-      <c r="B46" s="26" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30"/>
-      <c r="B47" s="26" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30"/>
-      <c r="B48" s="26" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30"/>
-      <c r="B49" s="26" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30"/>
-      <c r="B50" s="26" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30"/>
-      <c r="B51" s="26" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30"/>
-      <c r="B52" s="26" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30"/>
-      <c r="B53" s="26" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30"/>
-      <c r="B54" s="26" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30"/>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30"/>
-      <c r="B56" s="26" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30"/>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30"/>
-      <c r="B58" s="26" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30"/>
-      <c r="B59" s="26" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30"/>
-      <c r="B60" s="26" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30"/>
-      <c r="B61" s="26" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30"/>
-      <c r="B62" s="26" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30"/>
-      <c r="B63" s="26" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30"/>
-      <c r="B64" s="26" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30"/>
-      <c r="B65" s="26" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30"/>
-      <c r="B66" s="26" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30"/>
-      <c r="B67" s="26" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30"/>
-      <c r="B68" s="26" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30"/>
-      <c r="B69" s="26" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30"/>
-      <c r="B70" s="26" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30"/>
-      <c r="B71" s="26" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30"/>
-      <c r="B72" s="26" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30"/>
-      <c r="B73" s="26" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30"/>
-      <c r="B74" s="26" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30"/>
-      <c r="B75" s="26" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30"/>
-      <c r="B76" s="26" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30"/>
-      <c r="B77" s="26" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30"/>
-      <c r="B78" s="26" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30"/>
-      <c r="B79" s="26" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30"/>
-      <c r="B80" s="26" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30"/>
-      <c r="B81" s="26" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30"/>
-      <c r="B82" s="26" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30"/>
-      <c r="B83" s="26" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30"/>
-      <c r="B84" s="26" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30"/>
-      <c r="B85" s="26" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30"/>
-      <c r="B86" s="26" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30"/>
-      <c r="B87" s="26" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30"/>
-      <c r="B88" s="26" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30"/>
-      <c r="B89" s="26" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30"/>
-      <c r="B90" s="26" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30"/>
-      <c r="B91" s="26" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30"/>
-      <c r="B92" s="26" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30"/>
-      <c r="B93" s="26" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30"/>
-      <c r="B94" s="26" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30"/>
-      <c r="B95" s="26" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30"/>
-      <c r="B96" s="26" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30"/>
-      <c r="B97" s="26" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30"/>
-      <c r="B98" s="26" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30"/>
-      <c r="B99" s="26" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30"/>
-      <c r="B100" s="26" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30"/>
-      <c r="B101" s="26" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30"/>
-      <c r="B102" s="26" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30"/>
-      <c r="B103" s="26" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30"/>
-      <c r="B104" s="26" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30"/>
-      <c r="B105" s="26" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30"/>
-      <c r="B106" s="26" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30"/>
-      <c r="B107" s="26" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="30"/>
-      <c r="B108" s="26" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30"/>
-      <c r="B109" s="26" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30"/>
-      <c r="B110" s="26" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30"/>
-      <c r="B111" s="26" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="30"/>
-      <c r="B112" s="26" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30"/>
-      <c r="B113" s="26" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30"/>
-      <c r="B114" s="26" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7638,1266 +7652,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="33" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="B1" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="34" t="s">
+      <c r="F1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="J1" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="L1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="M1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="N1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="O1" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="R1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="31"/>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="31"/>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="31"/>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-    </row>
-    <row r="2" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="S1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="34">
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+      <c r="AO1" s="32"/>
+      <c r="AP1" s="32"/>
+      <c r="AQ1" s="32"/>
+      <c r="AR1" s="32"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="32"/>
+      <c r="AU1" s="32"/>
+      <c r="AV1" s="32"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="32"/>
+      <c r="AY1" s="32"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="32"/>
+      <c r="BB1" s="32"/>
+      <c r="BC1" s="32"/>
+    </row>
+    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35">
         <v>7</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="35">
         <v>4</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="35">
         <v>4</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="35">
         <v>7</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="35">
         <v>5</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="35">
         <v>7</v>
       </c>
-      <c r="I2" s="35">
-        <v>0</v>
-      </c>
-      <c r="J2" s="35">
-        <v>0</v>
-      </c>
-      <c r="K2" s="34">
+      <c r="I2" s="36">
+        <v>0</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0</v>
+      </c>
+      <c r="K2" s="35">
         <v>5</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="35">
         <v>4</v>
       </c>
-      <c r="M2" s="34">
+      <c r="M2" s="35">
         <v>7</v>
       </c>
-      <c r="N2" s="34">
+      <c r="N2" s="35">
         <v>4</v>
       </c>
-      <c r="O2" s="34">
+      <c r="O2" s="35">
         <v>5</v>
       </c>
-      <c r="P2" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="34">
+      <c r="P2" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="35">
         <v>4</v>
       </c>
-      <c r="R2" s="34">
+      <c r="R2" s="35">
         <v>7</v>
       </c>
-      <c r="S2" s="34">
+      <c r="S2" s="35">
         <v>5</v>
       </c>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="31"/>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="31"/>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="31"/>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-    </row>
-    <row r="3" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="38" t="s">
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
+      <c r="AS2" s="32"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="32"/>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="32"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+    </row>
+    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="39" t="str">
+      <c r="B3" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41" t="str">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41" t="str">
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="42" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-      <c r="AK3" s="31"/>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="31"/>
-      <c r="AN3" s="31"/>
-      <c r="AO3" s="31"/>
-      <c r="AP3" s="31"/>
-      <c r="AQ3" s="31"/>
-      <c r="AR3" s="31"/>
-      <c r="AS3" s="31"/>
-      <c r="AT3" s="31"/>
-      <c r="AU3" s="31"/>
-      <c r="AV3" s="31"/>
-      <c r="AW3" s="31"/>
-      <c r="AX3" s="31"/>
-      <c r="AY3" s="31"/>
-      <c r="AZ3" s="31"/>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="31"/>
-      <c r="BC3" s="31"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AQ3" s="32"/>
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AV3" s="32"/>
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BA3" s="32"/>
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="50"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="58"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="59"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="51"/>
-      <c r="B6" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="64"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="51"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="64"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="67" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="58"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="59"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="58"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="59"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="72"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="73"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="80"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="81"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="81" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="82" t="s">
+      <c r="A12" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="50"/>
+      <c r="B12" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="51"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="83"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="58"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="59"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="64"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="65"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="64"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="83"/>
-      <c r="B16" s="67" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="58"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="59"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="58"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="59"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="83"/>
-      <c r="B18" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="61"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="64"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="65"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="84"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="80"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76"/>
+      <c r="S19" s="81"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="82" t="s">
+      <c r="A20" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="50"/>
+      <c r="B20" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="51"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="51"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="58"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="59"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="51"/>
-      <c r="B22" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="64"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="65"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="51"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="64"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="65"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="51"/>
-      <c r="B24" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="S24" s="58"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="55"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="59"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="51"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="54"/>
-      <c r="S25" s="58"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="59"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="51"/>
-      <c r="B26" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="64"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="65"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="51"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="61"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="64"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="65"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="51"/>
-      <c r="B28" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="58"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="59"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="73"/>
-      <c r="B29" s="87"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="88"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="91"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="92"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="93" t="s">
+      <c r="A30" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
-      <c r="S30" s="97"/>
+      <c r="B30" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="98"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="64"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="65"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="98"/>
-      <c r="B32" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="54"/>
-      <c r="R32" s="54"/>
-      <c r="S32" s="58"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="59"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="98"/>
-      <c r="B33" s="65"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="58"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="59"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="98"/>
-      <c r="B34" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="64"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="65"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="65"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="62"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="64"/>
+      <c r="A35" s="99"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="65"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="98"/>
-      <c r="B36" s="67" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
-      <c r="Q36" s="54"/>
-      <c r="R36" s="54"/>
-      <c r="S36" s="58"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="59"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="98"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="58"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="59"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="98"/>
-      <c r="B38" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="61"/>
-      <c r="S38" s="64"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="65"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="98"/>
-      <c r="B39" s="65"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="61"/>
-      <c r="S39" s="64"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="65"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="98"/>
-      <c r="B40" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="56"/>
-      <c r="O40" s="54"/>
-      <c r="P40" s="54"/>
-      <c r="Q40" s="60"/>
-      <c r="R40" s="60"/>
-      <c r="S40" s="58"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="59"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="98"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="58"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="59"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="98"/>
-      <c r="B42" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="62"/>
-      <c r="N42" s="63"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="72"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="62"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="73"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="99"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="77"/>
-      <c r="N43" s="78"/>
-      <c r="O43" s="75"/>
-      <c r="P43" s="75"/>
-      <c r="Q43" s="75"/>
-      <c r="R43" s="75"/>
-      <c r="S43" s="80"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="81"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="44" t="s">
+      <c r="A44" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
-      <c r="S44" s="100"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="101"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="51"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="54"/>
-      <c r="L45" s="54"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="54"/>
-      <c r="R45" s="54"/>
-      <c r="S45" s="58"/>
-      <c r="V45" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="W45" s="60"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="56"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="59"/>
+      <c r="V45" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="51"/>
-      <c r="B46" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="62"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="62"/>
-      <c r="N46" s="63"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="61"/>
-      <c r="R46" s="61"/>
-      <c r="S46" s="72"/>
-      <c r="V46" s="101" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="W46" s="53"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="62"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="73"/>
+      <c r="V46" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="W46" s="54"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="73"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="79"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="75"/>
-      <c r="M47" s="77"/>
-      <c r="N47" s="78"/>
-      <c r="O47" s="75"/>
-      <c r="P47" s="75"/>
-      <c r="Q47" s="75"/>
-      <c r="R47" s="75"/>
-      <c r="S47" s="80"/>
-      <c r="V47" s="101" t="s">
-        <v>78</v>
-      </c>
-      <c r="W47" s="66"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="81"/>
+      <c r="V47" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="W47" s="67"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="104">
+      <c r="V54" s="105">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8905,7 +8919,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8913,7 +8927,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -8977,801 +8991,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="105"/>
+      <c r="B1" s="106"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="106" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="107" t="s">
+      <c r="B2" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="108" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="109" t="s">
+      <c r="C2" s="108" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="E2" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="110" t="s">
+      <c r="F2" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="110" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="110" t="s">
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="S2" s="111"/>
-      <c r="AD2" s="29"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111" t="s">
+        <v>88</v>
+      </c>
+      <c r="S2" s="112"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="115">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="116">
         <v>4</v>
       </c>
-      <c r="F3" s="116">
+      <c r="F3" s="117">
         <v>1</v>
       </c>
-      <c r="G3" s="117">
+      <c r="G3" s="118">
         <v>2</v>
       </c>
-      <c r="H3" s="117">
+      <c r="H3" s="118">
         <v>3</v>
       </c>
-      <c r="I3" s="115">
+      <c r="I3" s="116">
         <v>4</v>
       </c>
-      <c r="J3" s="116">
+      <c r="J3" s="117">
         <v>1</v>
       </c>
-      <c r="K3" s="117">
+      <c r="K3" s="118">
         <v>2</v>
       </c>
-      <c r="L3" s="117">
+      <c r="L3" s="118">
         <v>3</v>
       </c>
-      <c r="M3" s="115">
+      <c r="M3" s="116">
         <v>4</v>
       </c>
-      <c r="N3" s="116">
+      <c r="N3" s="117">
         <v>1</v>
       </c>
-      <c r="O3" s="117">
+      <c r="O3" s="118">
         <v>2</v>
       </c>
-      <c r="P3" s="117">
+      <c r="P3" s="118">
         <v>3</v>
       </c>
-      <c r="Q3" s="115">
+      <c r="Q3" s="116">
         <v>4</v>
       </c>
-      <c r="R3" s="116">
+      <c r="R3" s="117">
         <v>1</v>
       </c>
-      <c r="S3" s="118">
+      <c r="S3" s="119">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="119" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="107" t="s">
+      <c r="B4" s="120" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="125"/>
+      <c r="C4" s="108" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="119"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="131"/>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="133"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="119"/>
-      <c r="C6" s="134" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="135"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="139"/>
-      <c r="L6" s="139"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="140"/>
-      <c r="O6" s="139"/>
-      <c r="P6" s="139"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="140"/>
-      <c r="S6" s="141"/>
-      <c r="U6" s="142" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="135" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="142"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="141"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="142"/>
+      <c r="U6" s="143" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" s="143"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="119"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="128"/>
-      <c r="R7" s="132"/>
-      <c r="S7" s="133"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="119"/>
-      <c r="C8" s="134" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="135"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="141"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="135" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="136"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="141"/>
+      <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="119"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="132"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="133"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="134"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="119"/>
-      <c r="C10" s="134" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="135"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="136"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="141"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="136"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="142"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="143"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="148"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="147"/>
-      <c r="O11" s="149"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="146"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="150"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="148"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="151"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="106" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="107" t="s">
+      <c r="B12" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="120"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="124"/>
-      <c r="S12" s="125"/>
+      <c r="C12" s="108" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="125"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="119"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="133"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="134"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="119"/>
-      <c r="C14" s="134" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="153"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="140"/>
-      <c r="O14" s="139"/>
-      <c r="P14" s="139"/>
-      <c r="Q14" s="136"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="141"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="135" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="142"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="119"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="128"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="133"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="155"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="134"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="119"/>
-      <c r="C16" s="134" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="155"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="139"/>
-      <c r="L16" s="139"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="140"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="136"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="141"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="136"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="143"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="146"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="146"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="148"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="147"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="146"/>
-      <c r="R17" s="147"/>
-      <c r="S17" s="150"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="151"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="108" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="107" t="s">
+      <c r="B18" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="120"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="125"/>
+      <c r="C18" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="121"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="125"/>
+      <c r="S18" s="126"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="119"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="132"/>
-      <c r="O19" s="131"/>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="133"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="119"/>
-      <c r="C20" s="134" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="135"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="155"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="136"/>
-      <c r="R20" s="140"/>
-      <c r="S20" s="141"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="135" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="142"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="119"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="128"/>
-      <c r="N21" s="157"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="128"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="133"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="134"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="119"/>
-      <c r="C22" s="134" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="139"/>
-      <c r="P22" s="139"/>
-      <c r="Q22" s="136"/>
-      <c r="R22" s="140"/>
-      <c r="S22" s="141"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="141"/>
+      <c r="S22" s="142"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="143"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="147"/>
-      <c r="K23" s="149"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="147"/>
-      <c r="O23" s="149"/>
-      <c r="P23" s="149"/>
-      <c r="Q23" s="146"/>
-      <c r="R23" s="147"/>
-      <c r="S23" s="150"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="150"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="150"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="150"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="151"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="108" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="107" t="s">
+      <c r="B24" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="120"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="121"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="123"/>
-      <c r="L24" s="123"/>
-      <c r="M24" s="152"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="151"/>
-      <c r="P24" s="151"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="125"/>
+      <c r="C24" s="108" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="121"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="153"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="152"/>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="126"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="119"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="131"/>
-      <c r="L25" s="131"/>
-      <c r="M25" s="128"/>
-      <c r="N25" s="132"/>
-      <c r="O25" s="131"/>
-      <c r="P25" s="131"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="132"/>
-      <c r="S25" s="133"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="134"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="119"/>
-      <c r="C26" s="134" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="135"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="140"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="138"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="140"/>
-      <c r="S26" s="141"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="135" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="136"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="137"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="142"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="119"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="131"/>
-      <c r="L27" s="131"/>
-      <c r="M27" s="128"/>
-      <c r="N27" s="132"/>
-      <c r="O27" s="131"/>
-      <c r="P27" s="131"/>
-      <c r="Q27" s="128"/>
-      <c r="R27" s="132"/>
-      <c r="S27" s="133"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="133"/>
+      <c r="S27" s="134"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="119"/>
-      <c r="C28" s="134" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="140"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="139"/>
-      <c r="P28" s="138"/>
-      <c r="Q28" s="155"/>
-      <c r="R28" s="140"/>
-      <c r="S28" s="141"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="135" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="156"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="142"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="119"/>
-      <c r="C29" s="113"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="162"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="159"/>
-      <c r="N29" s="163"/>
-      <c r="O29" s="162"/>
-      <c r="P29" s="161"/>
-      <c r="Q29" s="159"/>
-      <c r="R29" s="160"/>
-      <c r="S29" s="164"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="163"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="163"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="163"/>
+      <c r="P29" s="162"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="165"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="165" t="s">
+      <c r="B30" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="166" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="120"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="168"/>
-      <c r="K30" s="168"/>
-      <c r="L30" s="169"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="168"/>
-      <c r="O30" s="169"/>
-      <c r="P30" s="168"/>
-      <c r="Q30" s="170"/>
-      <c r="R30" s="168"/>
-      <c r="S30" s="171"/>
+      <c r="C30" s="167" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="121"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="171"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="172"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="177"/>
-      <c r="N31" s="175"/>
-      <c r="O31" s="176"/>
-      <c r="P31" s="175"/>
-      <c r="Q31" s="177"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="133"/>
+      <c r="B31" s="173"/>
+      <c r="C31" s="174"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="177"/>
+      <c r="M31" s="178"/>
+      <c r="N31" s="176"/>
+      <c r="O31" s="177"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="178"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="134"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="172"/>
-      <c r="C32" s="173" t="s">
+      <c r="B32" s="173"/>
+      <c r="C32" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="135"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="180"/>
-      <c r="G32" s="180"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="182"/>
-      <c r="J32" s="180"/>
-      <c r="K32" s="180"/>
-      <c r="L32" s="181"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="181"/>
-      <c r="P32" s="180"/>
-      <c r="Q32" s="182"/>
-      <c r="R32" s="180"/>
-      <c r="S32" s="183"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="183"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="183"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="184"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="172"/>
-      <c r="C33" s="173"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="178"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="184"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="176"/>
-      <c r="M33" s="177"/>
-      <c r="N33" s="175"/>
-      <c r="O33" s="176"/>
-      <c r="P33" s="175"/>
-      <c r="Q33" s="177"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="133"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="174"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="176"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="177"/>
+      <c r="M33" s="178"/>
+      <c r="N33" s="176"/>
+      <c r="O33" s="177"/>
+      <c r="P33" s="176"/>
+      <c r="Q33" s="178"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="134"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="172"/>
-      <c r="C34" s="126" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" s="158"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="187"/>
-      <c r="G34" s="187"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="189"/>
-      <c r="J34" s="187"/>
-      <c r="K34" s="187"/>
-      <c r="L34" s="188"/>
-      <c r="M34" s="189"/>
-      <c r="N34" s="187"/>
-      <c r="O34" s="188"/>
-      <c r="P34" s="187"/>
-      <c r="Q34" s="189"/>
-      <c r="R34" s="187"/>
-      <c r="S34" s="190"/>
-      <c r="U34" s="191"/>
-      <c r="V34" s="192" t="s">
+      <c r="B34" s="173"/>
+      <c r="C34" s="127" t="s">
         <v>112</v>
       </c>
+      <c r="D34" s="159"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="188"/>
+      <c r="O34" s="189"/>
+      <c r="P34" s="188"/>
+      <c r="Q34" s="190"/>
+      <c r="R34" s="188"/>
+      <c r="S34" s="191"/>
+      <c r="U34" s="192"/>
+      <c r="V34" s="193" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="193"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="145"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="196"/>
-      <c r="K35" s="196"/>
-      <c r="L35" s="197"/>
-      <c r="M35" s="198"/>
-      <c r="N35" s="196"/>
-      <c r="O35" s="197"/>
-      <c r="P35" s="196"/>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="196"/>
-      <c r="S35" s="150"/>
-      <c r="U35" s="199"/>
-      <c r="V35" s="200" t="s">
-        <v>113</v>
+      <c r="B35" s="194"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="197"/>
+      <c r="Q35" s="199"/>
+      <c r="R35" s="197"/>
+      <c r="S35" s="151"/>
+      <c r="U35" s="200"/>
+      <c r="V35" s="201" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -1655,7 +1655,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="200">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1697,12 +1697,6 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -5233,7 +5227,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>7.5000000000000011e-002</v>
+        <v>7.1770334928229679e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5260,7 +5254,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.17999999999999999</v>
+        <v>0.17224880382775121</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5287,7 +5281,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.47500000000000003</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5364,7 +5358,7 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5415,7 +5409,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>33.333333333333329</v>
+        <v>34.833333333333329</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5446,7 +5440,7 @@
         <v>46146</v>
       </c>
       <c r="C13" s="6">
-        <v>0.10416666666666667</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>22</v>
@@ -5459,7 +5453,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>41.666666666666671</v>
+        <v>40.166666666666671</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5497,10 +5491,10 @@
       <c r="C16" s="6">
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5647,9 +5641,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5700,200 +5694,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="23"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="22"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="23"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="23"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="23"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="23"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="23"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="23"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="23"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="23"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="23"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="23"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="23"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="23"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="23"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="23"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="23"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="23"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="23"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="23"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="23"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="23"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="23"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="23"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="23"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="23"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="23"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="23"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="23"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="23"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="23"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="23"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="25"/>
+      <c r="C81" s="23"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5913,13 +5907,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00F600EE-0089-439D-B800-00B6005000A5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D600F9-002F-4649-905E-009D00C8003C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00190095-0040-40AD-9CD4-001A00E80027}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D800F6-0095-48BF-8C86-008500FF007E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5956,1674 +5950,1674 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
+      <c r="A2" s="24" t="str" cm="1">
         <f t="array" ref="A2:A7">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="24" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="24" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="24" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <f/>
         <v>46147</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.1388888888888889</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26"/>
-      <c r="C28" s="29">
+      <c r="A28" s="24"/>
+      <c r="C28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26"/>
-      <c r="C29" s="29">
+      <c r="A29" s="24"/>
+      <c r="C29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26"/>
-      <c r="C30" s="29">
+      <c r="A30" s="24"/>
+      <c r="C30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26"/>
-      <c r="C31" s="29">
+      <c r="A31" s="24"/>
+      <c r="C31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26"/>
-      <c r="C32" s="29">
+      <c r="A32" s="24"/>
+      <c r="C32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26"/>
-      <c r="C33" s="29">
+      <c r="A33" s="24"/>
+      <c r="C33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26"/>
-      <c r="C34" s="29">
+      <c r="A34" s="24"/>
+      <c r="C34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26"/>
-      <c r="C35" s="29">
+      <c r="A35" s="24"/>
+      <c r="C35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26"/>
-      <c r="C36" s="29">
+      <c r="A36" s="24"/>
+      <c r="C36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26"/>
-      <c r="C37" s="29">
+      <c r="A37" s="24"/>
+      <c r="C37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26"/>
-      <c r="C38" s="29">
+      <c r="A38" s="24"/>
+      <c r="C38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="24"/>
+      <c r="C39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="28"/>
+      <c r="B43" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="28"/>
+      <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="28"/>
+      <c r="B46" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="29"/>
+      <c r="B47" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="29"/>
+      <c r="B49" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="29"/>
+      <c r="B53" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="29"/>
+      <c r="B55" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="29"/>
+      <c r="B59" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="29"/>
+      <c r="B61" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="29"/>
+      <c r="B65" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="29"/>
+      <c r="B67" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="29"/>
+      <c r="B70" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="29"/>
+      <c r="B71" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="29"/>
+      <c r="B73" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="29"/>
+      <c r="B74" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="29"/>
+      <c r="B76" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="29"/>
+      <c r="B77" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="29"/>
+      <c r="B79" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="29"/>
+      <c r="B80" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="29"/>
+      <c r="B82" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="29"/>
+      <c r="B83" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="29"/>
+      <c r="B85" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="29"/>
+      <c r="B86" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="29"/>
+      <c r="B88" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="29"/>
+      <c r="B89" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="29"/>
+      <c r="B91" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="29"/>
+      <c r="B92" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="29"/>
+      <c r="B93" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="29"/>
+      <c r="B94" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="29"/>
+      <c r="B95" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="29"/>
+      <c r="B96" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="29"/>
+      <c r="B97" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="29"/>
+      <c r="B98" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="29"/>
+      <c r="B99" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="29"/>
+      <c r="B100" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="29"/>
+      <c r="B101" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="29"/>
+      <c r="B102" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="29"/>
+      <c r="B103" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="29"/>
+      <c r="B104" s="25" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="29"/>
+      <c r="B105" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="29"/>
+      <c r="B106" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="29"/>
+      <c r="B107" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="29"/>
+      <c r="B108" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="29"/>
+      <c r="B109" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="29"/>
+      <c r="B110" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="29"/>
+      <c r="B111" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="29"/>
+      <c r="B112" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="29"/>
+      <c r="B113" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="29"/>
+      <c r="B114" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="27"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="27"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="27"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="27"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="27"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="27"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="27"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="27"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="27"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="27"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="27"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="27"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="27"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="27"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="27"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="27"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="27"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="27"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="27"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="27"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="27"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="27"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="27"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="27"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="27"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="27"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="27"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="27"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="27"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="27"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="27"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="27"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="27"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="27"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="27"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="27"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="27"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="27"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="27"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7652,288 +7646,288 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="33" t="s">
+    <row r="1" s="30" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="N1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="O1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="P1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="Q1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-    </row>
-    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="30"/>
+      <c r="AT1" s="30"/>
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+    </row>
+    <row r="2" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33">
         <v>7</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="33">
         <v>4</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="33">
         <v>4</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="33">
         <v>7</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="33">
         <v>5</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="33">
         <v>7</v>
       </c>
-      <c r="I2" s="36">
-        <v>0</v>
-      </c>
-      <c r="J2" s="36">
-        <v>0</v>
-      </c>
-      <c r="K2" s="35">
+      <c r="I2" s="34">
+        <v>0</v>
+      </c>
+      <c r="J2" s="34">
+        <v>0</v>
+      </c>
+      <c r="K2" s="33">
         <v>5</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="33">
         <v>4</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="33">
         <v>7</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="33">
         <v>4</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="33">
         <v>5</v>
       </c>
-      <c r="P2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
+      <c r="P2" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="33">
         <v>4</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="33">
         <v>7</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="33">
         <v>5</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-    </row>
-    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+    </row>
+    <row r="3" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="40" t="str">
+      <c r="C3" s="38" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42" t="str">
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42" t="str">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="40" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="51"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="49"/>
       <c r="V4" t="s">
         <v>52</v>
       </c>
@@ -7942,972 +7936,972 @@
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="59"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="57"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="60" t="s">
+      <c r="A6" s="50"/>
+      <c r="B6" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="65"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="63"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="65"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="63"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="50"/>
+      <c r="B8" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="57"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="59"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="53"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="57"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="50"/>
+      <c r="B10" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="73"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="59"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="71"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="81"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="76"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
+      <c r="S11" s="79"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="49"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="59"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="57"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="70" t="s">
+      <c r="A14" s="82"/>
+      <c r="B14" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="65"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="63"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="65"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="63"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="68" t="s">
+      <c r="A16" s="82"/>
+      <c r="B16" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="57"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="59"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="57"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="70" t="s">
+      <c r="A18" s="82"/>
+      <c r="B18" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="65"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="63"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="81"/>
+      <c r="A19" s="83"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="79"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="51"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="49"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="59"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="57"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="70" t="s">
+      <c r="A22" s="50"/>
+      <c r="B22" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="65"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="63"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="65"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="63"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="68" t="s">
+      <c r="A24" s="50"/>
+      <c r="B24" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="59"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="57"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="57"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="70" t="s">
+      <c r="A26" s="50"/>
+      <c r="B26" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="65"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="63"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="65"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="63"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="68" t="s">
+      <c r="A28" s="50"/>
+      <c r="B28" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="59"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="57"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="92"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="78"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="88"/>
+      <c r="N29" s="89"/>
+      <c r="O29" s="87"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="90"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="93" t="s">
+      <c r="A30" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="98"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="93"/>
+      <c r="P30" s="93"/>
+      <c r="Q30" s="93"/>
+      <c r="R30" s="93"/>
+      <c r="S30" s="96"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="65"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="63"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="70" t="s">
+      <c r="A32" s="97"/>
+      <c r="B32" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="59"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="69"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="57"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="59"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="57"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="70" t="s">
+      <c r="A34" s="97"/>
+      <c r="B34" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="65"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="69"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="63"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="65"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="61"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="60"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="63"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="99"/>
-      <c r="B36" s="68" t="s">
+      <c r="A36" s="97"/>
+      <c r="B36" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="59"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="59"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="57"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="99"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="59"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="57"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="99"/>
-      <c r="B38" s="70" t="s">
+      <c r="A38" s="97"/>
+      <c r="B38" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="65"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="63"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="99"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="65"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="63"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="99"/>
-      <c r="B40" s="68" t="s">
+      <c r="A40" s="97"/>
+      <c r="B40" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="59"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="59"/>
+      <c r="R40" s="59"/>
+      <c r="S40" s="57"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="99"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="59"/>
+      <c r="A41" s="97"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="53"/>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="57"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="99"/>
-      <c r="B42" s="70" t="s">
+      <c r="A42" s="97"/>
+      <c r="B42" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="63"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="73"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="61"/>
+      <c r="N42" s="62"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="71"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="100"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="81"/>
+      <c r="A43" s="98"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="74"/>
+      <c r="M43" s="76"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="74"/>
+      <c r="P43" s="74"/>
+      <c r="Q43" s="74"/>
+      <c r="R43" s="74"/>
+      <c r="S43" s="79"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="101"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="45"/>
+      <c r="P44" s="45"/>
+      <c r="Q44" s="45"/>
+      <c r="R44" s="45"/>
+      <c r="S44" s="99"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="59"/>
-      <c r="V45" s="102" t="s">
+      <c r="A45" s="50"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="53"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="57"/>
+      <c r="V45" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="W45" s="61"/>
+      <c r="W45" s="59"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="103" t="s">
+      <c r="A46" s="50"/>
+      <c r="B46" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="73"/>
-      <c r="V46" s="102" t="s">
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="62"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="71"/>
+      <c r="V46" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="W46" s="54"/>
+      <c r="W46" s="52"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="74"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="81"/>
-      <c r="V47" s="102" t="s">
+      <c r="A47" s="72"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="78"/>
+      <c r="J47" s="78"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="76"/>
+      <c r="N47" s="77"/>
+      <c r="O47" s="74"/>
+      <c r="P47" s="74"/>
+      <c r="Q47" s="74"/>
+      <c r="R47" s="74"/>
+      <c r="S47" s="79"/>
+      <c r="V47" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="W47" s="67"/>
+      <c r="W47" s="65"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="105">
+      <c r="V54" s="103">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
@@ -8991,94 +8985,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="106"/>
+      <c r="B1" s="104"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="F2" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="111" t="s">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="111" t="s">
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="111" t="s">
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="AD2" s="30"/>
+      <c r="S2" s="110"/>
+      <c r="AD2" s="28"/>
     </row>
     <row r="3">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="116">
+      <c r="E3" s="114">
         <v>4</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="115">
         <v>1</v>
       </c>
-      <c r="G3" s="118">
+      <c r="G3" s="116">
         <v>2</v>
       </c>
-      <c r="H3" s="118">
+      <c r="H3" s="116">
         <v>3</v>
       </c>
-      <c r="I3" s="116">
+      <c r="I3" s="114">
         <v>4</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="115">
         <v>1</v>
       </c>
-      <c r="K3" s="118">
+      <c r="K3" s="116">
         <v>2</v>
       </c>
-      <c r="L3" s="118">
+      <c r="L3" s="116">
         <v>3</v>
       </c>
-      <c r="M3" s="116">
+      <c r="M3" s="114">
         <v>4</v>
       </c>
-      <c r="N3" s="117">
+      <c r="N3" s="115">
         <v>1</v>
       </c>
-      <c r="O3" s="118">
+      <c r="O3" s="116">
         <v>2</v>
       </c>
-      <c r="P3" s="118">
+      <c r="P3" s="116">
         <v>3</v>
       </c>
-      <c r="Q3" s="116">
+      <c r="Q3" s="114">
         <v>4</v>
       </c>
-      <c r="R3" s="117">
+      <c r="R3" s="115">
         <v>1</v>
       </c>
-      <c r="S3" s="119">
+      <c r="S3" s="117">
         <v>2</v>
       </c>
       <c r="U3" t="s">
@@ -9086,705 +9080,705 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="124"/>
       <c r="U4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="131"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="131"/>
+      <c r="O5" s="130"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="131"/>
+      <c r="S5" s="132"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="135" t="s">
+      <c r="B6" s="118"/>
+      <c r="C6" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="142"/>
-      <c r="U6" s="143" t="s">
+      <c r="D6" s="134"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="139"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="140"/>
+      <c r="U6" s="141" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="143"/>
+      <c r="V6" s="141"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="134"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="132"/>
       <c r="U7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="135" t="s">
+      <c r="B8" s="118"/>
+      <c r="C8" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="142"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="140"/>
       <c r="U8" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="134"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="132"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="135" t="s">
+      <c r="B10" s="118"/>
+      <c r="C10" s="133" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="138"/>
+      <c r="P10" s="138"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="140"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="151"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="148"/>
+      <c r="L11" s="148"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="148"/>
+      <c r="P11" s="148"/>
+      <c r="Q11" s="145"/>
+      <c r="R11" s="146"/>
+      <c r="S11" s="149"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="108" t="s">
+      <c r="C12" s="106" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="123"/>
+      <c r="S12" s="124"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="134"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="131"/>
+      <c r="S13" s="132"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="135" t="s">
+      <c r="B14" s="118"/>
+      <c r="C14" s="133" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="139"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="140"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="134"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="130"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="132"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="133" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="138"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="140"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="151"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="155"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="148"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="146"/>
+      <c r="O17" s="148"/>
+      <c r="P17" s="148"/>
+      <c r="Q17" s="145"/>
+      <c r="R17" s="146"/>
+      <c r="S17" s="149"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="109" t="s">
+      <c r="B18" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="123"/>
+      <c r="S18" s="124"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="129"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="131"/>
+      <c r="O19" s="130"/>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="131"/>
+      <c r="S19" s="132"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="135" t="s">
+      <c r="B20" s="118"/>
+      <c r="C20" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="154"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="138"/>
+      <c r="Q20" s="135"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="140"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="134"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="130"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="156"/>
+      <c r="O21" s="130"/>
+      <c r="P21" s="130"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="132"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="135" t="s">
+      <c r="B22" s="118"/>
+      <c r="C22" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="141"/>
-      <c r="S22" s="142"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="139"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="138"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="140"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="151"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="148"/>
+      <c r="L23" s="148"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="148"/>
+      <c r="P23" s="148"/>
+      <c r="Q23" s="145"/>
+      <c r="R23" s="146"/>
+      <c r="S23" s="149"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="109" t="s">
+      <c r="B24" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="126"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="151"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="150"/>
+      <c r="P24" s="150"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="123"/>
+      <c r="S24" s="124"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="133"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="134"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="130"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="130"/>
+      <c r="L25" s="130"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="131"/>
+      <c r="O25" s="130"/>
+      <c r="P25" s="130"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="132"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="135" t="s">
+      <c r="B26" s="118"/>
+      <c r="C26" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="141"/>
-      <c r="S26" s="142"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="137"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="135"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="140"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="134"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="127"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="130"/>
+      <c r="P27" s="130"/>
+      <c r="Q27" s="127"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="132"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="135" t="s">
+      <c r="B28" s="118"/>
+      <c r="C28" s="133" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="156"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="139"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="154"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="140"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="162"/>
-      <c r="Q29" s="160"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="165"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="158"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="161"/>
+      <c r="P29" s="160"/>
+      <c r="Q29" s="158"/>
+      <c r="R29" s="159"/>
+      <c r="S29" s="163"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="166" t="s">
+      <c r="B30" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="167" t="s">
+      <c r="C30" s="165" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="172"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="168"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="169"/>
+      <c r="R30" s="167"/>
+      <c r="S30" s="170"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="177"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="134"/>
+      <c r="B31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="177"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="174"/>
+      <c r="Q31" s="176"/>
+      <c r="R31" s="174"/>
+      <c r="S31" s="132"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174" t="s">
+      <c r="B32" s="171"/>
+      <c r="C32" s="172" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="183"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="183"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="184"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="179"/>
+      <c r="K32" s="179"/>
+      <c r="L32" s="180"/>
+      <c r="M32" s="181"/>
+      <c r="N32" s="179"/>
+      <c r="O32" s="180"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="181"/>
+      <c r="R32" s="179"/>
+      <c r="S32" s="182"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="177"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="178"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="134"/>
+      <c r="B33" s="171"/>
+      <c r="C33" s="172"/>
+      <c r="D33" s="126"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="177"/>
+      <c r="G33" s="174"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="184"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="177"/>
+      <c r="L33" s="175"/>
+      <c r="M33" s="176"/>
+      <c r="N33" s="174"/>
+      <c r="O33" s="175"/>
+      <c r="P33" s="174"/>
+      <c r="Q33" s="176"/>
+      <c r="R33" s="174"/>
+      <c r="S33" s="132"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="173"/>
-      <c r="C34" s="127" t="s">
+      <c r="B34" s="171"/>
+      <c r="C34" s="125" t="s">
         <v>112</v>
       </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="191"/>
-      <c r="U34" s="192"/>
-      <c r="V34" s="193" t="s">
+      <c r="D34" s="157"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="187"/>
+      <c r="M34" s="188"/>
+      <c r="N34" s="186"/>
+      <c r="O34" s="187"/>
+      <c r="P34" s="186"/>
+      <c r="Q34" s="188"/>
+      <c r="R34" s="186"/>
+      <c r="S34" s="189"/>
+      <c r="U34" s="190"/>
+      <c r="V34" s="191" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="194"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="199"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="151"/>
-      <c r="U35" s="200"/>
-      <c r="V35" s="201" t="s">
+      <c r="B35" s="192"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="144"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="195"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="197"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="196"/>
+      <c r="M35" s="197"/>
+      <c r="N35" s="195"/>
+      <c r="O35" s="196"/>
+      <c r="P35" s="195"/>
+      <c r="Q35" s="197"/>
+      <c r="R35" s="195"/>
+      <c r="S35" s="149"/>
+      <c r="U35" s="198"/>
+      <c r="V35" s="199" t="s">
         <v>114</v>
       </c>
     </row>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>date</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ajout de toutes les documentation + prix des composants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation technique du schéma du prototype</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1655,7 +1658,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="202">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1697,6 +1700,12 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -2897,6 +2906,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5/5/2026</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5/6/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4629,8 +4641,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E16">
-  <autoFilter ref="B2:E16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E17">
+  <autoFilter ref="B2:E17"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5227,7 +5239,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>7.1770334928229679e-002</v>
+        <v>6.8807339449541288e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5254,7 +5266,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.17224880382775121</v>
+        <v>0.16513761467889909</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5277,11 +5289,11 @@
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>15.833333333333332</v>
+        <v>17.333333333333332</v>
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.45454545454545459</v>
+        <v>0.47706422018348627</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5409,7 +5421,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>34.833333333333329</v>
+        <v>36.333333333333329</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5453,7 +5465,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>40.166666666666671</v>
+        <v>38.666666666666671</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5499,10 +5511,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
+      <c r="B17" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C17" s="6">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" ht="28.5">
       <c r="B18" s="5"/>
@@ -5641,9 +5661,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="22"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5694,200 +5714,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="21"/>
-      <c r="C49" s="22"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="21"/>
-      <c r="C50" s="22"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="21"/>
-      <c r="C51" s="22"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="21"/>
-      <c r="C52" s="22"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="21"/>
-      <c r="C53" s="22"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="21"/>
-      <c r="C54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="21"/>
-      <c r="C55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="25"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="21"/>
-      <c r="C56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="21"/>
-      <c r="C57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="21"/>
-      <c r="C58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="21"/>
-      <c r="C59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="21"/>
-      <c r="C60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="21"/>
-      <c r="C61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="21"/>
-      <c r="C62" s="23"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="21"/>
-      <c r="C63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="21"/>
-      <c r="C64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="21"/>
-      <c r="C65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="21"/>
-      <c r="C66" s="23"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="21"/>
-      <c r="C67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="21"/>
-      <c r="C68" s="23"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="21"/>
-      <c r="C69" s="23"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="21"/>
-      <c r="C70" s="23"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="21"/>
-      <c r="C71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="21"/>
-      <c r="C72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="21"/>
-      <c r="C73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="21"/>
-      <c r="C74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="21"/>
-      <c r="C75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="23"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5907,13 +5927,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00D600F9-002F-4649-905E-009D00C8003C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C700DE-002A-4E9A-9B82-00E4007C0078}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00D800F6-0095-48BF-8C86-008500FF007E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00270054-00FC-4FD7-86C2-006B000D006C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5950,1674 +5970,1677 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str" cm="1">
-        <f t="array" ref="A2:A7">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="26" t="str" cm="1">
+        <f t="array" ref="A2:A8">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24">
+      <c r="A6" s="26">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24">
+      <c r="A7" s="26">
         <f/>
         <v>46147</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.1388888888888889</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25">
+      <c r="A8" s="26">
+        <f/>
+        <v>46148</v>
+      </c>
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24"/>
-      <c r="C28" s="27">
+      <c r="A28" s="26"/>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="C29" s="27">
+      <c r="A29" s="26"/>
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24"/>
-      <c r="C30" s="27">
+      <c r="A30" s="26"/>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24"/>
-      <c r="C31" s="27">
+      <c r="A31" s="26"/>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24"/>
-      <c r="C32" s="27">
+      <c r="A32" s="26"/>
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24"/>
-      <c r="C33" s="27">
+      <c r="A33" s="26"/>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24"/>
-      <c r="C34" s="27">
+      <c r="A34" s="26"/>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24"/>
-      <c r="C35" s="27">
+      <c r="A35" s="26"/>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24"/>
-      <c r="C36" s="27">
+      <c r="A36" s="26"/>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24"/>
-      <c r="C37" s="27">
+      <c r="A37" s="26"/>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24"/>
-      <c r="C38" s="27">
+      <c r="A38" s="26"/>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="27"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="27"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="27"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7646,1266 +7669,1266 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="32" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="B1" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="I1" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="K1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="L1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="M1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="N1" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="O1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="Q1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="33" t="s">
+      <c r="R1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="35"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
-      <c r="AQ1" s="30"/>
-      <c r="AR1" s="30"/>
-      <c r="AS1" s="30"/>
-      <c r="AT1" s="30"/>
-      <c r="AU1" s="30"/>
-      <c r="AV1" s="30"/>
-      <c r="AW1" s="30"/>
-      <c r="AX1" s="30"/>
-      <c r="AY1" s="30"/>
-      <c r="AZ1" s="30"/>
-      <c r="BA1" s="30"/>
-      <c r="BB1" s="30"/>
-      <c r="BC1" s="30"/>
-    </row>
-    <row r="2" s="30" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="S1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33">
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+      <c r="AO1" s="32"/>
+      <c r="AP1" s="32"/>
+      <c r="AQ1" s="32"/>
+      <c r="AR1" s="32"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="32"/>
+      <c r="AU1" s="32"/>
+      <c r="AV1" s="32"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="32"/>
+      <c r="AY1" s="32"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="32"/>
+      <c r="BB1" s="32"/>
+      <c r="BC1" s="32"/>
+    </row>
+    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35">
         <v>7</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="35">
         <v>4</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="35">
         <v>4</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="35">
         <v>7</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="35">
         <v>5</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="35">
         <v>7</v>
       </c>
-      <c r="I2" s="34">
-        <v>0</v>
-      </c>
-      <c r="J2" s="34">
-        <v>0</v>
-      </c>
-      <c r="K2" s="33">
+      <c r="I2" s="36">
+        <v>0</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0</v>
+      </c>
+      <c r="K2" s="35">
         <v>5</v>
       </c>
-      <c r="L2" s="33">
+      <c r="L2" s="35">
         <v>4</v>
       </c>
-      <c r="M2" s="33">
+      <c r="M2" s="35">
         <v>7</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="35">
         <v>4</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="35">
         <v>5</v>
       </c>
-      <c r="P2" s="33">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="33">
+      <c r="P2" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="35">
         <v>4</v>
       </c>
-      <c r="R2" s="33">
+      <c r="R2" s="35">
         <v>7</v>
       </c>
-      <c r="S2" s="33">
+      <c r="S2" s="35">
         <v>5</v>
       </c>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-      <c r="AY2" s="30"/>
-      <c r="AZ2" s="30"/>
-      <c r="BA2" s="30"/>
-      <c r="BB2" s="30"/>
-      <c r="BC2" s="30"/>
-    </row>
-    <row r="3" s="30" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
+      <c r="AS2" s="32"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="32"/>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="32"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+    </row>
+    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="38" t="str">
+      <c r="B3" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40" t="str">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="40" t="str">
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="42" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="30"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="30"/>
-      <c r="AO3" s="30"/>
-      <c r="AP3" s="30"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="30"/>
-      <c r="AS3" s="30"/>
-      <c r="AT3" s="30"/>
-      <c r="AU3" s="30"/>
-      <c r="AV3" s="30"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="30"/>
-      <c r="AY3" s="30"/>
-      <c r="AZ3" s="30"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="30"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="32"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AQ3" s="32"/>
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AV3" s="32"/>
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BA3" s="32"/>
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="49"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="57"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="59"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="50"/>
-      <c r="B6" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="63"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="50"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="63"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="66" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="57"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="59"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="57"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="59"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="71"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="73"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="76"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="79"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="81"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="81" t="s">
+      <c r="A12" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="49"/>
+      <c r="B12" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="51"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="57"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="59"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="63"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="65"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="82"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="63"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="65"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="57"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="59"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="82"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="57"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="59"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="63"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="65"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="83"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="79"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76"/>
+      <c r="S19" s="81"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="81" t="s">
+      <c r="A20" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="49"/>
+      <c r="B20" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="51"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="50"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="57"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="59"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="50"/>
-      <c r="B22" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="63"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="65"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="63"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="65"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="50"/>
-      <c r="B24" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="57"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="55"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="59"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="57"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="59"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="50"/>
-      <c r="B26" s="68" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="63"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="65"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="50"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="63"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="65"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="57"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="59"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="72"/>
-      <c r="B29" s="86"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="87"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="90"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="92"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="91" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="92" t="s">
+      <c r="A30" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="93"/>
-      <c r="P30" s="93"/>
-      <c r="Q30" s="93"/>
-      <c r="R30" s="93"/>
-      <c r="S30" s="96"/>
+      <c r="B30" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="98"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="97"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="60"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="63"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="65"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="97"/>
-      <c r="B32" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="57"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="59"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="97"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="57"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="59"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="97"/>
-      <c r="B34" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="60"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="60"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="60"/>
-      <c r="S34" s="63"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="65"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="97"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="60"/>
-      <c r="P35" s="60"/>
-      <c r="Q35" s="60"/>
-      <c r="R35" s="60"/>
-      <c r="S35" s="63"/>
+      <c r="A35" s="99"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="65"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="97"/>
-      <c r="B36" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="54"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="57"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="59"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="97"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="57"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="59"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="97"/>
-      <c r="B38" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="59"/>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="60"/>
-      <c r="S38" s="63"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="65"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="97"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="62"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="63"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="65"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="97"/>
-      <c r="B40" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="54"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="57"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="56"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="59"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="97"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="57"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="59"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="97"/>
-      <c r="B42" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="62"/>
-      <c r="O42" s="60"/>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="71"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="62"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="73"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="98"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="74"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="76"/>
-      <c r="N43" s="77"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="79"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="81"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="43" t="s">
+      <c r="A44" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="45"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="99"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="47"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="101"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="50"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="54"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="57"/>
-      <c r="V45" s="100" t="s">
-        <v>76</v>
-      </c>
-      <c r="W45" s="59"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="56"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="59"/>
+      <c r="V45" s="102" t="s">
+        <v>77</v>
+      </c>
+      <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="50"/>
-      <c r="B46" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="62"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="60"/>
-      <c r="M46" s="61"/>
-      <c r="N46" s="62"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="60"/>
-      <c r="R46" s="60"/>
-      <c r="S46" s="71"/>
-      <c r="V46" s="100" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="W46" s="52"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="62"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="73"/>
+      <c r="V46" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="W46" s="54"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="72"/>
-      <c r="B47" s="102"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="74"/>
-      <c r="L47" s="74"/>
-      <c r="M47" s="76"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="74"/>
-      <c r="Q47" s="74"/>
-      <c r="R47" s="74"/>
-      <c r="S47" s="79"/>
-      <c r="V47" s="100" t="s">
-        <v>79</v>
-      </c>
-      <c r="W47" s="65"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="81"/>
+      <c r="V47" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="W47" s="67"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="103">
+      <c r="V54" s="105">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8913,7 +8936,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8921,7 +8944,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -8985,801 +9008,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="104"/>
+      <c r="B1" s="106"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="105" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="106" t="s">
+      <c r="B2" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="107" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="108" t="s">
+      <c r="C2" s="108" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="109" t="s">
+      <c r="E2" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="109" t="s">
+      <c r="F2" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="109" t="s">
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="109" t="s">
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="S2" s="110"/>
-      <c r="AD2" s="28"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111" t="s">
+        <v>89</v>
+      </c>
+      <c r="S2" s="112"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
-      <c r="B3" s="111"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="113" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="114">
+      <c r="B3" s="113"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="115" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="116">
         <v>4</v>
       </c>
-      <c r="F3" s="115">
+      <c r="F3" s="117">
         <v>1</v>
       </c>
-      <c r="G3" s="116">
+      <c r="G3" s="118">
         <v>2</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="118">
         <v>3</v>
       </c>
-      <c r="I3" s="114">
+      <c r="I3" s="116">
         <v>4</v>
       </c>
-      <c r="J3" s="115">
+      <c r="J3" s="117">
         <v>1</v>
       </c>
-      <c r="K3" s="116">
+      <c r="K3" s="118">
         <v>2</v>
       </c>
-      <c r="L3" s="116">
+      <c r="L3" s="118">
         <v>3</v>
       </c>
-      <c r="M3" s="114">
+      <c r="M3" s="116">
         <v>4</v>
       </c>
-      <c r="N3" s="115">
+      <c r="N3" s="117">
         <v>1</v>
       </c>
-      <c r="O3" s="116">
+      <c r="O3" s="118">
         <v>2</v>
       </c>
-      <c r="P3" s="116">
+      <c r="P3" s="118">
         <v>3</v>
       </c>
-      <c r="Q3" s="114">
+      <c r="Q3" s="116">
         <v>4</v>
       </c>
-      <c r="R3" s="115">
+      <c r="R3" s="117">
         <v>1</v>
       </c>
-      <c r="S3" s="117">
+      <c r="S3" s="119">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="118" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="106" t="s">
+      <c r="B4" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="124"/>
+      <c r="C4" s="108" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="131"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="132"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="118"/>
-      <c r="C6" s="133" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="134"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="139"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="139"/>
-      <c r="S6" s="140"/>
-      <c r="U6" s="141" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="141"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="141"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="142"/>
+      <c r="U6" s="143" t="s">
+        <v>95</v>
+      </c>
+      <c r="V6" s="143"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="118"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="132"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="118"/>
-      <c r="C8" s="133" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="134"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="140"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="136"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="141"/>
+      <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="118"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="131"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="132"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="134"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="118"/>
-      <c r="C10" s="133" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="134"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
-      <c r="M10" s="135"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="140"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="136"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="142"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="142"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="148"/>
-      <c r="L11" s="148"/>
-      <c r="M11" s="145"/>
-      <c r="N11" s="146"/>
-      <c r="O11" s="148"/>
-      <c r="P11" s="148"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="146"/>
-      <c r="S11" s="149"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="148"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="151"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="105" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="106" t="s">
+      <c r="B12" s="107" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="119"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="123"/>
-      <c r="S12" s="124"/>
+      <c r="C12" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="125"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="118"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="131"/>
-      <c r="S13" s="132"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="134"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="118"/>
-      <c r="C14" s="133" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="152"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="139"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="139"/>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="135"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="140"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="154"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="142"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="118"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="132"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="155"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="134"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="118"/>
-      <c r="C16" s="133" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="139"/>
-      <c r="O16" s="138"/>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="140"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="135" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="136"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="141"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="141"/>
+      <c r="S16" s="142"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="142"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="155"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="148"/>
-      <c r="M17" s="145"/>
-      <c r="N17" s="146"/>
-      <c r="O17" s="148"/>
-      <c r="P17" s="148"/>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="146"/>
-      <c r="S17" s="149"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="151"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="107" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="106" t="s">
+      <c r="B18" s="109" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="119"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="123"/>
-      <c r="S18" s="124"/>
+      <c r="C18" s="108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="121"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="125"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="125"/>
+      <c r="S18" s="126"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="118"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="131"/>
-      <c r="O19" s="130"/>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="127"/>
-      <c r="R19" s="131"/>
-      <c r="S19" s="132"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="118"/>
-      <c r="C20" s="133" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="154"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="138"/>
-      <c r="P20" s="138"/>
-      <c r="Q20" s="135"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="140"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="141"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="142"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="118"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="130"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="156"/>
-      <c r="O21" s="130"/>
-      <c r="P21" s="130"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="132"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="134"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="118"/>
-      <c r="C22" s="133" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="139"/>
-      <c r="O22" s="138"/>
-      <c r="P22" s="138"/>
-      <c r="Q22" s="135"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="140"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="135" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="141"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="141"/>
+      <c r="S22" s="142"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="142"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="148"/>
-      <c r="L23" s="148"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="146"/>
-      <c r="O23" s="148"/>
-      <c r="P23" s="148"/>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="146"/>
-      <c r="S23" s="149"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="150"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="150"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="148"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="150"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="151"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="107" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="106" t="s">
+      <c r="B24" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="120"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="151"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="150"/>
-      <c r="P24" s="150"/>
-      <c r="Q24" s="120"/>
-      <c r="R24" s="123"/>
-      <c r="S24" s="124"/>
+      <c r="C24" s="108" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="121"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="153"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="152"/>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="126"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="118"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="130"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="130"/>
-      <c r="L25" s="130"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="131"/>
-      <c r="O25" s="130"/>
-      <c r="P25" s="130"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="131"/>
-      <c r="S25" s="132"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="132"/>
+      <c r="M25" s="129"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="134"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="118"/>
-      <c r="C26" s="133" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="139"/>
-      <c r="O26" s="137"/>
-      <c r="P26" s="137"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="140"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="135" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="136"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="137"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="142"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="118"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="131"/>
-      <c r="O27" s="130"/>
-      <c r="P27" s="130"/>
-      <c r="Q27" s="127"/>
-      <c r="R27" s="131"/>
-      <c r="S27" s="132"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="133"/>
+      <c r="S27" s="134"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="118"/>
-      <c r="C28" s="133" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="139"/>
-      <c r="O28" s="138"/>
-      <c r="P28" s="137"/>
-      <c r="Q28" s="154"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="140"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="135" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="156"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="142"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="118"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="159"/>
-      <c r="K29" s="160"/>
-      <c r="L29" s="161"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="162"/>
-      <c r="O29" s="161"/>
-      <c r="P29" s="160"/>
-      <c r="Q29" s="158"/>
-      <c r="R29" s="159"/>
-      <c r="S29" s="163"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="163"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="163"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="163"/>
+      <c r="P29" s="162"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="165"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="165" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="119"/>
-      <c r="E30" s="166"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="169"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="167"/>
-      <c r="L30" s="168"/>
-      <c r="M30" s="169"/>
-      <c r="N30" s="167"/>
-      <c r="O30" s="168"/>
-      <c r="P30" s="167"/>
-      <c r="Q30" s="169"/>
-      <c r="R30" s="167"/>
-      <c r="S30" s="170"/>
+      <c r="C30" s="167" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="121"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="171"/>
+      <c r="R30" s="169"/>
+      <c r="S30" s="172"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="171"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="177"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="175"/>
-      <c r="P31" s="174"/>
-      <c r="Q31" s="176"/>
-      <c r="R31" s="174"/>
-      <c r="S31" s="132"/>
+      <c r="B31" s="173"/>
+      <c r="C31" s="174"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="177"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="177"/>
+      <c r="M31" s="178"/>
+      <c r="N31" s="176"/>
+      <c r="O31" s="177"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="178"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="134"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="171"/>
-      <c r="C32" s="172" t="s">
+      <c r="B32" s="173"/>
+      <c r="C32" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="134"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="179"/>
-      <c r="K32" s="179"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="181"/>
-      <c r="N32" s="179"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="181"/>
-      <c r="R32" s="179"/>
-      <c r="S32" s="182"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="183"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="183"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="184"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="172"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="173"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="174"/>
-      <c r="H33" s="183"/>
-      <c r="I33" s="184"/>
-      <c r="J33" s="174"/>
-      <c r="K33" s="177"/>
-      <c r="L33" s="175"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="174"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="174"/>
-      <c r="Q33" s="176"/>
-      <c r="R33" s="174"/>
-      <c r="S33" s="132"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="174"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="185"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="176"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="177"/>
+      <c r="M33" s="178"/>
+      <c r="N33" s="176"/>
+      <c r="O33" s="177"/>
+      <c r="P33" s="176"/>
+      <c r="Q33" s="178"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="134"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="171"/>
-      <c r="C34" s="125" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="157"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="187"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="186"/>
-      <c r="K34" s="186"/>
-      <c r="L34" s="187"/>
-      <c r="M34" s="188"/>
-      <c r="N34" s="186"/>
-      <c r="O34" s="187"/>
-      <c r="P34" s="186"/>
-      <c r="Q34" s="188"/>
-      <c r="R34" s="186"/>
-      <c r="S34" s="189"/>
-      <c r="U34" s="190"/>
-      <c r="V34" s="191" t="s">
+      <c r="B34" s="173"/>
+      <c r="C34" s="127" t="s">
         <v>113</v>
       </c>
+      <c r="D34" s="159"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="188"/>
+      <c r="O34" s="189"/>
+      <c r="P34" s="188"/>
+      <c r="Q34" s="190"/>
+      <c r="R34" s="188"/>
+      <c r="S34" s="191"/>
+      <c r="U34" s="192"/>
+      <c r="V34" s="193" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="192"/>
-      <c r="C35" s="193"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="196"/>
-      <c r="I35" s="197"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="196"/>
-      <c r="M35" s="197"/>
-      <c r="N35" s="195"/>
-      <c r="O35" s="196"/>
-      <c r="P35" s="195"/>
-      <c r="Q35" s="197"/>
-      <c r="R35" s="195"/>
-      <c r="S35" s="149"/>
-      <c r="U35" s="198"/>
-      <c r="V35" s="199" t="s">
-        <v>114</v>
+      <c r="B35" s="194"/>
+      <c r="C35" s="195"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="197"/>
+      <c r="Q35" s="199"/>
+      <c r="R35" s="197"/>
+      <c r="S35" s="151"/>
+      <c r="U35" s="200"/>
+      <c r="V35" s="201" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>date</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation technique du schéma du prototype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placement des composant, routage sur le PCB du prototype</t>
   </si>
   <si>
     <t>Phases</t>
@@ -4641,8 +4644,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E17">
-  <autoFilter ref="B2:E17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E18">
+  <autoFilter ref="B2:E18"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5239,7 +5242,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>6.8807339449541288e-002</v>
+        <v>0.059055118110236227</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5266,7 +5269,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.16513761467889909</v>
+        <v>0.14173228346456693</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5276,7 +5279,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
@@ -5293,7 +5296,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.47706422018348627</v>
+        <v>0.40944881889763779</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5303,7 +5306,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5370,7 +5373,7 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5381,7 +5384,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5408,7 +5411,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>6</v>
@@ -5421,7 +5424,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>36.333333333333329</v>
+        <v>42.333333333333329</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5435,7 +5438,7 @@
         <v>46146</v>
       </c>
       <c r="C12" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>22</v>
@@ -5465,7 +5468,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>38.666666666666671</v>
+        <v>32.666666666666671</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5473,7 +5476,7 @@
         <v>46146</v>
       </c>
       <c r="C14" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>22</v>
@@ -5501,7 +5504,7 @@
         <v>46147</v>
       </c>
       <c r="C16" s="6">
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>6</v>
@@ -5515,20 +5518,28 @@
         <v>46148</v>
       </c>
       <c r="C17" s="6">
-        <v>6.25e-002</v>
-      </c>
-      <c r="D17" s="18" t="s">
+        <v>0.0625</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" ht="28.5">
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="5">
+        <v>46148</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="5"/>
@@ -5927,13 +5938,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00C700DE-002A-4E9A-9B82-00E4007C0078}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C10075-003B-48F6-8BAC-00D200EC006B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00270054-00FC-4FD7-86C2-006B000D006C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FE00D1-00C8-49B3-B467-0027004200CB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6042,7 +6053,7 @@
       </c>
       <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>6.25e-002</v>
+        <v>0.3125</v>
       </c>
       <c r="C8"/>
     </row>
@@ -7671,10 +7682,10 @@
   <sheetData>
     <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="A1" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="35" t="s">
         <v>5</v>
@@ -7686,46 +7697,46 @@
         <v>12</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
@@ -7766,7 +7777,7 @@
     </row>
     <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
       <c r="A2" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="35">
@@ -7859,10 +7870,10 @@
     </row>
     <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="40" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
@@ -7952,10 +7963,10 @@
       <c r="R4" s="47"/>
       <c r="S4" s="51"/>
       <c r="V4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
@@ -7982,7 +7993,7 @@
     <row r="6" ht="10.5" customHeight="1">
       <c r="A6" s="52"/>
       <c r="B6" s="60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="62"/>
@@ -8070,7 +8081,7 @@
     <row r="10" ht="10.5" customHeight="1">
       <c r="A10" s="52"/>
       <c r="B10" s="70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="61"/>
@@ -8113,10 +8124,10 @@
     </row>
     <row r="12" ht="10.5" customHeight="1">
       <c r="A12" s="82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="46"/>
@@ -8160,7 +8171,7 @@
     <row r="14" ht="10.5" customHeight="1">
       <c r="A14" s="84"/>
       <c r="B14" s="70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="62"/>
       <c r="D14" s="61"/>
@@ -8204,7 +8215,7 @@
     <row r="16" ht="10.5" customHeight="1">
       <c r="A16" s="84"/>
       <c r="B16" s="68" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="61"/>
@@ -8248,7 +8259,7 @@
     <row r="18" ht="10.5" customHeight="1">
       <c r="A18" s="84"/>
       <c r="B18" s="70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
@@ -8291,10 +8302,10 @@
     </row>
     <row r="20" ht="10.5" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="83" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="47"/>
@@ -8338,7 +8349,7 @@
     <row r="22" ht="10.5" customHeight="1">
       <c r="A22" s="52"/>
       <c r="B22" s="70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -8382,7 +8393,7 @@
     <row r="24" ht="10.5" customHeight="1">
       <c r="A24" s="52"/>
       <c r="B24" s="68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
@@ -8426,7 +8437,7 @@
     <row r="26" ht="10.5" customHeight="1">
       <c r="A26" s="52"/>
       <c r="B26" s="70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
@@ -8470,7 +8481,7 @@
     <row r="28" ht="10.5" customHeight="1">
       <c r="A28" s="52"/>
       <c r="B28" s="68" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="55"/>
       <c r="D28" s="55"/>
@@ -8513,10 +8524,10 @@
     </row>
     <row r="30" ht="10.5" customHeight="1">
       <c r="A30" s="93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="95"/>
       <c r="D30" s="95"/>
@@ -8560,7 +8571,7 @@
     <row r="32" ht="10.5" customHeight="1">
       <c r="A32" s="99"/>
       <c r="B32" s="70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="55"/>
       <c r="D32" s="55"/>
@@ -8604,7 +8615,7 @@
     <row r="34" ht="10.5" customHeight="1">
       <c r="A34" s="99"/>
       <c r="B34" s="70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="62"/>
       <c r="D34" s="62"/>
@@ -8648,7 +8659,7 @@
     <row r="36" ht="10.5" customHeight="1">
       <c r="A36" s="99"/>
       <c r="B36" s="68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
@@ -8692,7 +8703,7 @@
     <row r="38" ht="10.5" customHeight="1">
       <c r="A38" s="99"/>
       <c r="B38" s="70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C38" s="62"/>
       <c r="D38" s="62"/>
@@ -8736,7 +8747,7 @@
     <row r="40" ht="10.5" customHeight="1">
       <c r="A40" s="99"/>
       <c r="B40" s="68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55"/>
@@ -8780,7 +8791,7 @@
     <row r="42" ht="10.5" customHeight="1">
       <c r="A42" s="99"/>
       <c r="B42" s="70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" s="62"/>
       <c r="D42" s="62"/>
@@ -8823,7 +8834,7 @@
     </row>
     <row r="44" ht="10.5" customHeight="1">
       <c r="A44" s="44" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B44" s="45" t="s">
         <v>24</v>
@@ -8867,14 +8878,14 @@
       <c r="R45" s="55"/>
       <c r="S45" s="59"/>
       <c r="V45" s="102" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W45" s="61"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
       <c r="A46" s="52"/>
       <c r="B46" s="103" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="62"/>
@@ -8894,7 +8905,7 @@
       <c r="R46" s="62"/>
       <c r="S46" s="73"/>
       <c r="V46" s="102" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W46" s="54"/>
     </row>
@@ -8919,7 +8930,7 @@
       <c r="R47" s="76"/>
       <c r="S47" s="81"/>
       <c r="V47" s="102" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W47" s="67"/>
     </row>
@@ -8928,7 +8939,7 @@
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8936,7 +8947,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8944,7 +8955,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -9012,37 +9023,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="108" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" s="111" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" s="111"/>
       <c r="H2" s="111"/>
       <c r="I2" s="110"/>
       <c r="J2" s="111" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K2" s="111"/>
       <c r="L2" s="111"/>
       <c r="M2" s="110"/>
       <c r="N2" s="111" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O2" s="111"/>
       <c r="P2" s="111"/>
       <c r="Q2" s="110"/>
       <c r="R2" s="111" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S2" s="112"/>
       <c r="AD2" s="30"/>
@@ -9051,7 +9062,7 @@
       <c r="B3" s="113"/>
       <c r="C3" s="114"/>
       <c r="D3" s="115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="116">
         <v>4</v>
@@ -9099,15 +9110,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="120" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="108" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="122"/>
@@ -9126,7 +9137,7 @@
       <c r="R4" s="125"/>
       <c r="S4" s="126"/>
       <c r="U4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -9152,7 +9163,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="120"/>
       <c r="C6" s="135" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="136"/>
       <c r="E6" s="137"/>
@@ -9171,7 +9182,7 @@
       <c r="R6" s="141"/>
       <c r="S6" s="142"/>
       <c r="U6" s="143" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V6" s="143"/>
     </row>
@@ -9195,13 +9206,13 @@
       <c r="R7" s="133"/>
       <c r="S7" s="134"/>
       <c r="U7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="120"/>
       <c r="C8" s="135" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="136"/>
       <c r="E8" s="137"/>
@@ -9220,7 +9231,7 @@
       <c r="R8" s="141"/>
       <c r="S8" s="142"/>
       <c r="U8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -9246,7 +9257,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="120"/>
       <c r="C10" s="135" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="136"/>
       <c r="E10" s="137"/>
@@ -9287,10 +9298,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="107" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="108" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="121"/>
       <c r="E12" s="122"/>
@@ -9332,7 +9343,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="120"/>
       <c r="C14" s="135" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="154"/>
       <c r="E14" s="137"/>
@@ -9374,7 +9385,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="120"/>
       <c r="C16" s="135" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" s="136"/>
       <c r="E16" s="137"/>
@@ -9415,10 +9426,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="121"/>
       <c r="E18" s="122"/>
@@ -9460,7 +9471,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="120"/>
       <c r="C20" s="135" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" s="136"/>
       <c r="E20" s="137"/>
@@ -9502,7 +9513,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="120"/>
       <c r="C22" s="135" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D22" s="136"/>
       <c r="E22" s="137"/>
@@ -9543,10 +9554,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" s="108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" s="121"/>
       <c r="E24" s="122"/>
@@ -9588,7 +9599,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="120"/>
       <c r="C26" s="135" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" s="136"/>
       <c r="E26" s="137"/>
@@ -9630,7 +9641,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="120"/>
       <c r="C28" s="135" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D28" s="136"/>
       <c r="E28" s="137"/>
@@ -9674,7 +9685,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="167" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30" s="121"/>
       <c r="E30" s="168"/>
@@ -9758,7 +9769,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="173"/>
       <c r="C34" s="127" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D34" s="159"/>
       <c r="E34" s="187"/>
@@ -9778,7 +9789,7 @@
       <c r="S34" s="191"/>
       <c r="U34" s="192"/>
       <c r="V34" s="193" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9802,7 +9813,7 @@
       <c r="S35" s="151"/>
       <c r="U35" s="200"/>
       <c r="V35" s="201" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>date</t>
   </si>
@@ -162,6 +162,9 @@
     <t xml:space="preserve">Placement des composant, routage sur le PCB du prototype</t>
   </si>
   <si>
+    <t xml:space="preserve">Documentation de l'implémentation du prototypage</t>
+  </si>
+  <si>
     <t>Phases</t>
   </si>
   <si>
@@ -240,7 +243,7 @@
     <t xml:space="preserve">Schéma électronique</t>
   </si>
   <si>
-    <t xml:space="preserve">Implémentation breadboard</t>
+    <t>Implémentation</t>
   </si>
   <si>
     <t xml:space="preserve">Tests fonctionnements prototype</t>
@@ -448,7 +451,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,6 +510,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0"/>
+        <bgColor theme="7" tint="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1661,7 +1670,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="203">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1703,12 +1712,6 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1775,6 +1778,10 @@
     </xf>
     <xf fontId="0" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf fontId="3" fillId="5" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1846,6 +1853,8 @@
     <xf fontId="3" fillId="9" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="11" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="11" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="3" fillId="9" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
@@ -1930,7 +1939,7 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="44" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1939,8 +1948,8 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="48" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="49" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1949,8 +1958,8 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="51" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="52" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="54" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="53" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="55" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1966,18 +1975,18 @@
     <xf fontId="0" fillId="2" borderId="56" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="58" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="59" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="60" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="60" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="60" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="61" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="51" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="12" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="59" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="13" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="59" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="14" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1992,10 +2001,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="67" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="68" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="69" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="70" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="68" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="69" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="70" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="71" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
@@ -2006,20 +2015,20 @@
     <xf fontId="0" fillId="0" borderId="74" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="75" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="76" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="74" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="74" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="77" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="78" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="79" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="80" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="75" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="76" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="78" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="79" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="80" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="75" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="13" borderId="76" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="81" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="82" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="83" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="84" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="11" borderId="85" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="12" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="12" borderId="85" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="44" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2035,7 +2044,7 @@
     <xf fontId="0" fillId="0" borderId="89" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="90" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="91" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="12" borderId="92" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="13" borderId="92" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="61" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2912,6 +2921,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>5/6/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5/7/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4644,8 +4656,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E18">
-  <autoFilter ref="B2:E18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E19">
+  <autoFilter ref="B2:E19"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5242,7 +5254,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.059055118110236227</v>
+        <v>5.3956834532374098e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5269,7 +5281,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.14173228346456693</v>
+        <v>0.12949640287769781</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5279,7 +5291,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
@@ -5292,11 +5304,11 @@
       </c>
       <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>17.333333333333332</v>
+        <v>19.333333333333336</v>
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.40944881889763779</v>
+        <v>0.41726618705035973</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5306,7 +5318,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5373,7 +5385,7 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5384,7 +5396,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5411,7 +5423,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>6</v>
@@ -5424,7 +5436,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>42.333333333333329</v>
+        <v>46.333333333333336</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5438,7 +5450,7 @@
         <v>46146</v>
       </c>
       <c r="C12" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>22</v>
@@ -5468,7 +5480,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>32.666666666666671</v>
+        <v>28.666666666666664</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5476,7 +5488,7 @@
         <v>46146</v>
       </c>
       <c r="C14" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>22</v>
@@ -5504,7 +5516,7 @@
         <v>46147</v>
       </c>
       <c r="C16" s="6">
-        <v>0.013888888888888888</v>
+        <v>1.3888888888888888e-002</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>6</v>
@@ -5518,7 +5530,7 @@
         <v>46148</v>
       </c>
       <c r="C17" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>6</v>
@@ -5532,20 +5544,28 @@
         <v>46148</v>
       </c>
       <c r="C18" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="D18" s="18" t="s">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
+      <c r="B19" s="5">
+        <v>46149</v>
+      </c>
+      <c r="C19" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="5"/>
@@ -5672,9 +5692,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5725,200 +5745,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="23"/>
-      <c r="C50" s="24"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="23"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="22"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="23"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="23"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="23"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="23"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="23"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="23"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="23"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="23"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="23"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="23"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="23"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="23"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="23"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="23"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="23"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="23"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="23"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="23"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="23"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="23"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="23"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="23"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="23"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="23"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="23"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="23"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="23"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="23"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="23"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="23"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="23"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="23"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="25"/>
+      <c r="C81" s="23"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5938,13 +5958,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00C10075-003B-48F6-8BAC-00D200EC006B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{006E0016-0074-4396-909B-00DD00E400BD}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00FE00D1-00C8-49B3-B467-0027004200CB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00750024-0007-4B41-AB44-002F008C00E0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5981,1677 +6001,1680 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
-        <f t="array" ref="A2:A8">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="24" t="str" cm="1">
+        <f t="array" ref="A2:A9">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="24" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="24" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="24" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <f/>
         <v>46147</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.1388888888888889</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <f/>
         <v>46148</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0.3125</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27">
+      <c r="A9" s="24">
+        <f/>
+        <v>46149</v>
+      </c>
+      <c r="B9" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>0</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26"/>
-      <c r="C28" s="29">
+      <c r="A28" s="24"/>
+      <c r="C28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26"/>
-      <c r="C29" s="29">
+      <c r="A29" s="24"/>
+      <c r="C29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26"/>
-      <c r="C30" s="29">
+      <c r="A30" s="24"/>
+      <c r="C30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26"/>
-      <c r="C31" s="29">
+      <c r="A31" s="24"/>
+      <c r="C31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26"/>
-      <c r="C32" s="29">
+      <c r="A32" s="24"/>
+      <c r="C32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26"/>
-      <c r="C33" s="29">
+      <c r="A33" s="24"/>
+      <c r="C33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26"/>
-      <c r="C34" s="29">
+      <c r="A34" s="24"/>
+      <c r="C34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26"/>
-      <c r="C35" s="29">
+      <c r="A35" s="24"/>
+      <c r="C35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26"/>
-      <c r="C36" s="29">
+      <c r="A36" s="24"/>
+      <c r="C36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26"/>
-      <c r="C37" s="29">
+      <c r="A37" s="24"/>
+      <c r="C37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26"/>
-      <c r="C38" s="29">
+      <c r="A38" s="24"/>
+      <c r="C38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="24"/>
+      <c r="C39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="28"/>
+      <c r="B43" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="28"/>
+      <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="28"/>
+      <c r="B46" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="29"/>
+      <c r="B47" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="29"/>
+      <c r="B49" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="29"/>
+      <c r="B53" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="29"/>
+      <c r="B55" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="29"/>
+      <c r="B59" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="29"/>
+      <c r="B61" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="29"/>
+      <c r="B65" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="29"/>
+      <c r="B67" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="29"/>
+      <c r="B70" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="29"/>
+      <c r="B71" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="29"/>
+      <c r="B73" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="29"/>
+      <c r="B74" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="29"/>
+      <c r="B76" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="29"/>
+      <c r="B77" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="29"/>
+      <c r="B79" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="29"/>
+      <c r="B80" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="29"/>
+      <c r="B82" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="29"/>
+      <c r="B83" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="29"/>
+      <c r="B85" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="29"/>
+      <c r="B86" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="29"/>
+      <c r="B88" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="29"/>
+      <c r="B89" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="29"/>
+      <c r="B91" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="29"/>
+      <c r="B92" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="29"/>
+      <c r="B93" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="29"/>
+      <c r="B94" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="29"/>
+      <c r="B95" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="29"/>
+      <c r="B96" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="29"/>
+      <c r="B97" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="29"/>
+      <c r="B98" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="29"/>
+      <c r="B99" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="29"/>
+      <c r="B100" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="29"/>
+      <c r="B101" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="29"/>
+      <c r="B102" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="29"/>
+      <c r="B103" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="29"/>
+      <c r="B104" s="25" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="29"/>
+      <c r="B105" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="29"/>
+      <c r="B106" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="29"/>
+      <c r="B107" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="29"/>
+      <c r="B108" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="29"/>
+      <c r="B109" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="29"/>
+      <c r="B110" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="29"/>
+      <c r="B111" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="29"/>
+      <c r="B112" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="29"/>
+      <c r="B113" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="29"/>
+      <c r="B114" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="27"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="27"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="27"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="27"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="27"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="27"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="27"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="27"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="27"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="27"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="27"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="27"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="27"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="27"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="27"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="27"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="27"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="27"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="27"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="27"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="27"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="27"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="27"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="27"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="27"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="27"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="27"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="27"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="27"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="27"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="27"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="27"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="27"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="27"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="27"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="27"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="27"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="27"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="27"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7680,1266 +7703,1269 @@
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="34" t="s">
+    <row r="1" s="30" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="H1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="I1" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="J1" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="M1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="N1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="O1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="Q1" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="R1" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-    </row>
-    <row r="2" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="S1" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35">
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="30"/>
+      <c r="AM1" s="30"/>
+      <c r="AN1" s="30"/>
+      <c r="AO1" s="30"/>
+      <c r="AP1" s="30"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="30"/>
+      <c r="AT1" s="30"/>
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+    </row>
+    <row r="2" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33">
         <v>7</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="33">
         <v>4</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="33">
         <v>4</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="33">
         <v>7</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="33">
         <v>5</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="33">
         <v>7</v>
       </c>
-      <c r="I2" s="36">
-        <v>0</v>
-      </c>
-      <c r="J2" s="36">
-        <v>0</v>
-      </c>
-      <c r="K2" s="35">
+      <c r="I2" s="34">
+        <v>0</v>
+      </c>
+      <c r="J2" s="34">
+        <v>0</v>
+      </c>
+      <c r="K2" s="33">
         <v>5</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="33">
         <v>4</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="33">
         <v>7</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="33">
         <v>4</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="33">
         <v>5</v>
       </c>
-      <c r="P2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
+      <c r="P2" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="33">
         <v>4</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="33">
         <v>7</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="33">
         <v>5</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="32"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-    </row>
-    <row r="3" s="32" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="39" t="s">
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="30"/>
+      <c r="AN2" s="30"/>
+      <c r="AO2" s="30"/>
+      <c r="AP2" s="30"/>
+      <c r="AQ2" s="30"/>
+      <c r="AR2" s="30"/>
+      <c r="AS2" s="30"/>
+      <c r="AT2" s="30"/>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="30"/>
+      <c r="AX2" s="30"/>
+      <c r="AY2" s="30"/>
+      <c r="AZ2" s="30"/>
+      <c r="BA2" s="30"/>
+      <c r="BB2" s="30"/>
+      <c r="BC2" s="30"/>
+    </row>
+    <row r="3" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="40" t="str">
+      <c r="B3" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="38" t="str">
         <f>_xlfn.CONCAT("Conception Matérielle (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Conception Matérielle (27h)</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42" t="str">
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40" t="str">
         <f>_xlfn.CONCAT("Développement Logiciel (",SUM(H2:L2),"h)")</f>
         <v xml:space="preserve">Développement Logiciel (16h)</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42" t="str">
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="40" t="str">
         <f>_xlfn.CONCAT("Tests, Validation et Livrables (",SUM(C2:G2),"h)")</f>
         <v xml:space="preserve">Tests, Validation et Livrables (27h)</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AL3" s="32"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BA3" s="32"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="42">
+        <f>SUM(C2:S2)</f>
+        <v>75</v>
+      </c>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="30"/>
+      <c r="AE3" s="30"/>
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="30"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
+      <c r="AL3" s="30"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="30"/>
+      <c r="AO3" s="30"/>
+      <c r="AP3" s="30"/>
+      <c r="AQ3" s="30"/>
+      <c r="AR3" s="30"/>
+      <c r="AS3" s="30"/>
+      <c r="AT3" s="30"/>
+      <c r="AU3" s="30"/>
+      <c r="AV3" s="30"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="30"/>
+      <c r="AY3" s="30"/>
+      <c r="AZ3" s="30"/>
+      <c r="BA3" s="30"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="30"/>
     </row>
     <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="51"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="50"/>
       <c r="V4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="10.5" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="59"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="58"/>
     </row>
     <row r="6" ht="10.5" customHeight="1">
-      <c r="A6" s="52"/>
-      <c r="B6" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="65"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="64"/>
     </row>
     <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="65"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="64"/>
     </row>
     <row r="8" ht="10.5" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="51"/>
+      <c r="B8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="57"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="58"/>
     </row>
     <row r="9" ht="10.5" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="59"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="58"/>
     </row>
     <row r="10" ht="10.5" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="73"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="72"/>
     </row>
     <row r="11" ht="10.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="76"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="76"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="81"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="80"/>
     </row>
     <row r="12" ht="10.5" customHeight="1">
-      <c r="A12" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="83" t="s">
+      <c r="A12" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
+      <c r="B12" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="50"/>
     </row>
     <row r="13" ht="10.5" customHeight="1">
-      <c r="A13" s="84"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="59"/>
+      <c r="A13" s="83"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="58"/>
     </row>
     <row r="14" ht="10.5" customHeight="1">
-      <c r="A14" s="84"/>
-      <c r="B14" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="65"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="64"/>
     </row>
     <row r="15" ht="10.5" customHeight="1">
-      <c r="A15" s="84"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="65"/>
+      <c r="A15" s="83"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="64"/>
     </row>
     <row r="16" ht="10.5" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="59"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="58"/>
     </row>
     <row r="17" ht="10.5" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="59"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="58"/>
     </row>
     <row r="18" ht="10.5" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="65"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="64"/>
     </row>
     <row r="19" ht="10.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="81"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="S19" s="80"/>
     </row>
     <row r="20" ht="10.5" customHeight="1">
-      <c r="A20" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="83" t="s">
+      <c r="A20" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="51"/>
+      <c r="B20" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="50"/>
     </row>
     <row r="21" ht="10.5" customHeight="1">
-      <c r="A21" s="52"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="59"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="58"/>
     </row>
     <row r="22" ht="10.5" customHeight="1">
-      <c r="A22" s="52"/>
-      <c r="B22" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="65"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="64"/>
     </row>
     <row r="23" ht="10.5" customHeight="1">
-      <c r="A23" s="52"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="65"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="64"/>
     </row>
     <row r="24" ht="10.5" customHeight="1">
-      <c r="A24" s="52"/>
-      <c r="B24" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="59"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="58"/>
     </row>
     <row r="25" ht="10.5" customHeight="1">
-      <c r="A25" s="52"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="59"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="58"/>
     </row>
     <row r="26" ht="10.5" customHeight="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="65"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="64"/>
     </row>
     <row r="27" ht="10.5" customHeight="1">
-      <c r="A27" s="52"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="65"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="64"/>
     </row>
     <row r="28" ht="10.5" customHeight="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="59"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="58"/>
     </row>
     <row r="29" ht="10.5" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="92"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="92"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="93"/>
     </row>
     <row r="30" ht="10.5" customHeight="1">
-      <c r="A30" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="94" t="s">
+      <c r="A30" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="98"/>
+      <c r="B30" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="87"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="96"/>
+      <c r="S30" s="99"/>
     </row>
     <row r="31" ht="10.5" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="65"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="64"/>
     </row>
     <row r="32" ht="10.5" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="59"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="58"/>
     </row>
     <row r="33" ht="10.5" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="57"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="59"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="54"/>
+      <c r="R33" s="54"/>
+      <c r="S33" s="58"/>
     </row>
     <row r="34" ht="10.5" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="70" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="65"/>
+      <c r="A34" s="100"/>
+      <c r="B34" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="64"/>
     </row>
     <row r="35" ht="10.5" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="66"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="65"/>
+      <c r="A35" s="100"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="64"/>
     </row>
     <row r="36" ht="10.5" customHeight="1">
-      <c r="A36" s="99"/>
-      <c r="B36" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="59"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="60"/>
+      <c r="Q36" s="54"/>
+      <c r="R36" s="54"/>
+      <c r="S36" s="58"/>
     </row>
     <row r="37" ht="10.5" customHeight="1">
-      <c r="A37" s="99"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="59"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="56"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="54"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="54"/>
+      <c r="S37" s="58"/>
     </row>
     <row r="38" ht="10.5" customHeight="1">
-      <c r="A38" s="99"/>
-      <c r="B38" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="65"/>
+      <c r="A38" s="100"/>
+      <c r="B38" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="64"/>
     </row>
     <row r="39" ht="10.5" customHeight="1">
-      <c r="A39" s="99"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="65"/>
+      <c r="A39" s="100"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="64"/>
     </row>
     <row r="40" ht="10.5" customHeight="1">
-      <c r="A40" s="99"/>
-      <c r="B40" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="56"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="59"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="54"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="58"/>
     </row>
     <row r="41" ht="10.5" customHeight="1">
-      <c r="A41" s="99"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="59"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="56"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="58"/>
     </row>
     <row r="42" ht="10.5" customHeight="1">
-      <c r="A42" s="99"/>
-      <c r="B42" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="63"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="73"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="72"/>
     </row>
     <row r="43" ht="10.5" customHeight="1">
-      <c r="A43" s="100"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="79"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="81"/>
+      <c r="A43" s="101"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="77"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="75"/>
+      <c r="S43" s="80"/>
     </row>
     <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="101"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="48"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="102"/>
     </row>
     <row r="45" ht="10.5" customHeight="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="59"/>
-      <c r="V45" s="102" t="s">
-        <v>78</v>
-      </c>
-      <c r="W45" s="61"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="54"/>
+      <c r="S45" s="58"/>
+      <c r="V45" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="W45" s="60"/>
     </row>
     <row r="46" ht="10.5" customHeight="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="103" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63"/>
-      <c r="N46" s="64"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="73"/>
-      <c r="V46" s="102" t="s">
+      <c r="A46" s="51"/>
+      <c r="B46" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="W46" s="54"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="72"/>
+      <c r="V46" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="W46" s="53"/>
     </row>
     <row r="47" ht="10.5" customHeight="1">
-      <c r="A47" s="74"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="81"/>
-      <c r="V47" s="102" t="s">
-        <v>81</v>
-      </c>
-      <c r="W47" s="67"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="78"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="75"/>
+      <c r="P47" s="75"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="75"/>
+      <c r="S47" s="80"/>
+      <c r="V47" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="W47" s="66"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="V54" s="105">
+      <c r="V54" s="106">
         <v>46185</v>
       </c>
       <c r="W54" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" ht="14.25">
@@ -8947,7 +8973,7 @@
         <v>17</v>
       </c>
       <c r="W55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" ht="14.25">
@@ -8955,7 +8981,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -9019,801 +9045,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="106"/>
+      <c r="B1" s="107"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="107" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="108" t="s">
+      <c r="B2" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="109" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="110" t="s">
+      <c r="C2" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="E2" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="111" t="s">
+      <c r="F2" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="111" t="s">
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="112" t="s">
         <v>89</v>
       </c>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="111" t="s">
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="AD2" s="30"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="112" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" s="113"/>
+      <c r="AD2" s="28"/>
     </row>
     <row r="3">
-      <c r="B3" s="113"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="115" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="116">
+      <c r="B3" s="114"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="116" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="117">
         <v>4</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="118">
         <v>1</v>
       </c>
-      <c r="G3" s="118">
+      <c r="G3" s="119">
         <v>2</v>
       </c>
-      <c r="H3" s="118">
+      <c r="H3" s="119">
         <v>3</v>
       </c>
-      <c r="I3" s="116">
+      <c r="I3" s="117">
         <v>4</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="118">
         <v>1</v>
       </c>
-      <c r="K3" s="118">
+      <c r="K3" s="119">
         <v>2</v>
       </c>
-      <c r="L3" s="118">
+      <c r="L3" s="119">
         <v>3</v>
       </c>
-      <c r="M3" s="116">
+      <c r="M3" s="117">
         <v>4</v>
       </c>
-      <c r="N3" s="117">
+      <c r="N3" s="118">
         <v>1</v>
       </c>
-      <c r="O3" s="118">
+      <c r="O3" s="119">
         <v>2</v>
       </c>
-      <c r="P3" s="118">
+      <c r="P3" s="119">
         <v>3</v>
       </c>
-      <c r="Q3" s="116">
+      <c r="Q3" s="117">
         <v>4</v>
       </c>
-      <c r="R3" s="117">
+      <c r="R3" s="118">
         <v>1</v>
       </c>
-      <c r="S3" s="119">
+      <c r="S3" s="120">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="120" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="108" t="s">
+      <c r="B4" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
+      <c r="C4" s="109" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="126"/>
+      <c r="S4" s="127"/>
       <c r="U4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="142"/>
-      <c r="U6" s="143" t="s">
+      <c r="B6" s="121"/>
+      <c r="C6" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="V6" s="143"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="141"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="138"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="141"/>
+      <c r="P6" s="141"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="143"/>
+      <c r="U6" s="144" t="s">
+        <v>97</v>
+      </c>
+      <c r="V6" s="144"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="134"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="134"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="135"/>
       <c r="U7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="135" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="142"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="136" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="137"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="142"/>
+      <c r="S8" s="143"/>
       <c r="U8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="134"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="134"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="130"/>
+      <c r="R9" s="134"/>
+      <c r="S9" s="135"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="135" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="137"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="138"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="141"/>
+      <c r="P10" s="141"/>
+      <c r="Q10" s="138"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="143"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="144"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="150"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="151"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="148"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="151"/>
+      <c r="M11" s="148"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="151"/>
+      <c r="P11" s="151"/>
+      <c r="Q11" s="148"/>
+      <c r="R11" s="149"/>
+      <c r="S11" s="152"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="107" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="108" t="s">
+      <c r="B12" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
+      <c r="C12" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="122"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="154"/>
+      <c r="J12" s="126"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="125"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="126"/>
+      <c r="O12" s="125"/>
+      <c r="P12" s="125"/>
+      <c r="Q12" s="123"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="127"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="133"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="133"/>
-      <c r="S13" s="134"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="130"/>
+      <c r="R13" s="134"/>
+      <c r="S13" s="135"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="154"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="136" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="155"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="141"/>
+      <c r="L14" s="141"/>
+      <c r="M14" s="138"/>
+      <c r="N14" s="142"/>
+      <c r="O14" s="141"/>
+      <c r="P14" s="141"/>
+      <c r="Q14" s="138"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="143"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="134"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="156"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="130"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="135"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="141"/>
-      <c r="S16" s="142"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="136" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="137"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="157"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
+      <c r="M16" s="138"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="141"/>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="138"/>
+      <c r="R16" s="142"/>
+      <c r="S16" s="143"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="151"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="146"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="158"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="151"/>
+      <c r="M17" s="148"/>
+      <c r="N17" s="149"/>
+      <c r="O17" s="151"/>
+      <c r="P17" s="151"/>
+      <c r="Q17" s="148"/>
+      <c r="R17" s="149"/>
+      <c r="S17" s="152"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="109" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="108" t="s">
+      <c r="B18" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
+      <c r="C18" s="109" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="122"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="154"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="125"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="125"/>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="126"/>
+      <c r="S18" s="127"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="132"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="129"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="134"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="130"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="133"/>
+      <c r="Q19" s="130"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="135"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="135" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="136" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="137"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="157"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="138"/>
+      <c r="N20" s="142"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="138"/>
+      <c r="R20" s="142"/>
+      <c r="S20" s="143"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="129"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="134"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="130"/>
+      <c r="N21" s="159"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="130"/>
+      <c r="R21" s="134"/>
+      <c r="S21" s="135"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="135" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="141"/>
-      <c r="S22" s="142"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="136" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="137"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="141"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="138"/>
+      <c r="N22" s="142"/>
+      <c r="O22" s="141"/>
+      <c r="P22" s="141"/>
+      <c r="Q22" s="138"/>
+      <c r="R22" s="142"/>
+      <c r="S22" s="143"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="151"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="151"/>
+      <c r="H23" s="151"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="149"/>
+      <c r="K23" s="151"/>
+      <c r="L23" s="151"/>
+      <c r="M23" s="148"/>
+      <c r="N23" s="149"/>
+      <c r="O23" s="151"/>
+      <c r="P23" s="151"/>
+      <c r="Q23" s="148"/>
+      <c r="R23" s="149"/>
+      <c r="S23" s="152"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="109" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="108" t="s">
+      <c r="B24" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="152"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="126"/>
+      <c r="C24" s="109" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="122"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="154"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="153"/>
+      <c r="P24" s="153"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="126"/>
+      <c r="S24" s="127"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="132"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="133"/>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="134"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="133"/>
+      <c r="I25" s="130"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="130"/>
+      <c r="N25" s="134"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="130"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="135"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="135" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="139"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="141"/>
-      <c r="S26" s="142"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="136" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="137"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="141"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="141"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="142"/>
+      <c r="O26" s="140"/>
+      <c r="P26" s="140"/>
+      <c r="Q26" s="138"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="143"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="129"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="134"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="134"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="130"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="130"/>
+      <c r="N27" s="134"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="133"/>
+      <c r="Q27" s="130"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="135"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="135" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="156"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="136" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="137"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="138"/>
+      <c r="N28" s="142"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="140"/>
+      <c r="Q28" s="157"/>
+      <c r="R28" s="142"/>
+      <c r="S28" s="143"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="162"/>
-      <c r="Q29" s="160"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="165"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="164"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="162"/>
+      <c r="K29" s="163"/>
+      <c r="L29" s="164"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="165"/>
+      <c r="O29" s="164"/>
+      <c r="P29" s="163"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="162"/>
+      <c r="S29" s="166"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="166" t="s">
+      <c r="B30" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="167" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="169"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="169"/>
-      <c r="S30" s="172"/>
+      <c r="C30" s="168" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="122"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="170"/>
+      <c r="H30" s="171"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="171"/>
+      <c r="M30" s="172"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="171"/>
+      <c r="P30" s="170"/>
+      <c r="Q30" s="172"/>
+      <c r="R30" s="170"/>
+      <c r="S30" s="173"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="173"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="177"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="134"/>
+      <c r="B31" s="174"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="177"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="179"/>
+      <c r="J31" s="177"/>
+      <c r="K31" s="180"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="179"/>
+      <c r="N31" s="177"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="177"/>
+      <c r="Q31" s="179"/>
+      <c r="R31" s="177"/>
+      <c r="S31" s="135"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174" t="s">
+      <c r="B32" s="174"/>
+      <c r="C32" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="183"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="183"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="184"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="182"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="183"/>
+      <c r="I32" s="184"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="182"/>
+      <c r="L32" s="183"/>
+      <c r="M32" s="184"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="183"/>
+      <c r="P32" s="182"/>
+      <c r="Q32" s="184"/>
+      <c r="R32" s="182"/>
+      <c r="S32" s="185"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="173"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="178"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="177"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="178"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="134"/>
+      <c r="B33" s="174"/>
+      <c r="C33" s="175"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="180"/>
+      <c r="G33" s="177"/>
+      <c r="H33" s="186"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="177"/>
+      <c r="K33" s="180"/>
+      <c r="L33" s="178"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="177"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="177"/>
+      <c r="Q33" s="179"/>
+      <c r="R33" s="177"/>
+      <c r="S33" s="135"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="173"/>
-      <c r="C34" s="127" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="188"/>
-      <c r="S34" s="191"/>
-      <c r="U34" s="192"/>
-      <c r="V34" s="193" t="s">
+      <c r="B34" s="174"/>
+      <c r="C34" s="128" t="s">
         <v>115</v>
       </c>
+      <c r="D34" s="160"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="189"/>
+      <c r="G34" s="189"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="189"/>
+      <c r="K34" s="189"/>
+      <c r="L34" s="190"/>
+      <c r="M34" s="191"/>
+      <c r="N34" s="189"/>
+      <c r="O34" s="190"/>
+      <c r="P34" s="189"/>
+      <c r="Q34" s="191"/>
+      <c r="R34" s="189"/>
+      <c r="S34" s="192"/>
+      <c r="U34" s="193"/>
+      <c r="V34" s="194" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="194"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="198"/>
-      <c r="M35" s="199"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="151"/>
-      <c r="U35" s="200"/>
-      <c r="V35" s="201" t="s">
-        <v>116</v>
+      <c r="B35" s="195"/>
+      <c r="C35" s="196"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="197"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="200"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="198"/>
+      <c r="L35" s="199"/>
+      <c r="M35" s="200"/>
+      <c r="N35" s="198"/>
+      <c r="O35" s="199"/>
+      <c r="P35" s="198"/>
+      <c r="Q35" s="200"/>
+      <c r="R35" s="198"/>
+      <c r="S35" s="152"/>
+      <c r="U35" s="201"/>
+      <c r="V35" s="202" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/HoferL - JournalPlanif - M7.xlsx
+++ b/Documents/HoferL - JournalPlanif - M7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>date</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation de l'implémentation du prototypage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discution avec JT (ELT2) pour l'impression de la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction de la violation de la RDC.</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1670,7 +1676,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="205">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1712,6 +1718,12 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -4656,8 +4668,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E19">
-  <autoFilter ref="B2:E19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E21">
+  <autoFilter ref="B2:E21"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5254,7 +5266,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.3956834532374098e-002</v>
+        <v>5.1194539249146756e-002</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -5281,7 +5293,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.12949640287769781</v>
+        <v>0.1228668941979522</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13"/>
@@ -5308,7 +5320,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.41726618705035973</v>
+        <v>0.39590443686006827</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="13"/>
@@ -5358,11 +5370,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0</v>
+        <v>2.0477815699658702e-002</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="13"/>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="4"/>
@@ -5436,7 +5448,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>46.333333333333336</v>
+        <v>48.833333333333336</v>
       </c>
       <c r="I11" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
@@ -5480,7 +5492,7 @@
       </c>
       <c r="H13" s="10">
         <f>SUM(Plannification!C2:S2)-H11</f>
-        <v>28.666666666666664</v>
+        <v>26.166666666666664</v>
       </c>
     </row>
     <row r="14" ht="42.75">
@@ -5568,16 +5580,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
+      <c r="B20" s="5">
+        <v>46149</v>
+      </c>
+      <c r="C20" s="6">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
+      <c r="B21" s="5">
+        <v>46149</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="5"/>
@@ -5692,9 +5720,9 @@
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="22"/>
     </row>
     <row r="41">
       <c r="B41" s="5"/>
@@ -5745,200 +5773,200 @@
       <c r="E48" s="8"/>
     </row>
     <row r="49" ht="28.5">
-      <c r="B49" s="21"/>
-      <c r="C49" s="22"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="7"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" ht="42.75">
-      <c r="B50" s="21"/>
-      <c r="C50" s="22"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="7"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" ht="57">
-      <c r="B51" s="21"/>
-      <c r="C51" s="22"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="7"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" ht="28.5">
-      <c r="B52" s="21"/>
-      <c r="C52" s="22"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53" ht="28.5">
-      <c r="B53" s="21"/>
-      <c r="C53" s="22"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="21"/>
-      <c r="C54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="21"/>
-      <c r="C55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="25"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="21"/>
-      <c r="C56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="25"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="21"/>
-      <c r="C57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="21"/>
-      <c r="C58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="21"/>
-      <c r="C59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="21"/>
-      <c r="C60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="21"/>
-      <c r="C61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="21"/>
-      <c r="C62" s="23"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="21"/>
-      <c r="C63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="21"/>
-      <c r="C64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="21"/>
-      <c r="C65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="21"/>
-      <c r="C66" s="23"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="21"/>
-      <c r="C67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="21"/>
-      <c r="C68" s="23"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="21"/>
-      <c r="C69" s="23"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="21"/>
-      <c r="C70" s="23"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="21"/>
-      <c r="C71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="21"/>
-      <c r="C72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="21"/>
-      <c r="C73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="21"/>
-      <c r="C74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="21"/>
-      <c r="C75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="23"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5958,13 +5986,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{006E0016-0074-4396-909B-00DD00E400BD}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{003600E8-006D-4CC2-9228-00AA001F0084}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$11</xm:f>
           </x14:formula1>
           <xm:sqref>D8 D13:D56 D11 D12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00750024-0007-4B41-AB44-002F008C00E0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00940001-00B5-4FBA-AB6C-005300D1007A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6001,1680 +6029,1680 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str" cm="1">
+      <c r="A2" s="26" t="str" cm="1">
         <f t="array" ref="A2:A9">_xlfn.UNIQUE(Journal[date])</f>
         <v>22.04.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.04.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.10416666666666667</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.04.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>01.05.2026</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24">
+      <c r="A6" s="26">
         <f/>
         <v>46146</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.3125</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24">
+      <c r="A7" s="26">
         <f/>
         <v>46147</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.1388888888888889</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="26">
         <f/>
         <v>46148</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0.39583333333333331</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="26">
         <f/>
         <v>46149</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.18749999999999997</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24"/>
-      <c r="C28" s="27">
+      <c r="A28" s="26"/>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="C29" s="27">
+      <c r="A29" s="26"/>
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24"/>
-      <c r="C30" s="27">
+      <c r="A30" s="26"/>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24"/>
-      <c r="C31" s="27">
+      <c r="A31" s="26"/>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24"/>
-      <c r="C32" s="27">
+      <c r="A32" s="26"/>
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24"/>
-      <c r="C33" s="27">
+      <c r="A33" s="26"/>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24"/>
-      <c r="C34" s="27">
+      <c r="A34" s="26"/>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24"/>
-      <c r="C35" s="27">
+      <c r="A35" s="26"/>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24"/>
-      <c r="C36" s="27">
+      <c r="A36" s="26"/>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24"/>
-      <c r="C37" s="27">
+      <c r="A37" s="26"/>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24"/>
-      <c r="C38" s="27">
+      <c r="A38" s="26"/>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="31"/>
+   